--- a/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E0509D-2D44-4ACE-A3F3-7F886FFA7FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476AD030-5D53-482B-A3B3-976CAB9E6F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MilestoneParam" sheetId="1" r:id="rId1"/>
@@ -122,9 +122,6 @@
     <t>MonPointInc</t>
   </si>
   <si>
-    <t>TerPointInc</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -162,6 +159,10 @@
   </si>
   <si>
     <t>MonsterKillReq</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TerPointInc</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -238,7 +239,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -455,32 +456,32 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AB1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="22.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -488,11 +489,11 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
+      <c r="I1" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -513,36 +514,36 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -563,9 +564,9 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1"/>
       <c r="D3" s="1"/>
@@ -592,9 +593,9 @@
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1"/>
       <c r="D4" s="1"/>
@@ -621,7 +622,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>0</v>
@@ -669,7 +670,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1</v>
@@ -711,7 +712,7 @@
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
@@ -753,7 +754,7 @@
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
@@ -795,7 +796,7 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
@@ -837,7 +838,7 @@
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
     </row>
-    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>5</v>
@@ -879,7 +880,7 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>6</v>
@@ -922,7 +923,7 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>7</v>
@@ -965,7 +966,7 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
     </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>8</v>
@@ -1009,7 +1010,7 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
     </row>
-    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>9</v>
@@ -1055,7 +1056,7 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>10</v>
@@ -1101,7 +1102,7 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
     </row>
-    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>11</v>
@@ -1147,7 +1148,7 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>12</v>
@@ -1193,7 +1194,7 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
@@ -1239,7 +1240,7 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>14</v>
@@ -1285,7 +1286,7 @@
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
     </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>15</v>
@@ -1331,7 +1332,7 @@
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
     </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>16</v>
@@ -1377,7 +1378,7 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>17</v>
@@ -1423,7 +1424,7 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>18</v>
@@ -1469,7 +1470,7 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>19</v>
@@ -1515,7 +1516,7 @@
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
     </row>
-    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>20</v>
@@ -1561,7 +1562,7 @@
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
     </row>
-    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>21</v>
@@ -1607,7 +1608,7 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>22</v>
@@ -1652,7 +1653,7 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>23</v>
@@ -1698,7 +1699,7 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>24</v>
@@ -1744,7 +1745,7 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>25</v>
@@ -1790,7 +1791,7 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
     </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1820,7 +1821,7 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1850,7 +1851,7 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1880,7 +1881,7 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
     </row>
-    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1910,7 +1911,7 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
     </row>
-    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1940,7 +1941,7 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
     </row>
-    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1970,7 +1971,7 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2000,7 +2001,7 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2030,7 +2031,7 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
     </row>
-    <row r="39" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2060,7 +2061,7 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
     </row>
-    <row r="40" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2090,7 +2091,7 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
     </row>
-    <row r="41" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2120,7 +2121,7 @@
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
     </row>
-    <row r="42" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2150,7 +2151,7 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
     </row>
-    <row r="43" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2180,7 +2181,7 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
     </row>
-    <row r="44" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2210,7 +2211,7 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
     </row>
-    <row r="45" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2240,7 +2241,7 @@
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
     </row>
-    <row r="46" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2270,7 +2271,7 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2300,7 +2301,7 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
     </row>
-    <row r="48" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2330,7 +2331,7 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
     </row>
-    <row r="49" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2360,7 +2361,7 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2390,7 +2391,7 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
     </row>
-    <row r="51" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2420,7 +2421,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2450,7 +2451,7 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
     </row>
-    <row r="53" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2480,7 +2481,7 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
     </row>
-    <row r="54" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2510,7 +2511,7 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
     </row>
-    <row r="55" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2540,7 +2541,7 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2570,7 +2571,7 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2600,7 +2601,7 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2630,7 +2631,7 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2660,7 +2661,7 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2690,7 +2691,7 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2720,7 +2721,7 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2750,7 +2751,7 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2780,7 +2781,7 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2810,7 +2811,7 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2840,7 +2841,7 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="66" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2870,7 +2871,7 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
     </row>
-    <row r="67" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2900,7 +2901,7 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
     </row>
-    <row r="68" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2930,7 +2931,7 @@
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
     </row>
-    <row r="69" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2960,7 +2961,7 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
     </row>
-    <row r="70" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2990,7 +2991,7 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3020,7 +3021,7 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3050,7 +3051,7 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
     </row>
-    <row r="73" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3080,7 +3081,7 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
     </row>
-    <row r="74" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3110,7 +3111,7 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
     </row>
-    <row r="75" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3140,7 +3141,7 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
     </row>
-    <row r="76" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3170,7 +3171,7 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
     </row>
-    <row r="77" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3200,7 +3201,7 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
     </row>
-    <row r="78" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3230,7 +3231,7 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
     </row>
-    <row r="79" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3260,7 +3261,7 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
     </row>
-    <row r="80" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3290,7 +3291,7 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
     </row>
-    <row r="81" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3320,7 +3321,7 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
     </row>
-    <row r="82" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3350,7 +3351,7 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
     </row>
-    <row r="83" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3380,7 +3381,7 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
     </row>
-    <row r="84" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3410,7 +3411,7 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
     </row>
-    <row r="85" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3440,7 +3441,7 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
     </row>
-    <row r="86" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3470,7 +3471,7 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
     </row>
-    <row r="87" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3500,7 +3501,7 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
     </row>
-    <row r="88" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3530,7 +3531,7 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
     </row>
-    <row r="89" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3560,7 +3561,7 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
     </row>
-    <row r="90" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3590,7 +3591,7 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
     </row>
-    <row r="91" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3620,7 +3621,7 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
     </row>
-    <row r="92" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3650,7 +3651,7 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
     </row>
-    <row r="93" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3680,7 +3681,7 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
     </row>
-    <row r="94" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3710,7 +3711,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3740,7 +3741,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3770,7 +3771,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3800,7 +3801,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3830,7 +3831,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3860,7 +3861,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3890,7 +3891,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3920,7 +3921,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3950,7 +3951,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3980,7 +3981,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4010,7 +4011,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4040,7 +4041,7 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
     </row>
-    <row r="106" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4070,7 +4071,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4100,7 +4101,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4130,7 +4131,7 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
     </row>
-    <row r="109" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4160,7 +4161,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4190,7 +4191,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4220,7 +4221,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4250,7 +4251,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4280,7 +4281,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4310,7 +4311,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4340,7 +4341,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4370,7 +4371,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4400,7 +4401,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4430,7 +4431,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4460,7 +4461,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4490,7 +4491,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4520,7 +4521,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4550,7 +4551,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4580,7 +4581,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4610,7 +4611,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4640,7 +4641,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4670,7 +4671,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4700,7 +4701,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4730,7 +4731,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4760,7 +4761,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4790,7 +4791,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4820,7 +4821,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4850,7 +4851,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4880,7 +4881,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4910,7 +4911,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4940,7 +4941,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4970,7 +4971,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5000,7 +5001,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5030,7 +5031,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5060,7 +5061,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5090,7 +5091,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5120,7 +5121,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5150,7 +5151,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5180,7 +5181,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5210,7 +5211,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5240,7 +5241,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5270,7 +5271,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5300,7 +5301,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5330,7 +5331,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5360,7 +5361,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5390,7 +5391,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5420,7 +5421,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5450,7 +5451,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5480,7 +5481,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5510,7 +5511,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5540,7 +5541,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5570,7 +5571,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5600,7 +5601,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5630,7 +5631,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5660,7 +5661,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5690,7 +5691,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5720,7 +5721,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5750,7 +5751,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5780,7 +5781,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5810,7 +5811,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5840,7 +5841,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5870,7 +5871,7 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
     </row>
-    <row r="167" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5900,7 +5901,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5930,7 +5931,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5960,7 +5961,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5990,7 +5991,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6020,7 +6021,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6050,7 +6051,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6080,7 +6081,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6110,7 +6111,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6140,7 +6141,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6170,7 +6171,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6200,7 +6201,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6230,7 +6231,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6260,7 +6261,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6290,7 +6291,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6320,7 +6321,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6350,7 +6351,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6380,7 +6381,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6410,7 +6411,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6440,7 +6441,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6470,7 +6471,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6500,7 +6501,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6530,7 +6531,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6560,7 +6561,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6590,7 +6591,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6620,7 +6621,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6650,7 +6651,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6680,7 +6681,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6710,7 +6711,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6740,7 +6741,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6770,7 +6771,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6800,7 +6801,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6830,7 +6831,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6860,7 +6861,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6890,7 +6891,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6920,7 +6921,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6950,7 +6951,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6980,7 +6981,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7010,7 +7011,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7040,7 +7041,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7070,7 +7071,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7100,7 +7101,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7130,7 +7131,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7160,7 +7161,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7190,7 +7191,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7220,7 +7221,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7250,7 +7251,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7280,7 +7281,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7310,7 +7311,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7340,7 +7341,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7370,7 +7371,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7400,7 +7401,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7430,7 +7431,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7460,7 +7461,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7490,7 +7491,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7520,7 +7521,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7550,7 +7551,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7580,7 +7581,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7610,7 +7611,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7640,7 +7641,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7670,7 +7671,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7700,7 +7701,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7730,7 +7731,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7760,7 +7761,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7790,7 +7791,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7820,7 +7821,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7850,7 +7851,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7880,7 +7881,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -7910,7 +7911,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7940,7 +7941,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -7970,7 +7971,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8000,7 +8001,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8030,7 +8031,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8060,7 +8061,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8090,7 +8091,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8120,7 +8121,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8150,7 +8151,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8180,7 +8181,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8210,7 +8211,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8240,7 +8241,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8270,7 +8271,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8300,7 +8301,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8330,7 +8331,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8360,7 +8361,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8390,7 +8391,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8420,7 +8421,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8450,7 +8451,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8480,7 +8481,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8510,7 +8511,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8540,7 +8541,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8570,7 +8571,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8600,7 +8601,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8630,7 +8631,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8660,7 +8661,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8690,7 +8691,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8720,7 +8721,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8750,7 +8751,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8780,7 +8781,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8810,7 +8811,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -8840,7 +8841,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -8870,7 +8871,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -8900,7 +8901,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -8930,7 +8931,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -8960,7 +8961,7 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
     </row>
-    <row r="270" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -8990,7 +8991,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9020,7 +9021,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9050,7 +9051,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9080,7 +9081,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9110,7 +9111,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
     </row>
-    <row r="275" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9140,7 +9141,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9170,7 +9171,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9200,7 +9201,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9230,7 +9231,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9260,7 +9261,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9290,7 +9291,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9320,7 +9321,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9350,7 +9351,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9380,7 +9381,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9410,7 +9411,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9440,7 +9441,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -9470,7 +9471,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -9500,7 +9501,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -9530,7 +9531,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -9560,7 +9561,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -9590,7 +9591,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -9620,7 +9621,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -9650,7 +9651,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -9680,7 +9681,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -9710,7 +9711,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -9740,7 +9741,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -9770,7 +9771,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -9800,7 +9801,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -9830,7 +9831,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -9860,7 +9861,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -9890,7 +9891,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -9920,7 +9921,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -9950,7 +9951,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -9980,7 +9981,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10010,7 +10011,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10040,7 +10041,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10070,7 +10071,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10100,7 +10101,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10130,7 +10131,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10160,7 +10161,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10190,7 +10191,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10220,7 +10221,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10250,7 +10251,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10280,7 +10281,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10310,7 +10311,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10340,7 +10341,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10370,7 +10371,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10400,7 +10401,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -10430,7 +10431,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -10460,7 +10461,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -10490,7 +10491,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -10520,7 +10521,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -10550,7 +10551,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -10580,7 +10581,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10610,7 +10611,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10640,7 +10641,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -10670,7 +10671,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -10700,7 +10701,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -10730,7 +10731,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -10760,7 +10761,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -10790,7 +10791,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -10820,7 +10821,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -10850,7 +10851,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -10880,7 +10881,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -10910,7 +10911,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -10940,7 +10941,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -10970,7 +10971,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11000,7 +11001,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11030,7 +11031,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11060,7 +11061,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11090,7 +11091,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11120,7 +11121,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11150,7 +11151,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11180,7 +11181,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11210,7 +11211,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11240,7 +11241,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11270,7 +11271,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11300,7 +11301,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11330,7 +11331,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11360,7 +11361,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11390,7 +11391,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11420,7 +11421,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11450,7 +11451,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -11480,7 +11481,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -11510,7 +11511,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -11540,7 +11541,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -11570,7 +11571,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -11600,7 +11601,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -11630,7 +11631,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -11660,7 +11661,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -11690,7 +11691,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -11720,7 +11721,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -11750,7 +11751,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -11780,7 +11781,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -11810,7 +11811,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -11840,7 +11841,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -11870,7 +11871,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -11900,7 +11901,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -11930,7 +11931,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -11960,7 +11961,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -11990,7 +11991,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12020,7 +12021,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12050,7 +12051,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12080,7 +12081,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12110,7 +12111,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12140,7 +12141,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12170,7 +12171,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12200,7 +12201,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12230,7 +12231,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12260,7 +12261,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12290,7 +12291,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12320,7 +12321,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12350,7 +12351,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12380,7 +12381,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12410,7 +12411,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12440,7 +12441,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12470,7 +12471,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12500,7 +12501,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12530,7 +12531,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -12560,7 +12561,7 @@
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
     </row>
-    <row r="390" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -12590,7 +12591,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -12620,7 +12621,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -12650,7 +12651,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -12680,7 +12681,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -12710,7 +12711,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -12740,7 +12741,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -12770,7 +12771,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -12800,7 +12801,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -12830,7 +12831,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -12860,7 +12861,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -12890,7 +12891,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -12920,7 +12921,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -12950,7 +12951,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -12980,7 +12981,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13010,7 +13011,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13040,7 +13041,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13070,7 +13071,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13100,7 +13101,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13130,7 +13131,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13160,7 +13161,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13190,7 +13191,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13220,7 +13221,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13250,7 +13251,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13280,7 +13281,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13310,7 +13311,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13340,7 +13341,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13370,7 +13371,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13400,7 +13401,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13430,7 +13431,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13460,7 +13461,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13490,7 +13491,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -13520,7 +13521,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -13550,7 +13551,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -13580,7 +13581,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -13610,7 +13611,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -13640,7 +13641,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -13670,7 +13671,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -13700,7 +13701,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -13730,7 +13731,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -13760,7 +13761,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -13790,7 +13791,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -13820,7 +13821,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -13850,7 +13851,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -13880,7 +13881,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -13910,7 +13911,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -13940,7 +13941,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -13970,7 +13971,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14000,7 +14001,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14030,7 +14031,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14060,7 +14061,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14090,7 +14091,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14120,7 +14121,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14150,7 +14151,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14180,7 +14181,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14210,7 +14211,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14240,7 +14241,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14270,7 +14271,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14300,7 +14301,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14330,7 +14331,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14360,7 +14361,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14390,7 +14391,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14420,7 +14421,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14450,7 +14451,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -14480,7 +14481,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -14510,7 +14511,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -14540,7 +14541,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -14570,7 +14571,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -14600,7 +14601,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -14630,7 +14631,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -14660,7 +14661,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -14690,7 +14691,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -14720,7 +14721,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -14750,7 +14751,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -14780,7 +14781,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -14810,7 +14811,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -14840,7 +14841,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -14870,7 +14871,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -14900,7 +14901,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -14930,7 +14931,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -14960,7 +14961,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -14990,7 +14991,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15020,7 +15021,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15050,7 +15051,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15080,7 +15081,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15110,7 +15111,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15140,7 +15141,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15170,7 +15171,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15200,7 +15201,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15230,7 +15231,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15260,7 +15261,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15290,7 +15291,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15320,7 +15321,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15350,7 +15351,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15380,7 +15381,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -15410,7 +15411,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -15440,7 +15441,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -15470,7 +15471,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -15500,7 +15501,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -15530,7 +15531,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -15560,7 +15561,7 @@
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
     </row>
-    <row r="490" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -15590,7 +15591,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -15620,7 +15621,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -15650,7 +15651,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -15680,7 +15681,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -15710,7 +15711,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -15740,7 +15741,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -15770,7 +15771,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -15800,7 +15801,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -15830,7 +15831,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -15860,7 +15861,7 @@
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
     </row>
-    <row r="500" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -15890,7 +15891,7 @@
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
     </row>
-    <row r="501" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -15920,7 +15921,7 @@
       <c r="AA501" s="1"/>
       <c r="AB501" s="1"/>
     </row>
-    <row r="502" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -15950,7 +15951,7 @@
       <c r="AA502" s="1"/>
       <c r="AB502" s="1"/>
     </row>
-    <row r="503" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -15980,7 +15981,7 @@
       <c r="AA503" s="1"/>
       <c r="AB503" s="1"/>
     </row>
-    <row r="504" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16010,7 +16011,7 @@
       <c r="AA504" s="1"/>
       <c r="AB504" s="1"/>
     </row>
-    <row r="505" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16040,7 +16041,7 @@
       <c r="AA505" s="1"/>
       <c r="AB505" s="1"/>
     </row>
-    <row r="506" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16070,7 +16071,7 @@
       <c r="AA506" s="1"/>
       <c r="AB506" s="1"/>
     </row>
-    <row r="507" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16100,7 +16101,7 @@
       <c r="AA507" s="1"/>
       <c r="AB507" s="1"/>
     </row>
-    <row r="508" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16130,7 +16131,7 @@
       <c r="AA508" s="1"/>
       <c r="AB508" s="1"/>
     </row>
-    <row r="509" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16160,7 +16161,7 @@
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
     </row>
-    <row r="510" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16190,7 +16191,7 @@
       <c r="AA510" s="1"/>
       <c r="AB510" s="1"/>
     </row>
-    <row r="511" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16220,7 +16221,7 @@
       <c r="AA511" s="1"/>
       <c r="AB511" s="1"/>
     </row>
-    <row r="512" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16250,7 +16251,7 @@
       <c r="AA512" s="1"/>
       <c r="AB512" s="1"/>
     </row>
-    <row r="513" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16280,7 +16281,7 @@
       <c r="AA513" s="1"/>
       <c r="AB513" s="1"/>
     </row>
-    <row r="514" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16310,7 +16311,7 @@
       <c r="AA514" s="1"/>
       <c r="AB514" s="1"/>
     </row>
-    <row r="515" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16340,7 +16341,7 @@
       <c r="AA515" s="1"/>
       <c r="AB515" s="1"/>
     </row>
-    <row r="516" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -16370,7 +16371,7 @@
       <c r="AA516" s="1"/>
       <c r="AB516" s="1"/>
     </row>
-    <row r="517" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -16400,7 +16401,7 @@
       <c r="AA517" s="1"/>
       <c r="AB517" s="1"/>
     </row>
-    <row r="518" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -16430,7 +16431,7 @@
       <c r="AA518" s="1"/>
       <c r="AB518" s="1"/>
     </row>
-    <row r="519" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -16460,7 +16461,7 @@
       <c r="AA519" s="1"/>
       <c r="AB519" s="1"/>
     </row>
-    <row r="520" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -16490,7 +16491,7 @@
       <c r="AA520" s="1"/>
       <c r="AB520" s="1"/>
     </row>
-    <row r="521" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -16520,7 +16521,7 @@
       <c r="AA521" s="1"/>
       <c r="AB521" s="1"/>
     </row>
-    <row r="522" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -16550,7 +16551,7 @@
       <c r="AA522" s="1"/>
       <c r="AB522" s="1"/>
     </row>
-    <row r="523" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -16580,7 +16581,7 @@
       <c r="AA523" s="1"/>
       <c r="AB523" s="1"/>
     </row>
-    <row r="524" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -16610,7 +16611,7 @@
       <c r="AA524" s="1"/>
       <c r="AB524" s="1"/>
     </row>
-    <row r="525" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -16640,7 +16641,7 @@
       <c r="AA525" s="1"/>
       <c r="AB525" s="1"/>
     </row>
-    <row r="526" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -16670,7 +16671,7 @@
       <c r="AA526" s="1"/>
       <c r="AB526" s="1"/>
     </row>
-    <row r="527" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -16700,7 +16701,7 @@
       <c r="AA527" s="1"/>
       <c r="AB527" s="1"/>
     </row>
-    <row r="528" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -16730,7 +16731,7 @@
       <c r="AA528" s="1"/>
       <c r="AB528" s="1"/>
     </row>
-    <row r="529" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -16760,7 +16761,7 @@
       <c r="AA529" s="1"/>
       <c r="AB529" s="1"/>
     </row>
-    <row r="530" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -16790,7 +16791,7 @@
       <c r="AA530" s="1"/>
       <c r="AB530" s="1"/>
     </row>
-    <row r="531" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -16820,7 +16821,7 @@
       <c r="AA531" s="1"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -16850,7 +16851,7 @@
       <c r="AA532" s="1"/>
       <c r="AB532" s="1"/>
     </row>
-    <row r="533" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -16880,7 +16881,7 @@
       <c r="AA533" s="1"/>
       <c r="AB533" s="1"/>
     </row>
-    <row r="534" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -16910,7 +16911,7 @@
       <c r="AA534" s="1"/>
       <c r="AB534" s="1"/>
     </row>
-    <row r="535" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -16940,7 +16941,7 @@
       <c r="AA535" s="1"/>
       <c r="AB535" s="1"/>
     </row>
-    <row r="536" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -16970,7 +16971,7 @@
       <c r="AA536" s="1"/>
       <c r="AB536" s="1"/>
     </row>
-    <row r="537" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17000,7 +17001,7 @@
       <c r="AA537" s="1"/>
       <c r="AB537" s="1"/>
     </row>
-    <row r="538" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17030,7 +17031,7 @@
       <c r="AA538" s="1"/>
       <c r="AB538" s="1"/>
     </row>
-    <row r="539" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17060,7 +17061,7 @@
       <c r="AA539" s="1"/>
       <c r="AB539" s="1"/>
     </row>
-    <row r="540" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17090,7 +17091,7 @@
       <c r="AA540" s="1"/>
       <c r="AB540" s="1"/>
     </row>
-    <row r="541" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17120,7 +17121,7 @@
       <c r="AA541" s="1"/>
       <c r="AB541" s="1"/>
     </row>
-    <row r="542" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17150,7 +17151,7 @@
       <c r="AA542" s="1"/>
       <c r="AB542" s="1"/>
     </row>
-    <row r="543" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17180,7 +17181,7 @@
       <c r="AA543" s="1"/>
       <c r="AB543" s="1"/>
     </row>
-    <row r="544" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17210,7 +17211,7 @@
       <c r="AA544" s="1"/>
       <c r="AB544" s="1"/>
     </row>
-    <row r="545" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17240,7 +17241,7 @@
       <c r="AA545" s="1"/>
       <c r="AB545" s="1"/>
     </row>
-    <row r="546" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -17270,7 +17271,7 @@
       <c r="AA546" s="1"/>
       <c r="AB546" s="1"/>
     </row>
-    <row r="547" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -17300,7 +17301,7 @@
       <c r="AA547" s="1"/>
       <c r="AB547" s="1"/>
     </row>
-    <row r="548" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -17330,7 +17331,7 @@
       <c r="AA548" s="1"/>
       <c r="AB548" s="1"/>
     </row>
-    <row r="549" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -17360,7 +17361,7 @@
       <c r="AA549" s="1"/>
       <c r="AB549" s="1"/>
     </row>
-    <row r="550" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -17390,7 +17391,7 @@
       <c r="AA550" s="1"/>
       <c r="AB550" s="1"/>
     </row>
-    <row r="551" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -17420,7 +17421,7 @@
       <c r="AA551" s="1"/>
       <c r="AB551" s="1"/>
     </row>
-    <row r="552" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -17450,7 +17451,7 @@
       <c r="AA552" s="1"/>
       <c r="AB552" s="1"/>
     </row>
-    <row r="553" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -17480,7 +17481,7 @@
       <c r="AA553" s="1"/>
       <c r="AB553" s="1"/>
     </row>
-    <row r="554" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -17510,7 +17511,7 @@
       <c r="AA554" s="1"/>
       <c r="AB554" s="1"/>
     </row>
-    <row r="555" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -17540,7 +17541,7 @@
       <c r="AA555" s="1"/>
       <c r="AB555" s="1"/>
     </row>
-    <row r="556" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -17570,7 +17571,7 @@
       <c r="AA556" s="1"/>
       <c r="AB556" s="1"/>
     </row>
-    <row r="557" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -17600,7 +17601,7 @@
       <c r="AA557" s="1"/>
       <c r="AB557" s="1"/>
     </row>
-    <row r="558" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -17630,7 +17631,7 @@
       <c r="AA558" s="1"/>
       <c r="AB558" s="1"/>
     </row>
-    <row r="559" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -17660,7 +17661,7 @@
       <c r="AA559" s="1"/>
       <c r="AB559" s="1"/>
     </row>
-    <row r="560" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -17690,7 +17691,7 @@
       <c r="AA560" s="1"/>
       <c r="AB560" s="1"/>
     </row>
-    <row r="561" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -17720,7 +17721,7 @@
       <c r="AA561" s="1"/>
       <c r="AB561" s="1"/>
     </row>
-    <row r="562" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -17750,7 +17751,7 @@
       <c r="AA562" s="1"/>
       <c r="AB562" s="1"/>
     </row>
-    <row r="563" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -17780,7 +17781,7 @@
       <c r="AA563" s="1"/>
       <c r="AB563" s="1"/>
     </row>
-    <row r="564" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -17810,7 +17811,7 @@
       <c r="AA564" s="1"/>
       <c r="AB564" s="1"/>
     </row>
-    <row r="565" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -17840,7 +17841,7 @@
       <c r="AA565" s="1"/>
       <c r="AB565" s="1"/>
     </row>
-    <row r="566" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -17870,7 +17871,7 @@
       <c r="AA566" s="1"/>
       <c r="AB566" s="1"/>
     </row>
-    <row r="567" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -17900,7 +17901,7 @@
       <c r="AA567" s="1"/>
       <c r="AB567" s="1"/>
     </row>
-    <row r="568" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -17930,7 +17931,7 @@
       <c r="AA568" s="1"/>
       <c r="AB568" s="1"/>
     </row>
-    <row r="569" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -17960,7 +17961,7 @@
       <c r="AA569" s="1"/>
       <c r="AB569" s="1"/>
     </row>
-    <row r="570" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -17990,7 +17991,7 @@
       <c r="AA570" s="1"/>
       <c r="AB570" s="1"/>
     </row>
-    <row r="571" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18020,7 +18021,7 @@
       <c r="AA571" s="1"/>
       <c r="AB571" s="1"/>
     </row>
-    <row r="572" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18050,7 +18051,7 @@
       <c r="AA572" s="1"/>
       <c r="AB572" s="1"/>
     </row>
-    <row r="573" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18080,7 +18081,7 @@
       <c r="AA573" s="1"/>
       <c r="AB573" s="1"/>
     </row>
-    <row r="574" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18110,7 +18111,7 @@
       <c r="AA574" s="1"/>
       <c r="AB574" s="1"/>
     </row>
-    <row r="575" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18140,7 +18141,7 @@
       <c r="AA575" s="1"/>
       <c r="AB575" s="1"/>
     </row>
-    <row r="576" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18170,7 +18171,7 @@
       <c r="AA576" s="1"/>
       <c r="AB576" s="1"/>
     </row>
-    <row r="577" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18200,7 +18201,7 @@
       <c r="AA577" s="1"/>
       <c r="AB577" s="1"/>
     </row>
-    <row r="578" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -18230,7 +18231,7 @@
       <c r="AA578" s="1"/>
       <c r="AB578" s="1"/>
     </row>
-    <row r="579" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -18260,7 +18261,7 @@
       <c r="AA579" s="1"/>
       <c r="AB579" s="1"/>
     </row>
-    <row r="580" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -18290,7 +18291,7 @@
       <c r="AA580" s="1"/>
       <c r="AB580" s="1"/>
     </row>
-    <row r="581" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -18320,7 +18321,7 @@
       <c r="AA581" s="1"/>
       <c r="AB581" s="1"/>
     </row>
-    <row r="582" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -18350,7 +18351,7 @@
       <c r="AA582" s="1"/>
       <c r="AB582" s="1"/>
     </row>
-    <row r="583" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -18380,7 +18381,7 @@
       <c r="AA583" s="1"/>
       <c r="AB583" s="1"/>
     </row>
-    <row r="584" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -18410,7 +18411,7 @@
       <c r="AA584" s="1"/>
       <c r="AB584" s="1"/>
     </row>
-    <row r="585" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -18440,7 +18441,7 @@
       <c r="AA585" s="1"/>
       <c r="AB585" s="1"/>
     </row>
-    <row r="586" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -18470,7 +18471,7 @@
       <c r="AA586" s="1"/>
       <c r="AB586" s="1"/>
     </row>
-    <row r="587" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -18500,7 +18501,7 @@
       <c r="AA587" s="1"/>
       <c r="AB587" s="1"/>
     </row>
-    <row r="588" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -18530,7 +18531,7 @@
       <c r="AA588" s="1"/>
       <c r="AB588" s="1"/>
     </row>
-    <row r="589" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -18560,7 +18561,7 @@
       <c r="AA589" s="1"/>
       <c r="AB589" s="1"/>
     </row>
-    <row r="590" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -18590,7 +18591,7 @@
       <c r="AA590" s="1"/>
       <c r="AB590" s="1"/>
     </row>
-    <row r="591" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -18620,7 +18621,7 @@
       <c r="AA591" s="1"/>
       <c r="AB591" s="1"/>
     </row>
-    <row r="592" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -18650,7 +18651,7 @@
       <c r="AA592" s="1"/>
       <c r="AB592" s="1"/>
     </row>
-    <row r="593" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -18680,7 +18681,7 @@
       <c r="AA593" s="1"/>
       <c r="AB593" s="1"/>
     </row>
-    <row r="594" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -18710,7 +18711,7 @@
       <c r="AA594" s="1"/>
       <c r="AB594" s="1"/>
     </row>
-    <row r="595" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -18740,7 +18741,7 @@
       <c r="AA595" s="1"/>
       <c r="AB595" s="1"/>
     </row>
-    <row r="596" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -18770,7 +18771,7 @@
       <c r="AA596" s="1"/>
       <c r="AB596" s="1"/>
     </row>
-    <row r="597" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -18800,7 +18801,7 @@
       <c r="AA597" s="1"/>
       <c r="AB597" s="1"/>
     </row>
-    <row r="598" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -18830,7 +18831,7 @@
       <c r="AA598" s="1"/>
       <c r="AB598" s="1"/>
     </row>
-    <row r="599" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -18860,7 +18861,7 @@
       <c r="AA599" s="1"/>
       <c r="AB599" s="1"/>
     </row>
-    <row r="600" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -18890,7 +18891,7 @@
       <c r="AA600" s="1"/>
       <c r="AB600" s="1"/>
     </row>
-    <row r="601" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -18920,7 +18921,7 @@
       <c r="AA601" s="1"/>
       <c r="AB601" s="1"/>
     </row>
-    <row r="602" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -18950,7 +18951,7 @@
       <c r="AA602" s="1"/>
       <c r="AB602" s="1"/>
     </row>
-    <row r="603" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -18980,7 +18981,7 @@
       <c r="AA603" s="1"/>
       <c r="AB603" s="1"/>
     </row>
-    <row r="604" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19010,7 +19011,7 @@
       <c r="AA604" s="1"/>
       <c r="AB604" s="1"/>
     </row>
-    <row r="605" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19040,7 +19041,7 @@
       <c r="AA605" s="1"/>
       <c r="AB605" s="1"/>
     </row>
-    <row r="606" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19070,7 +19071,7 @@
       <c r="AA606" s="1"/>
       <c r="AB606" s="1"/>
     </row>
-    <row r="607" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19100,7 +19101,7 @@
       <c r="AA607" s="1"/>
       <c r="AB607" s="1"/>
     </row>
-    <row r="608" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19130,7 +19131,7 @@
       <c r="AA608" s="1"/>
       <c r="AB608" s="1"/>
     </row>
-    <row r="609" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -19160,7 +19161,7 @@
       <c r="AA609" s="1"/>
       <c r="AB609" s="1"/>
     </row>
-    <row r="610" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -19190,7 +19191,7 @@
       <c r="AA610" s="1"/>
       <c r="AB610" s="1"/>
     </row>
-    <row r="611" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -19220,7 +19221,7 @@
       <c r="AA611" s="1"/>
       <c r="AB611" s="1"/>
     </row>
-    <row r="612" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -19250,7 +19251,7 @@
       <c r="AA612" s="1"/>
       <c r="AB612" s="1"/>
     </row>
-    <row r="613" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -19280,7 +19281,7 @@
       <c r="AA613" s="1"/>
       <c r="AB613" s="1"/>
     </row>
-    <row r="614" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -19310,7 +19311,7 @@
       <c r="AA614" s="1"/>
       <c r="AB614" s="1"/>
     </row>
-    <row r="615" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -19340,7 +19341,7 @@
       <c r="AA615" s="1"/>
       <c r="AB615" s="1"/>
     </row>
-    <row r="616" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -19370,7 +19371,7 @@
       <c r="AA616" s="1"/>
       <c r="AB616" s="1"/>
     </row>
-    <row r="617" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -19400,7 +19401,7 @@
       <c r="AA617" s="1"/>
       <c r="AB617" s="1"/>
     </row>
-    <row r="618" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -19430,7 +19431,7 @@
       <c r="AA618" s="1"/>
       <c r="AB618" s="1"/>
     </row>
-    <row r="619" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -19460,7 +19461,7 @@
       <c r="AA619" s="1"/>
       <c r="AB619" s="1"/>
     </row>
-    <row r="620" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -19490,7 +19491,7 @@
       <c r="AA620" s="1"/>
       <c r="AB620" s="1"/>
     </row>
-    <row r="621" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -19520,7 +19521,7 @@
       <c r="AA621" s="1"/>
       <c r="AB621" s="1"/>
     </row>
-    <row r="622" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -19550,7 +19551,7 @@
       <c r="AA622" s="1"/>
       <c r="AB622" s="1"/>
     </row>
-    <row r="623" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -19580,7 +19581,7 @@
       <c r="AA623" s="1"/>
       <c r="AB623" s="1"/>
     </row>
-    <row r="624" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -19610,7 +19611,7 @@
       <c r="AA624" s="1"/>
       <c r="AB624" s="1"/>
     </row>
-    <row r="625" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -19640,7 +19641,7 @@
       <c r="AA625" s="1"/>
       <c r="AB625" s="1"/>
     </row>
-    <row r="626" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -19670,7 +19671,7 @@
       <c r="AA626" s="1"/>
       <c r="AB626" s="1"/>
     </row>
-    <row r="627" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -19700,7 +19701,7 @@
       <c r="AA627" s="1"/>
       <c r="AB627" s="1"/>
     </row>
-    <row r="628" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -19730,7 +19731,7 @@
       <c r="AA628" s="1"/>
       <c r="AB628" s="1"/>
     </row>
-    <row r="629" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -19760,7 +19761,7 @@
       <c r="AA629" s="1"/>
       <c r="AB629" s="1"/>
     </row>
-    <row r="630" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -19790,7 +19791,7 @@
       <c r="AA630" s="1"/>
       <c r="AB630" s="1"/>
     </row>
-    <row r="631" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -19820,7 +19821,7 @@
       <c r="AA631" s="1"/>
       <c r="AB631" s="1"/>
     </row>
-    <row r="632" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -19850,7 +19851,7 @@
       <c r="AA632" s="1"/>
       <c r="AB632" s="1"/>
     </row>
-    <row r="633" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -19880,7 +19881,7 @@
       <c r="AA633" s="1"/>
       <c r="AB633" s="1"/>
     </row>
-    <row r="634" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -19910,7 +19911,7 @@
       <c r="AA634" s="1"/>
       <c r="AB634" s="1"/>
     </row>
-    <row r="635" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -19940,7 +19941,7 @@
       <c r="AA635" s="1"/>
       <c r="AB635" s="1"/>
     </row>
-    <row r="636" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -19970,7 +19971,7 @@
       <c r="AA636" s="1"/>
       <c r="AB636" s="1"/>
     </row>
-    <row r="637" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20000,7 +20001,7 @@
       <c r="AA637" s="1"/>
       <c r="AB637" s="1"/>
     </row>
-    <row r="638" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20030,7 +20031,7 @@
       <c r="AA638" s="1"/>
       <c r="AB638" s="1"/>
     </row>
-    <row r="639" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20060,7 +20061,7 @@
       <c r="AA639" s="1"/>
       <c r="AB639" s="1"/>
     </row>
-    <row r="640" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20090,7 +20091,7 @@
       <c r="AA640" s="1"/>
       <c r="AB640" s="1"/>
     </row>
-    <row r="641" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -20120,7 +20121,7 @@
       <c r="AA641" s="1"/>
       <c r="AB641" s="1"/>
     </row>
-    <row r="642" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -20150,7 +20151,7 @@
       <c r="AA642" s="1"/>
       <c r="AB642" s="1"/>
     </row>
-    <row r="643" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -20180,7 +20181,7 @@
       <c r="AA643" s="1"/>
       <c r="AB643" s="1"/>
     </row>
-    <row r="644" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -20210,7 +20211,7 @@
       <c r="AA644" s="1"/>
       <c r="AB644" s="1"/>
     </row>
-    <row r="645" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -20240,7 +20241,7 @@
       <c r="AA645" s="1"/>
       <c r="AB645" s="1"/>
     </row>
-    <row r="646" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -20270,7 +20271,7 @@
       <c r="AA646" s="1"/>
       <c r="AB646" s="1"/>
     </row>
-    <row r="647" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -20300,7 +20301,7 @@
       <c r="AA647" s="1"/>
       <c r="AB647" s="1"/>
     </row>
-    <row r="648" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -20330,7 +20331,7 @@
       <c r="AA648" s="1"/>
       <c r="AB648" s="1"/>
     </row>
-    <row r="649" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -20360,7 +20361,7 @@
       <c r="AA649" s="1"/>
       <c r="AB649" s="1"/>
     </row>
-    <row r="650" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -20390,7 +20391,7 @@
       <c r="AA650" s="1"/>
       <c r="AB650" s="1"/>
     </row>
-    <row r="651" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -20420,7 +20421,7 @@
       <c r="AA651" s="1"/>
       <c r="AB651" s="1"/>
     </row>
-    <row r="652" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -20450,7 +20451,7 @@
       <c r="AA652" s="1"/>
       <c r="AB652" s="1"/>
     </row>
-    <row r="653" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -20480,7 +20481,7 @@
       <c r="AA653" s="1"/>
       <c r="AB653" s="1"/>
     </row>
-    <row r="654" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -20510,7 +20511,7 @@
       <c r="AA654" s="1"/>
       <c r="AB654" s="1"/>
     </row>
-    <row r="655" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -20540,7 +20541,7 @@
       <c r="AA655" s="1"/>
       <c r="AB655" s="1"/>
     </row>
-    <row r="656" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -20570,7 +20571,7 @@
       <c r="AA656" s="1"/>
       <c r="AB656" s="1"/>
     </row>
-    <row r="657" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -20600,7 +20601,7 @@
       <c r="AA657" s="1"/>
       <c r="AB657" s="1"/>
     </row>
-    <row r="658" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -20630,7 +20631,7 @@
       <c r="AA658" s="1"/>
       <c r="AB658" s="1"/>
     </row>
-    <row r="659" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -20660,7 +20661,7 @@
       <c r="AA659" s="1"/>
       <c r="AB659" s="1"/>
     </row>
-    <row r="660" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -20690,7 +20691,7 @@
       <c r="AA660" s="1"/>
       <c r="AB660" s="1"/>
     </row>
-    <row r="661" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -20720,7 +20721,7 @@
       <c r="AA661" s="1"/>
       <c r="AB661" s="1"/>
     </row>
-    <row r="662" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -20750,7 +20751,7 @@
       <c r="AA662" s="1"/>
       <c r="AB662" s="1"/>
     </row>
-    <row r="663" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -20780,7 +20781,7 @@
       <c r="AA663" s="1"/>
       <c r="AB663" s="1"/>
     </row>
-    <row r="664" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -20810,7 +20811,7 @@
       <c r="AA664" s="1"/>
       <c r="AB664" s="1"/>
     </row>
-    <row r="665" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -20840,7 +20841,7 @@
       <c r="AA665" s="1"/>
       <c r="AB665" s="1"/>
     </row>
-    <row r="666" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -20870,7 +20871,7 @@
       <c r="AA666" s="1"/>
       <c r="AB666" s="1"/>
     </row>
-    <row r="667" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -20900,7 +20901,7 @@
       <c r="AA667" s="1"/>
       <c r="AB667" s="1"/>
     </row>
-    <row r="668" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -20930,7 +20931,7 @@
       <c r="AA668" s="1"/>
       <c r="AB668" s="1"/>
     </row>
-    <row r="669" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -20960,7 +20961,7 @@
       <c r="AA669" s="1"/>
       <c r="AB669" s="1"/>
     </row>
-    <row r="670" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -20990,7 +20991,7 @@
       <c r="AA670" s="1"/>
       <c r="AB670" s="1"/>
     </row>
-    <row r="671" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21020,7 +21021,7 @@
       <c r="AA671" s="1"/>
       <c r="AB671" s="1"/>
     </row>
-    <row r="672" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -21050,7 +21051,7 @@
       <c r="AA672" s="1"/>
       <c r="AB672" s="1"/>
     </row>
-    <row r="673" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -21080,7 +21081,7 @@
       <c r="AA673" s="1"/>
       <c r="AB673" s="1"/>
     </row>
-    <row r="674" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -21110,7 +21111,7 @@
       <c r="AA674" s="1"/>
       <c r="AB674" s="1"/>
     </row>
-    <row r="675" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -21140,7 +21141,7 @@
       <c r="AA675" s="1"/>
       <c r="AB675" s="1"/>
     </row>
-    <row r="676" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -21170,7 +21171,7 @@
       <c r="AA676" s="1"/>
       <c r="AB676" s="1"/>
     </row>
-    <row r="677" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -21200,7 +21201,7 @@
       <c r="AA677" s="1"/>
       <c r="AB677" s="1"/>
     </row>
-    <row r="678" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -21230,7 +21231,7 @@
       <c r="AA678" s="1"/>
       <c r="AB678" s="1"/>
     </row>
-    <row r="679" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -21260,7 +21261,7 @@
       <c r="AA679" s="1"/>
       <c r="AB679" s="1"/>
     </row>
-    <row r="680" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -21290,7 +21291,7 @@
       <c r="AA680" s="1"/>
       <c r="AB680" s="1"/>
     </row>
-    <row r="681" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -21320,7 +21321,7 @@
       <c r="AA681" s="1"/>
       <c r="AB681" s="1"/>
     </row>
-    <row r="682" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -21350,7 +21351,7 @@
       <c r="AA682" s="1"/>
       <c r="AB682" s="1"/>
     </row>
-    <row r="683" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -21380,7 +21381,7 @@
       <c r="AA683" s="1"/>
       <c r="AB683" s="1"/>
     </row>
-    <row r="684" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -21410,7 +21411,7 @@
       <c r="AA684" s="1"/>
       <c r="AB684" s="1"/>
     </row>
-    <row r="685" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -21440,7 +21441,7 @@
       <c r="AA685" s="1"/>
       <c r="AB685" s="1"/>
     </row>
-    <row r="686" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -21470,7 +21471,7 @@
       <c r="AA686" s="1"/>
       <c r="AB686" s="1"/>
     </row>
-    <row r="687" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -21500,7 +21501,7 @@
       <c r="AA687" s="1"/>
       <c r="AB687" s="1"/>
     </row>
-    <row r="688" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -21530,7 +21531,7 @@
       <c r="AA688" s="1"/>
       <c r="AB688" s="1"/>
     </row>
-    <row r="689" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -21560,7 +21561,7 @@
       <c r="AA689" s="1"/>
       <c r="AB689" s="1"/>
     </row>
-    <row r="690" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -21590,7 +21591,7 @@
       <c r="AA690" s="1"/>
       <c r="AB690" s="1"/>
     </row>
-    <row r="691" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -21620,7 +21621,7 @@
       <c r="AA691" s="1"/>
       <c r="AB691" s="1"/>
     </row>
-    <row r="692" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -21650,7 +21651,7 @@
       <c r="AA692" s="1"/>
       <c r="AB692" s="1"/>
     </row>
-    <row r="693" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -21680,7 +21681,7 @@
       <c r="AA693" s="1"/>
       <c r="AB693" s="1"/>
     </row>
-    <row r="694" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -21710,7 +21711,7 @@
       <c r="AA694" s="1"/>
       <c r="AB694" s="1"/>
     </row>
-    <row r="695" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -21740,7 +21741,7 @@
       <c r="AA695" s="1"/>
       <c r="AB695" s="1"/>
     </row>
-    <row r="696" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -21770,7 +21771,7 @@
       <c r="AA696" s="1"/>
       <c r="AB696" s="1"/>
     </row>
-    <row r="697" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -21800,7 +21801,7 @@
       <c r="AA697" s="1"/>
       <c r="AB697" s="1"/>
     </row>
-    <row r="698" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -21830,7 +21831,7 @@
       <c r="AA698" s="1"/>
       <c r="AB698" s="1"/>
     </row>
-    <row r="699" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -21860,7 +21861,7 @@
       <c r="AA699" s="1"/>
       <c r="AB699" s="1"/>
     </row>
-    <row r="700" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -21890,7 +21891,7 @@
       <c r="AA700" s="1"/>
       <c r="AB700" s="1"/>
     </row>
-    <row r="701" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -21920,7 +21921,7 @@
       <c r="AA701" s="1"/>
       <c r="AB701" s="1"/>
     </row>
-    <row r="702" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -21950,7 +21951,7 @@
       <c r="AA702" s="1"/>
       <c r="AB702" s="1"/>
     </row>
-    <row r="703" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -21980,7 +21981,7 @@
       <c r="AA703" s="1"/>
       <c r="AB703" s="1"/>
     </row>
-    <row r="704" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -22010,7 +22011,7 @@
       <c r="AA704" s="1"/>
       <c r="AB704" s="1"/>
     </row>
-    <row r="705" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -22040,7 +22041,7 @@
       <c r="AA705" s="1"/>
       <c r="AB705" s="1"/>
     </row>
-    <row r="706" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -22070,7 +22071,7 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
-    <row r="707" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -22100,7 +22101,7 @@
       <c r="AA707" s="1"/>
       <c r="AB707" s="1"/>
     </row>
-    <row r="708" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -22130,7 +22131,7 @@
       <c r="AA708" s="1"/>
       <c r="AB708" s="1"/>
     </row>
-    <row r="709" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -22160,7 +22161,7 @@
       <c r="AA709" s="1"/>
       <c r="AB709" s="1"/>
     </row>
-    <row r="710" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -22190,7 +22191,7 @@
       <c r="AA710" s="1"/>
       <c r="AB710" s="1"/>
     </row>
-    <row r="711" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -22220,7 +22221,7 @@
       <c r="AA711" s="1"/>
       <c r="AB711" s="1"/>
     </row>
-    <row r="712" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -22250,7 +22251,7 @@
       <c r="AA712" s="1"/>
       <c r="AB712" s="1"/>
     </row>
-    <row r="713" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -22280,7 +22281,7 @@
       <c r="AA713" s="1"/>
       <c r="AB713" s="1"/>
     </row>
-    <row r="714" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -22310,7 +22311,7 @@
       <c r="AA714" s="1"/>
       <c r="AB714" s="1"/>
     </row>
-    <row r="715" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -22340,7 +22341,7 @@
       <c r="AA715" s="1"/>
       <c r="AB715" s="1"/>
     </row>
-    <row r="716" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -22370,7 +22371,7 @@
       <c r="AA716" s="1"/>
       <c r="AB716" s="1"/>
     </row>
-    <row r="717" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -22400,7 +22401,7 @@
       <c r="AA717" s="1"/>
       <c r="AB717" s="1"/>
     </row>
-    <row r="718" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -22430,7 +22431,7 @@
       <c r="AA718" s="1"/>
       <c r="AB718" s="1"/>
     </row>
-    <row r="719" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -22460,7 +22461,7 @@
       <c r="AA719" s="1"/>
       <c r="AB719" s="1"/>
     </row>
-    <row r="720" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -22490,7 +22491,7 @@
       <c r="AA720" s="1"/>
       <c r="AB720" s="1"/>
     </row>
-    <row r="721" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -22520,7 +22521,7 @@
       <c r="AA721" s="1"/>
       <c r="AB721" s="1"/>
     </row>
-    <row r="722" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -22550,7 +22551,7 @@
       <c r="AA722" s="1"/>
       <c r="AB722" s="1"/>
     </row>
-    <row r="723" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -22580,7 +22581,7 @@
       <c r="AA723" s="1"/>
       <c r="AB723" s="1"/>
     </row>
-    <row r="724" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -22610,7 +22611,7 @@
       <c r="AA724" s="1"/>
       <c r="AB724" s="1"/>
     </row>
-    <row r="725" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -22640,7 +22641,7 @@
       <c r="AA725" s="1"/>
       <c r="AB725" s="1"/>
     </row>
-    <row r="726" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -22670,7 +22671,7 @@
       <c r="AA726" s="1"/>
       <c r="AB726" s="1"/>
     </row>
-    <row r="727" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -22700,7 +22701,7 @@
       <c r="AA727" s="1"/>
       <c r="AB727" s="1"/>
     </row>
-    <row r="728" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -22730,7 +22731,7 @@
       <c r="AA728" s="1"/>
       <c r="AB728" s="1"/>
     </row>
-    <row r="729" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -22760,7 +22761,7 @@
       <c r="AA729" s="1"/>
       <c r="AB729" s="1"/>
     </row>
-    <row r="730" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -22790,7 +22791,7 @@
       <c r="AA730" s="1"/>
       <c r="AB730" s="1"/>
     </row>
-    <row r="731" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -22820,7 +22821,7 @@
       <c r="AA731" s="1"/>
       <c r="AB731" s="1"/>
     </row>
-    <row r="732" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -22850,7 +22851,7 @@
       <c r="AA732" s="1"/>
       <c r="AB732" s="1"/>
     </row>
-    <row r="733" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -22880,7 +22881,7 @@
       <c r="AA733" s="1"/>
       <c r="AB733" s="1"/>
     </row>
-    <row r="734" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -22910,7 +22911,7 @@
       <c r="AA734" s="1"/>
       <c r="AB734" s="1"/>
     </row>
-    <row r="735" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -22940,7 +22941,7 @@
       <c r="AA735" s="1"/>
       <c r="AB735" s="1"/>
     </row>
-    <row r="736" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -22970,7 +22971,7 @@
       <c r="AA736" s="1"/>
       <c r="AB736" s="1"/>
     </row>
-    <row r="737" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -23000,7 +23001,7 @@
       <c r="AA737" s="1"/>
       <c r="AB737" s="1"/>
     </row>
-    <row r="738" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -23030,7 +23031,7 @@
       <c r="AA738" s="1"/>
       <c r="AB738" s="1"/>
     </row>
-    <row r="739" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -23060,7 +23061,7 @@
       <c r="AA739" s="1"/>
       <c r="AB739" s="1"/>
     </row>
-    <row r="740" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -23090,7 +23091,7 @@
       <c r="AA740" s="1"/>
       <c r="AB740" s="1"/>
     </row>
-    <row r="741" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -23120,7 +23121,7 @@
       <c r="AA741" s="1"/>
       <c r="AB741" s="1"/>
     </row>
-    <row r="742" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -23150,7 +23151,7 @@
       <c r="AA742" s="1"/>
       <c r="AB742" s="1"/>
     </row>
-    <row r="743" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -23180,7 +23181,7 @@
       <c r="AA743" s="1"/>
       <c r="AB743" s="1"/>
     </row>
-    <row r="744" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -23210,7 +23211,7 @@
       <c r="AA744" s="1"/>
       <c r="AB744" s="1"/>
     </row>
-    <row r="745" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -23240,7 +23241,7 @@
       <c r="AA745" s="1"/>
       <c r="AB745" s="1"/>
     </row>
-    <row r="746" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -23270,7 +23271,7 @@
       <c r="AA746" s="1"/>
       <c r="AB746" s="1"/>
     </row>
-    <row r="747" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -23300,7 +23301,7 @@
       <c r="AA747" s="1"/>
       <c r="AB747" s="1"/>
     </row>
-    <row r="748" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -23330,7 +23331,7 @@
       <c r="AA748" s="1"/>
       <c r="AB748" s="1"/>
     </row>
-    <row r="749" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -23360,7 +23361,7 @@
       <c r="AA749" s="1"/>
       <c r="AB749" s="1"/>
     </row>
-    <row r="750" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -23390,7 +23391,7 @@
       <c r="AA750" s="1"/>
       <c r="AB750" s="1"/>
     </row>
-    <row r="751" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -23420,7 +23421,7 @@
       <c r="AA751" s="1"/>
       <c r="AB751" s="1"/>
     </row>
-    <row r="752" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -23450,7 +23451,7 @@
       <c r="AA752" s="1"/>
       <c r="AB752" s="1"/>
     </row>
-    <row r="753" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -23480,7 +23481,7 @@
       <c r="AA753" s="1"/>
       <c r="AB753" s="1"/>
     </row>
-    <row r="754" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -23510,7 +23511,7 @@
       <c r="AA754" s="1"/>
       <c r="AB754" s="1"/>
     </row>
-    <row r="755" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -23540,7 +23541,7 @@
       <c r="AA755" s="1"/>
       <c r="AB755" s="1"/>
     </row>
-    <row r="756" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -23570,7 +23571,7 @@
       <c r="AA756" s="1"/>
       <c r="AB756" s="1"/>
     </row>
-    <row r="757" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -23600,7 +23601,7 @@
       <c r="AA757" s="1"/>
       <c r="AB757" s="1"/>
     </row>
-    <row r="758" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -23630,7 +23631,7 @@
       <c r="AA758" s="1"/>
       <c r="AB758" s="1"/>
     </row>
-    <row r="759" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -23660,7 +23661,7 @@
       <c r="AA759" s="1"/>
       <c r="AB759" s="1"/>
     </row>
-    <row r="760" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -23690,7 +23691,7 @@
       <c r="AA760" s="1"/>
       <c r="AB760" s="1"/>
     </row>
-    <row r="761" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -23720,7 +23721,7 @@
       <c r="AA761" s="1"/>
       <c r="AB761" s="1"/>
     </row>
-    <row r="762" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -23750,7 +23751,7 @@
       <c r="AA762" s="1"/>
       <c r="AB762" s="1"/>
     </row>
-    <row r="763" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -23780,7 +23781,7 @@
       <c r="AA763" s="1"/>
       <c r="AB763" s="1"/>
     </row>
-    <row r="764" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -23810,7 +23811,7 @@
       <c r="AA764" s="1"/>
       <c r="AB764" s="1"/>
     </row>
-    <row r="765" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -23840,7 +23841,7 @@
       <c r="AA765" s="1"/>
       <c r="AB765" s="1"/>
     </row>
-    <row r="766" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -23870,7 +23871,7 @@
       <c r="AA766" s="1"/>
       <c r="AB766" s="1"/>
     </row>
-    <row r="767" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -23900,7 +23901,7 @@
       <c r="AA767" s="1"/>
       <c r="AB767" s="1"/>
     </row>
-    <row r="768" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -23930,7 +23931,7 @@
       <c r="AA768" s="1"/>
       <c r="AB768" s="1"/>
     </row>
-    <row r="769" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -23960,7 +23961,7 @@
       <c r="AA769" s="1"/>
       <c r="AB769" s="1"/>
     </row>
-    <row r="770" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -23990,7 +23991,7 @@
       <c r="AA770" s="1"/>
       <c r="AB770" s="1"/>
     </row>
-    <row r="771" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -24020,7 +24021,7 @@
       <c r="AA771" s="1"/>
       <c r="AB771" s="1"/>
     </row>
-    <row r="772" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -24050,7 +24051,7 @@
       <c r="AA772" s="1"/>
       <c r="AB772" s="1"/>
     </row>
-    <row r="773" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -24080,7 +24081,7 @@
       <c r="AA773" s="1"/>
       <c r="AB773" s="1"/>
     </row>
-    <row r="774" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -24110,7 +24111,7 @@
       <c r="AA774" s="1"/>
       <c r="AB774" s="1"/>
     </row>
-    <row r="775" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -24140,7 +24141,7 @@
       <c r="AA775" s="1"/>
       <c r="AB775" s="1"/>
     </row>
-    <row r="776" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -24170,7 +24171,7 @@
       <c r="AA776" s="1"/>
       <c r="AB776" s="1"/>
     </row>
-    <row r="777" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -24200,7 +24201,7 @@
       <c r="AA777" s="1"/>
       <c r="AB777" s="1"/>
     </row>
-    <row r="778" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -24230,7 +24231,7 @@
       <c r="AA778" s="1"/>
       <c r="AB778" s="1"/>
     </row>
-    <row r="779" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -24260,7 +24261,7 @@
       <c r="AA779" s="1"/>
       <c r="AB779" s="1"/>
     </row>
-    <row r="780" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -24290,7 +24291,7 @@
       <c r="AA780" s="1"/>
       <c r="AB780" s="1"/>
     </row>
-    <row r="781" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -24320,7 +24321,7 @@
       <c r="AA781" s="1"/>
       <c r="AB781" s="1"/>
     </row>
-    <row r="782" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -24350,7 +24351,7 @@
       <c r="AA782" s="1"/>
       <c r="AB782" s="1"/>
     </row>
-    <row r="783" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -24380,7 +24381,7 @@
       <c r="AA783" s="1"/>
       <c r="AB783" s="1"/>
     </row>
-    <row r="784" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -24410,7 +24411,7 @@
       <c r="AA784" s="1"/>
       <c r="AB784" s="1"/>
     </row>
-    <row r="785" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -24440,7 +24441,7 @@
       <c r="AA785" s="1"/>
       <c r="AB785" s="1"/>
     </row>
-    <row r="786" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -24470,7 +24471,7 @@
       <c r="AA786" s="1"/>
       <c r="AB786" s="1"/>
     </row>
-    <row r="787" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -24500,7 +24501,7 @@
       <c r="AA787" s="1"/>
       <c r="AB787" s="1"/>
     </row>
-    <row r="788" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -24530,7 +24531,7 @@
       <c r="AA788" s="1"/>
       <c r="AB788" s="1"/>
     </row>
-    <row r="789" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -24560,7 +24561,7 @@
       <c r="AA789" s="1"/>
       <c r="AB789" s="1"/>
     </row>
-    <row r="790" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -24590,7 +24591,7 @@
       <c r="AA790" s="1"/>
       <c r="AB790" s="1"/>
     </row>
-    <row r="791" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -24620,7 +24621,7 @@
       <c r="AA791" s="1"/>
       <c r="AB791" s="1"/>
     </row>
-    <row r="792" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -24650,7 +24651,7 @@
       <c r="AA792" s="1"/>
       <c r="AB792" s="1"/>
     </row>
-    <row r="793" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -24680,7 +24681,7 @@
       <c r="AA793" s="1"/>
       <c r="AB793" s="1"/>
     </row>
-    <row r="794" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -24710,7 +24711,7 @@
       <c r="AA794" s="1"/>
       <c r="AB794" s="1"/>
     </row>
-    <row r="795" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -24740,7 +24741,7 @@
       <c r="AA795" s="1"/>
       <c r="AB795" s="1"/>
     </row>
-    <row r="796" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -24770,7 +24771,7 @@
       <c r="AA796" s="1"/>
       <c r="AB796" s="1"/>
     </row>
-    <row r="797" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -24800,7 +24801,7 @@
       <c r="AA797" s="1"/>
       <c r="AB797" s="1"/>
     </row>
-    <row r="798" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -24830,7 +24831,7 @@
       <c r="AA798" s="1"/>
       <c r="AB798" s="1"/>
     </row>
-    <row r="799" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -24860,7 +24861,7 @@
       <c r="AA799" s="1"/>
       <c r="AB799" s="1"/>
     </row>
-    <row r="800" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -24890,7 +24891,7 @@
       <c r="AA800" s="1"/>
       <c r="AB800" s="1"/>
     </row>
-    <row r="801" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -24920,7 +24921,7 @@
       <c r="AA801" s="1"/>
       <c r="AB801" s="1"/>
     </row>
-    <row r="802" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -24950,7 +24951,7 @@
       <c r="AA802" s="1"/>
       <c r="AB802" s="1"/>
     </row>
-    <row r="803" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -24980,7 +24981,7 @@
       <c r="AA803" s="1"/>
       <c r="AB803" s="1"/>
     </row>
-    <row r="804" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -25010,7 +25011,7 @@
       <c r="AA804" s="1"/>
       <c r="AB804" s="1"/>
     </row>
-    <row r="805" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -25040,7 +25041,7 @@
       <c r="AA805" s="1"/>
       <c r="AB805" s="1"/>
     </row>
-    <row r="806" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -25070,7 +25071,7 @@
       <c r="AA806" s="1"/>
       <c r="AB806" s="1"/>
     </row>
-    <row r="807" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -25100,7 +25101,7 @@
       <c r="AA807" s="1"/>
       <c r="AB807" s="1"/>
     </row>
-    <row r="808" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -25130,7 +25131,7 @@
       <c r="AA808" s="1"/>
       <c r="AB808" s="1"/>
     </row>
-    <row r="809" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -25160,7 +25161,7 @@
       <c r="AA809" s="1"/>
       <c r="AB809" s="1"/>
     </row>
-    <row r="810" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -25190,7 +25191,7 @@
       <c r="AA810" s="1"/>
       <c r="AB810" s="1"/>
     </row>
-    <row r="811" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -25220,7 +25221,7 @@
       <c r="AA811" s="1"/>
       <c r="AB811" s="1"/>
     </row>
-    <row r="812" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -25250,7 +25251,7 @@
       <c r="AA812" s="1"/>
       <c r="AB812" s="1"/>
     </row>
-    <row r="813" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -25280,7 +25281,7 @@
       <c r="AA813" s="1"/>
       <c r="AB813" s="1"/>
     </row>
-    <row r="814" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -25310,7 +25311,7 @@
       <c r="AA814" s="1"/>
       <c r="AB814" s="1"/>
     </row>
-    <row r="815" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -25340,7 +25341,7 @@
       <c r="AA815" s="1"/>
       <c r="AB815" s="1"/>
     </row>
-    <row r="816" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -25370,7 +25371,7 @@
       <c r="AA816" s="1"/>
       <c r="AB816" s="1"/>
     </row>
-    <row r="817" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -25400,7 +25401,7 @@
       <c r="AA817" s="1"/>
       <c r="AB817" s="1"/>
     </row>
-    <row r="818" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -25430,7 +25431,7 @@
       <c r="AA818" s="1"/>
       <c r="AB818" s="1"/>
     </row>
-    <row r="819" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -25460,7 +25461,7 @@
       <c r="AA819" s="1"/>
       <c r="AB819" s="1"/>
     </row>
-    <row r="820" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -25490,7 +25491,7 @@
       <c r="AA820" s="1"/>
       <c r="AB820" s="1"/>
     </row>
-    <row r="821" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -25520,7 +25521,7 @@
       <c r="AA821" s="1"/>
       <c r="AB821" s="1"/>
     </row>
-    <row r="822" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -25550,7 +25551,7 @@
       <c r="AA822" s="1"/>
       <c r="AB822" s="1"/>
     </row>
-    <row r="823" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -25580,7 +25581,7 @@
       <c r="AA823" s="1"/>
       <c r="AB823" s="1"/>
     </row>
-    <row r="824" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -25610,7 +25611,7 @@
       <c r="AA824" s="1"/>
       <c r="AB824" s="1"/>
     </row>
-    <row r="825" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -25640,7 +25641,7 @@
       <c r="AA825" s="1"/>
       <c r="AB825" s="1"/>
     </row>
-    <row r="826" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -25670,7 +25671,7 @@
       <c r="AA826" s="1"/>
       <c r="AB826" s="1"/>
     </row>
-    <row r="827" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -25700,7 +25701,7 @@
       <c r="AA827" s="1"/>
       <c r="AB827" s="1"/>
     </row>
-    <row r="828" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -25730,7 +25731,7 @@
       <c r="AA828" s="1"/>
       <c r="AB828" s="1"/>
     </row>
-    <row r="829" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -25760,7 +25761,7 @@
       <c r="AA829" s="1"/>
       <c r="AB829" s="1"/>
     </row>
-    <row r="830" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -25790,7 +25791,7 @@
       <c r="AA830" s="1"/>
       <c r="AB830" s="1"/>
     </row>
-    <row r="831" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -25820,7 +25821,7 @@
       <c r="AA831" s="1"/>
       <c r="AB831" s="1"/>
     </row>
-    <row r="832" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -25850,7 +25851,7 @@
       <c r="AA832" s="1"/>
       <c r="AB832" s="1"/>
     </row>
-    <row r="833" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -25880,7 +25881,7 @@
       <c r="AA833" s="1"/>
       <c r="AB833" s="1"/>
     </row>
-    <row r="834" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -25910,7 +25911,7 @@
       <c r="AA834" s="1"/>
       <c r="AB834" s="1"/>
     </row>
-    <row r="835" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -25940,7 +25941,7 @@
       <c r="AA835" s="1"/>
       <c r="AB835" s="1"/>
     </row>
-    <row r="836" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -25970,7 +25971,7 @@
       <c r="AA836" s="1"/>
       <c r="AB836" s="1"/>
     </row>
-    <row r="837" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -26000,7 +26001,7 @@
       <c r="AA837" s="1"/>
       <c r="AB837" s="1"/>
     </row>
-    <row r="838" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -26030,7 +26031,7 @@
       <c r="AA838" s="1"/>
       <c r="AB838" s="1"/>
     </row>
-    <row r="839" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -26060,7 +26061,7 @@
       <c r="AA839" s="1"/>
       <c r="AB839" s="1"/>
     </row>
-    <row r="840" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -26090,7 +26091,7 @@
       <c r="AA840" s="1"/>
       <c r="AB840" s="1"/>
     </row>
-    <row r="841" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -26120,7 +26121,7 @@
       <c r="AA841" s="1"/>
       <c r="AB841" s="1"/>
     </row>
-    <row r="842" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -26150,7 +26151,7 @@
       <c r="AA842" s="1"/>
       <c r="AB842" s="1"/>
     </row>
-    <row r="843" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -26180,7 +26181,7 @@
       <c r="AA843" s="1"/>
       <c r="AB843" s="1"/>
     </row>
-    <row r="844" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -26210,7 +26211,7 @@
       <c r="AA844" s="1"/>
       <c r="AB844" s="1"/>
     </row>
-    <row r="845" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -26240,7 +26241,7 @@
       <c r="AA845" s="1"/>
       <c r="AB845" s="1"/>
     </row>
-    <row r="846" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -26270,7 +26271,7 @@
       <c r="AA846" s="1"/>
       <c r="AB846" s="1"/>
     </row>
-    <row r="847" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -26300,7 +26301,7 @@
       <c r="AA847" s="1"/>
       <c r="AB847" s="1"/>
     </row>
-    <row r="848" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -26330,7 +26331,7 @@
       <c r="AA848" s="1"/>
       <c r="AB848" s="1"/>
     </row>
-    <row r="849" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -26360,7 +26361,7 @@
       <c r="AA849" s="1"/>
       <c r="AB849" s="1"/>
     </row>
-    <row r="850" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -26390,7 +26391,7 @@
       <c r="AA850" s="1"/>
       <c r="AB850" s="1"/>
     </row>
-    <row r="851" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -26420,7 +26421,7 @@
       <c r="AA851" s="1"/>
       <c r="AB851" s="1"/>
     </row>
-    <row r="852" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -26450,7 +26451,7 @@
       <c r="AA852" s="1"/>
       <c r="AB852" s="1"/>
     </row>
-    <row r="853" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -26480,7 +26481,7 @@
       <c r="AA853" s="1"/>
       <c r="AB853" s="1"/>
     </row>
-    <row r="854" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -26510,7 +26511,7 @@
       <c r="AA854" s="1"/>
       <c r="AB854" s="1"/>
     </row>
-    <row r="855" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -26540,7 +26541,7 @@
       <c r="AA855" s="1"/>
       <c r="AB855" s="1"/>
     </row>
-    <row r="856" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -26570,7 +26571,7 @@
       <c r="AA856" s="1"/>
       <c r="AB856" s="1"/>
     </row>
-    <row r="857" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -26600,7 +26601,7 @@
       <c r="AA857" s="1"/>
       <c r="AB857" s="1"/>
     </row>
-    <row r="858" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -26630,7 +26631,7 @@
       <c r="AA858" s="1"/>
       <c r="AB858" s="1"/>
     </row>
-    <row r="859" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -26660,7 +26661,7 @@
       <c r="AA859" s="1"/>
       <c r="AB859" s="1"/>
     </row>
-    <row r="860" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -26690,7 +26691,7 @@
       <c r="AA860" s="1"/>
       <c r="AB860" s="1"/>
     </row>
-    <row r="861" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -26720,7 +26721,7 @@
       <c r="AA861" s="1"/>
       <c r="AB861" s="1"/>
     </row>
-    <row r="862" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -26750,7 +26751,7 @@
       <c r="AA862" s="1"/>
       <c r="AB862" s="1"/>
     </row>
-    <row r="863" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -26780,7 +26781,7 @@
       <c r="AA863" s="1"/>
       <c r="AB863" s="1"/>
     </row>
-    <row r="864" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -26810,7 +26811,7 @@
       <c r="AA864" s="1"/>
       <c r="AB864" s="1"/>
     </row>
-    <row r="865" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -26840,7 +26841,7 @@
       <c r="AA865" s="1"/>
       <c r="AB865" s="1"/>
     </row>
-    <row r="866" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -26870,7 +26871,7 @@
       <c r="AA866" s="1"/>
       <c r="AB866" s="1"/>
     </row>
-    <row r="867" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -26900,7 +26901,7 @@
       <c r="AA867" s="1"/>
       <c r="AB867" s="1"/>
     </row>
-    <row r="868" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -26930,7 +26931,7 @@
       <c r="AA868" s="1"/>
       <c r="AB868" s="1"/>
     </row>
-    <row r="869" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -26960,7 +26961,7 @@
       <c r="AA869" s="1"/>
       <c r="AB869" s="1"/>
     </row>
-    <row r="870" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -26990,7 +26991,7 @@
       <c r="AA870" s="1"/>
       <c r="AB870" s="1"/>
     </row>
-    <row r="871" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -27020,7 +27021,7 @@
       <c r="AA871" s="1"/>
       <c r="AB871" s="1"/>
     </row>
-    <row r="872" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -27050,7 +27051,7 @@
       <c r="AA872" s="1"/>
       <c r="AB872" s="1"/>
     </row>
-    <row r="873" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -27080,7 +27081,7 @@
       <c r="AA873" s="1"/>
       <c r="AB873" s="1"/>
     </row>
-    <row r="874" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -27110,7 +27111,7 @@
       <c r="AA874" s="1"/>
       <c r="AB874" s="1"/>
     </row>
-    <row r="875" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -27140,7 +27141,7 @@
       <c r="AA875" s="1"/>
       <c r="AB875" s="1"/>
     </row>
-    <row r="876" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -27170,7 +27171,7 @@
       <c r="AA876" s="1"/>
       <c r="AB876" s="1"/>
     </row>
-    <row r="877" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -27200,7 +27201,7 @@
       <c r="AA877" s="1"/>
       <c r="AB877" s="1"/>
     </row>
-    <row r="878" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -27230,7 +27231,7 @@
       <c r="AA878" s="1"/>
       <c r="AB878" s="1"/>
     </row>
-    <row r="879" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -27260,7 +27261,7 @@
       <c r="AA879" s="1"/>
       <c r="AB879" s="1"/>
     </row>
-    <row r="880" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -27290,7 +27291,7 @@
       <c r="AA880" s="1"/>
       <c r="AB880" s="1"/>
     </row>
-    <row r="881" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -27320,7 +27321,7 @@
       <c r="AA881" s="1"/>
       <c r="AB881" s="1"/>
     </row>
-    <row r="882" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -27350,7 +27351,7 @@
       <c r="AA882" s="1"/>
       <c r="AB882" s="1"/>
     </row>
-    <row r="883" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -27380,7 +27381,7 @@
       <c r="AA883" s="1"/>
       <c r="AB883" s="1"/>
     </row>
-    <row r="884" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -27410,7 +27411,7 @@
       <c r="AA884" s="1"/>
       <c r="AB884" s="1"/>
     </row>
-    <row r="885" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -27440,7 +27441,7 @@
       <c r="AA885" s="1"/>
       <c r="AB885" s="1"/>
     </row>
-    <row r="886" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -27470,7 +27471,7 @@
       <c r="AA886" s="1"/>
       <c r="AB886" s="1"/>
     </row>
-    <row r="887" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -27500,7 +27501,7 @@
       <c r="AA887" s="1"/>
       <c r="AB887" s="1"/>
     </row>
-    <row r="888" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -27530,7 +27531,7 @@
       <c r="AA888" s="1"/>
       <c r="AB888" s="1"/>
     </row>
-    <row r="889" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -27560,7 +27561,7 @@
       <c r="AA889" s="1"/>
       <c r="AB889" s="1"/>
     </row>
-    <row r="890" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -27590,7 +27591,7 @@
       <c r="AA890" s="1"/>
       <c r="AB890" s="1"/>
     </row>
-    <row r="891" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -27620,7 +27621,7 @@
       <c r="AA891" s="1"/>
       <c r="AB891" s="1"/>
     </row>
-    <row r="892" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -27650,7 +27651,7 @@
       <c r="AA892" s="1"/>
       <c r="AB892" s="1"/>
     </row>
-    <row r="893" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -27680,7 +27681,7 @@
       <c r="AA893" s="1"/>
       <c r="AB893" s="1"/>
     </row>
-    <row r="894" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -27710,7 +27711,7 @@
       <c r="AA894" s="1"/>
       <c r="AB894" s="1"/>
     </row>
-    <row r="895" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -27740,7 +27741,7 @@
       <c r="AA895" s="1"/>
       <c r="AB895" s="1"/>
     </row>
-    <row r="896" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -27770,7 +27771,7 @@
       <c r="AA896" s="1"/>
       <c r="AB896" s="1"/>
     </row>
-    <row r="897" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -27800,7 +27801,7 @@
       <c r="AA897" s="1"/>
       <c r="AB897" s="1"/>
     </row>
-    <row r="898" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -27830,7 +27831,7 @@
       <c r="AA898" s="1"/>
       <c r="AB898" s="1"/>
     </row>
-    <row r="899" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -27860,7 +27861,7 @@
       <c r="AA899" s="1"/>
       <c r="AB899" s="1"/>
     </row>
-    <row r="900" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -27890,7 +27891,7 @@
       <c r="AA900" s="1"/>
       <c r="AB900" s="1"/>
     </row>
-    <row r="901" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -27920,7 +27921,7 @@
       <c r="AA901" s="1"/>
       <c r="AB901" s="1"/>
     </row>
-    <row r="902" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -27950,7 +27951,7 @@
       <c r="AA902" s="1"/>
       <c r="AB902" s="1"/>
     </row>
-    <row r="903" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -27980,7 +27981,7 @@
       <c r="AA903" s="1"/>
       <c r="AB903" s="1"/>
     </row>
-    <row r="904" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -28010,7 +28011,7 @@
       <c r="AA904" s="1"/>
       <c r="AB904" s="1"/>
     </row>
-    <row r="905" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -28040,7 +28041,7 @@
       <c r="AA905" s="1"/>
       <c r="AB905" s="1"/>
     </row>
-    <row r="906" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -28070,7 +28071,7 @@
       <c r="AA906" s="1"/>
       <c r="AB906" s="1"/>
     </row>
-    <row r="907" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -28100,7 +28101,7 @@
       <c r="AA907" s="1"/>
       <c r="AB907" s="1"/>
     </row>
-    <row r="908" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -28130,7 +28131,7 @@
       <c r="AA908" s="1"/>
       <c r="AB908" s="1"/>
     </row>
-    <row r="909" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -28160,7 +28161,7 @@
       <c r="AA909" s="1"/>
       <c r="AB909" s="1"/>
     </row>
-    <row r="910" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -28190,7 +28191,7 @@
       <c r="AA910" s="1"/>
       <c r="AB910" s="1"/>
     </row>
-    <row r="911" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -28220,7 +28221,7 @@
       <c r="AA911" s="1"/>
       <c r="AB911" s="1"/>
     </row>
-    <row r="912" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -28250,7 +28251,7 @@
       <c r="AA912" s="1"/>
       <c r="AB912" s="1"/>
     </row>
-    <row r="913" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -28280,7 +28281,7 @@
       <c r="AA913" s="1"/>
       <c r="AB913" s="1"/>
     </row>
-    <row r="914" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -28310,7 +28311,7 @@
       <c r="AA914" s="1"/>
       <c r="AB914" s="1"/>
     </row>
-    <row r="915" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -28340,7 +28341,7 @@
       <c r="AA915" s="1"/>
       <c r="AB915" s="1"/>
     </row>
-    <row r="916" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -28370,7 +28371,7 @@
       <c r="AA916" s="1"/>
       <c r="AB916" s="1"/>
     </row>
-    <row r="917" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -28400,7 +28401,7 @@
       <c r="AA917" s="1"/>
       <c r="AB917" s="1"/>
     </row>
-    <row r="918" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -28430,7 +28431,7 @@
       <c r="AA918" s="1"/>
       <c r="AB918" s="1"/>
     </row>
-    <row r="919" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -28460,7 +28461,7 @@
       <c r="AA919" s="1"/>
       <c r="AB919" s="1"/>
     </row>
-    <row r="920" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -28490,7 +28491,7 @@
       <c r="AA920" s="1"/>
       <c r="AB920" s="1"/>
     </row>
-    <row r="921" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -28520,7 +28521,7 @@
       <c r="AA921" s="1"/>
       <c r="AB921" s="1"/>
     </row>
-    <row r="922" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -28550,7 +28551,7 @@
       <c r="AA922" s="1"/>
       <c r="AB922" s="1"/>
     </row>
-    <row r="923" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -28580,7 +28581,7 @@
       <c r="AA923" s="1"/>
       <c r="AB923" s="1"/>
     </row>
-    <row r="924" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -28610,7 +28611,7 @@
       <c r="AA924" s="1"/>
       <c r="AB924" s="1"/>
     </row>
-    <row r="925" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -28640,7 +28641,7 @@
       <c r="AA925" s="1"/>
       <c r="AB925" s="1"/>
     </row>
-    <row r="926" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -28670,7 +28671,7 @@
       <c r="AA926" s="1"/>
       <c r="AB926" s="1"/>
     </row>
-    <row r="927" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -28700,7 +28701,7 @@
       <c r="AA927" s="1"/>
       <c r="AB927" s="1"/>
     </row>
-    <row r="928" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -28730,7 +28731,7 @@
       <c r="AA928" s="1"/>
       <c r="AB928" s="1"/>
     </row>
-    <row r="929" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -28760,7 +28761,7 @@
       <c r="AA929" s="1"/>
       <c r="AB929" s="1"/>
     </row>
-    <row r="930" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -28790,7 +28791,7 @@
       <c r="AA930" s="1"/>
       <c r="AB930" s="1"/>
     </row>
-    <row r="931" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -28820,7 +28821,7 @@
       <c r="AA931" s="1"/>
       <c r="AB931" s="1"/>
     </row>
-    <row r="932" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -28850,7 +28851,7 @@
       <c r="AA932" s="1"/>
       <c r="AB932" s="1"/>
     </row>
-    <row r="933" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -28880,7 +28881,7 @@
       <c r="AA933" s="1"/>
       <c r="AB933" s="1"/>
     </row>
-    <row r="934" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -28910,7 +28911,7 @@
       <c r="AA934" s="1"/>
       <c r="AB934" s="1"/>
     </row>
-    <row r="935" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -28940,7 +28941,7 @@
       <c r="AA935" s="1"/>
       <c r="AB935" s="1"/>
     </row>
-    <row r="936" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -28970,7 +28971,7 @@
       <c r="AA936" s="1"/>
       <c r="AB936" s="1"/>
     </row>
-    <row r="937" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -29000,7 +29001,7 @@
       <c r="AA937" s="1"/>
       <c r="AB937" s="1"/>
     </row>
-    <row r="938" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -29030,7 +29031,7 @@
       <c r="AA938" s="1"/>
       <c r="AB938" s="1"/>
     </row>
-    <row r="939" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -29060,7 +29061,7 @@
       <c r="AA939" s="1"/>
       <c r="AB939" s="1"/>
     </row>
-    <row r="940" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -29090,7 +29091,7 @@
       <c r="AA940" s="1"/>
       <c r="AB940" s="1"/>
     </row>
-    <row r="941" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -29120,7 +29121,7 @@
       <c r="AA941" s="1"/>
       <c r="AB941" s="1"/>
     </row>
-    <row r="942" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -29150,7 +29151,7 @@
       <c r="AA942" s="1"/>
       <c r="AB942" s="1"/>
     </row>
-    <row r="943" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -29180,7 +29181,7 @@
       <c r="AA943" s="1"/>
       <c r="AB943" s="1"/>
     </row>
-    <row r="944" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -29210,7 +29211,7 @@
       <c r="AA944" s="1"/>
       <c r="AB944" s="1"/>
     </row>
-    <row r="945" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -29240,7 +29241,7 @@
       <c r="AA945" s="1"/>
       <c r="AB945" s="1"/>
     </row>
-    <row r="946" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -29270,7 +29271,7 @@
       <c r="AA946" s="1"/>
       <c r="AB946" s="1"/>
     </row>
-    <row r="947" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -29300,7 +29301,7 @@
       <c r="AA947" s="1"/>
       <c r="AB947" s="1"/>
     </row>
-    <row r="948" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -29330,7 +29331,7 @@
       <c r="AA948" s="1"/>
       <c r="AB948" s="1"/>
     </row>
-    <row r="949" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -29360,7 +29361,7 @@
       <c r="AA949" s="1"/>
       <c r="AB949" s="1"/>
     </row>
-    <row r="950" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -29390,7 +29391,7 @@
       <c r="AA950" s="1"/>
       <c r="AB950" s="1"/>
     </row>
-    <row r="951" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -29420,7 +29421,7 @@
       <c r="AA951" s="1"/>
       <c r="AB951" s="1"/>
     </row>
-    <row r="952" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -29450,7 +29451,7 @@
       <c r="AA952" s="1"/>
       <c r="AB952" s="1"/>
     </row>
-    <row r="953" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -29480,7 +29481,7 @@
       <c r="AA953" s="1"/>
       <c r="AB953" s="1"/>
     </row>
-    <row r="954" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -29510,7 +29511,7 @@
       <c r="AA954" s="1"/>
       <c r="AB954" s="1"/>
     </row>
-    <row r="955" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -29540,7 +29541,7 @@
       <c r="AA955" s="1"/>
       <c r="AB955" s="1"/>
     </row>
-    <row r="956" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -29570,7 +29571,7 @@
       <c r="AA956" s="1"/>
       <c r="AB956" s="1"/>
     </row>
-    <row r="957" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -29600,7 +29601,7 @@
       <c r="AA957" s="1"/>
       <c r="AB957" s="1"/>
     </row>
-    <row r="958" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -29630,7 +29631,7 @@
       <c r="AA958" s="1"/>
       <c r="AB958" s="1"/>
     </row>
-    <row r="959" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -29660,7 +29661,7 @@
       <c r="AA959" s="1"/>
       <c r="AB959" s="1"/>
     </row>
-    <row r="960" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -29690,7 +29691,7 @@
       <c r="AA960" s="1"/>
       <c r="AB960" s="1"/>
     </row>
-    <row r="961" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -29720,7 +29721,7 @@
       <c r="AA961" s="1"/>
       <c r="AB961" s="1"/>
     </row>
-    <row r="962" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -29750,7 +29751,7 @@
       <c r="AA962" s="1"/>
       <c r="AB962" s="1"/>
     </row>
-    <row r="963" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -29780,7 +29781,7 @@
       <c r="AA963" s="1"/>
       <c r="AB963" s="1"/>
     </row>
-    <row r="964" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -29810,7 +29811,7 @@
       <c r="AA964" s="1"/>
       <c r="AB964" s="1"/>
     </row>
-    <row r="965" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -29840,7 +29841,7 @@
       <c r="AA965" s="1"/>
       <c r="AB965" s="1"/>
     </row>
-    <row r="966" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -29870,7 +29871,7 @@
       <c r="AA966" s="1"/>
       <c r="AB966" s="1"/>
     </row>
-    <row r="967" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -29900,7 +29901,7 @@
       <c r="AA967" s="1"/>
       <c r="AB967" s="1"/>
     </row>
-    <row r="968" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -29930,7 +29931,7 @@
       <c r="AA968" s="1"/>
       <c r="AB968" s="1"/>
     </row>
-    <row r="969" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -29960,7 +29961,7 @@
       <c r="AA969" s="1"/>
       <c r="AB969" s="1"/>
     </row>
-    <row r="970" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -29990,7 +29991,7 @@
       <c r="AA970" s="1"/>
       <c r="AB970" s="1"/>
     </row>
-    <row r="971" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -30020,7 +30021,7 @@
       <c r="AA971" s="1"/>
       <c r="AB971" s="1"/>
     </row>
-    <row r="972" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -30050,7 +30051,7 @@
       <c r="AA972" s="1"/>
       <c r="AB972" s="1"/>
     </row>
-    <row r="973" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -30080,7 +30081,7 @@
       <c r="AA973" s="1"/>
       <c r="AB973" s="1"/>
     </row>
-    <row r="974" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -30110,7 +30111,7 @@
       <c r="AA974" s="1"/>
       <c r="AB974" s="1"/>
     </row>
-    <row r="975" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -30140,7 +30141,7 @@
       <c r="AA975" s="1"/>
       <c r="AB975" s="1"/>
     </row>
-    <row r="976" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -30170,7 +30171,7 @@
       <c r="AA976" s="1"/>
       <c r="AB976" s="1"/>
     </row>
-    <row r="977" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -30200,7 +30201,7 @@
       <c r="AA977" s="1"/>
       <c r="AB977" s="1"/>
     </row>
-    <row r="978" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -30230,7 +30231,7 @@
       <c r="AA978" s="1"/>
       <c r="AB978" s="1"/>
     </row>
-    <row r="979" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -30260,7 +30261,7 @@
       <c r="AA979" s="1"/>
       <c r="AB979" s="1"/>
     </row>
-    <row r="980" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -30290,7 +30291,7 @@
       <c r="AA980" s="1"/>
       <c r="AB980" s="1"/>
     </row>
-    <row r="981" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -30320,7 +30321,7 @@
       <c r="AA981" s="1"/>
       <c r="AB981" s="1"/>
     </row>
-    <row r="982" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -30350,7 +30351,7 @@
       <c r="AA982" s="1"/>
       <c r="AB982" s="1"/>
     </row>
-    <row r="983" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -30380,7 +30381,7 @@
       <c r="AA983" s="1"/>
       <c r="AB983" s="1"/>
     </row>
-    <row r="984" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -30410,7 +30411,7 @@
       <c r="AA984" s="1"/>
       <c r="AB984" s="1"/>
     </row>
-    <row r="985" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -30440,7 +30441,7 @@
       <c r="AA985" s="1"/>
       <c r="AB985" s="1"/>
     </row>
-    <row r="986" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -30470,7 +30471,7 @@
       <c r="AA986" s="1"/>
       <c r="AB986" s="1"/>
     </row>
-    <row r="987" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -30500,7 +30501,7 @@
       <c r="AA987" s="1"/>
       <c r="AB987" s="1"/>
     </row>
-    <row r="988" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -30530,7 +30531,7 @@
       <c r="AA988" s="1"/>
       <c r="AB988" s="1"/>
     </row>
-    <row r="989" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -30560,7 +30561,7 @@
       <c r="AA989" s="1"/>
       <c r="AB989" s="1"/>
     </row>
-    <row r="990" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -30590,7 +30591,7 @@
       <c r="AA990" s="1"/>
       <c r="AB990" s="1"/>
     </row>
-    <row r="991" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -30620,7 +30621,7 @@
       <c r="AA991" s="1"/>
       <c r="AB991" s="1"/>
     </row>
-    <row r="992" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -30650,7 +30651,7 @@
       <c r="AA992" s="1"/>
       <c r="AB992" s="1"/>
     </row>
-    <row r="993" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -30680,7 +30681,7 @@
       <c r="AA993" s="1"/>
       <c r="AB993" s="1"/>
     </row>
-    <row r="994" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -30710,7 +30711,7 @@
       <c r="AA994" s="1"/>
       <c r="AB994" s="1"/>
     </row>
-    <row r="995" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -30740,7 +30741,7 @@
       <c r="AA995" s="1"/>
       <c r="AB995" s="1"/>
     </row>
-    <row r="996" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -30770,7 +30771,7 @@
       <c r="AA996" s="1"/>
       <c r="AB996" s="1"/>
     </row>
-    <row r="997" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -30800,7 +30801,7 @@
       <c r="AA997" s="1"/>
       <c r="AB997" s="1"/>
     </row>
-    <row r="998" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -30830,7 +30831,7 @@
       <c r="AA998" s="1"/>
       <c r="AB998" s="1"/>
     </row>
-    <row r="999" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -30860,7 +30861,7 @@
       <c r="AA999" s="1"/>
       <c r="AB999" s="1"/>
     </row>
-    <row r="1000" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -30890,7 +30891,7 @@
       <c r="AA1000" s="1"/>
       <c r="AB1000" s="1"/>
     </row>
-    <row r="1001" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476AD030-5D53-482B-A3B3-976CAB9E6F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA39B26-EF7C-48D5-BE5F-7E0B9DF2214E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MilestoneParam" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -239,7 +239,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -456,15 +456,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AB1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" customWidth="1"/>
+    <col min="10" max="10" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -514,7 +514,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -564,7 +564,7 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -593,7 +593,7 @@
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -622,7 +622,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>0</v>
@@ -633,8 +633,8 @@
       <c r="D5" s="1">
         <v>9000</v>
       </c>
-      <c r="E5" s="4">
-        <v>5</v>
+      <c r="E5" s="1">
+        <v>3</v>
       </c>
       <c r="F5" s="4">
         <v>1.25</v>
@@ -651,8 +651,9 @@
       <c r="J5" s="1">
         <v>3</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="L5" s="4">
+        <v>5</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -670,7 +671,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1</v>
@@ -678,8 +679,8 @@
       <c r="C6" s="4">
         <v>2</v>
       </c>
-      <c r="E6" s="4">
-        <v>6</v>
+      <c r="E6" s="1">
+        <v>3</v>
       </c>
       <c r="F6" s="4">
         <v>1.25</v>
@@ -696,6 +697,9 @@
       <c r="J6" s="1">
         <v>3</v>
       </c>
+      <c r="L6" s="4">
+        <v>6</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -712,7 +716,7 @@
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
@@ -720,8 +724,8 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="4">
-        <v>7</v>
+      <c r="E7" s="1">
+        <v>4</v>
       </c>
       <c r="F7" s="1">
         <v>1.25</v>
@@ -738,6 +742,9 @@
       <c r="J7" s="1">
         <v>4</v>
       </c>
+      <c r="L7" s="4">
+        <v>7</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -754,7 +761,7 @@
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
@@ -762,8 +769,8 @@
       <c r="C8" s="1">
         <v>9</v>
       </c>
-      <c r="E8" s="4">
-        <v>8</v>
+      <c r="E8" s="1">
+        <v>4</v>
       </c>
       <c r="F8" s="1">
         <v>1.3</v>
@@ -780,6 +787,9 @@
       <c r="J8" s="1">
         <v>4</v>
       </c>
+      <c r="L8" s="4">
+        <v>8</v>
+      </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -796,7 +806,7 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
@@ -805,7 +815,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1">
         <v>1.3</v>
@@ -822,6 +832,9 @@
       <c r="J9" s="1">
         <v>4</v>
       </c>
+      <c r="L9" s="1">
+        <v>9</v>
+      </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -838,7 +851,7 @@
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
     </row>
-    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>5</v>
@@ -847,7 +860,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1">
         <v>1.3</v>
@@ -864,6 +877,9 @@
       <c r="J10" s="1">
         <v>5</v>
       </c>
+      <c r="L10" s="1">
+        <v>10</v>
+      </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -880,7 +896,7 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>6</v>
@@ -889,7 +905,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F11" s="1">
         <v>1.3</v>
@@ -905,6 +921,9 @@
       </c>
       <c r="J11" s="1">
         <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>11</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -923,7 +942,7 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>7</v>
@@ -932,7 +951,7 @@
         <v>17</v>
       </c>
       <c r="E12" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F12" s="1">
         <v>1.3</v>
@@ -948,6 +967,9 @@
       </c>
       <c r="J12" s="1">
         <v>5</v>
+      </c>
+      <c r="L12" s="1">
+        <v>12</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -966,7 +988,7 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
     </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>8</v>
@@ -976,7 +998,7 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1">
         <v>1.3</v>
@@ -992,6 +1014,9 @@
       </c>
       <c r="J13" s="1">
         <v>5</v>
+      </c>
+      <c r="L13" s="1">
+        <v>13</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1010,7 +1035,7 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
     </row>
-    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>9</v>
@@ -1020,7 +1045,7 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1">
         <v>1.35</v>
@@ -1037,8 +1062,9 @@
       <c r="J14" s="1">
         <v>6</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="L14" s="1">
+        <v>14</v>
+      </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1056,7 +1082,7 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>10</v>
@@ -1066,7 +1092,7 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1">
         <v>1.35</v>
@@ -1083,8 +1109,9 @@
       <c r="J15" s="1">
         <v>6</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="L15" s="1">
+        <v>15</v>
+      </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1102,7 +1129,7 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
     </row>
-    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>11</v>
@@ -1112,7 +1139,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1">
         <v>1.35</v>
@@ -1129,8 +1156,9 @@
       <c r="J16" s="1">
         <v>6</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="L16" s="1">
+        <v>16</v>
+      </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1148,7 +1176,7 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>12</v>
@@ -1158,7 +1186,7 @@
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1">
         <v>1.35</v>
@@ -1175,8 +1203,9 @@
       <c r="J17" s="1">
         <v>7</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="L17" s="1">
+        <v>17</v>
+      </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1194,7 +1223,7 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
@@ -1203,8 +1232,8 @@
         <v>29</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="2">
-        <v>18</v>
+      <c r="E18" s="1">
+        <v>9</v>
       </c>
       <c r="F18" s="1">
         <v>1.35</v>
@@ -1221,8 +1250,9 @@
       <c r="J18" s="1">
         <v>7</v>
       </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="L18" s="2">
+        <v>18</v>
+      </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1240,7 +1270,7 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>14</v>
@@ -1250,7 +1280,7 @@
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1">
         <v>1.35</v>
@@ -1267,8 +1297,9 @@
       <c r="J19" s="1">
         <v>7</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="L19" s="1">
+        <v>19</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1286,7 +1317,7 @@
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
     </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>15</v>
@@ -1296,7 +1327,7 @@
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1">
         <v>1.35</v>
@@ -1313,8 +1344,9 @@
       <c r="J20" s="1">
         <v>8</v>
       </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="L20" s="1">
+        <v>20</v>
+      </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -1332,7 +1364,7 @@
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
     </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>16</v>
@@ -1342,7 +1374,7 @@
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1">
         <v>1.35</v>
@@ -1359,8 +1391,9 @@
       <c r="J21" s="1">
         <v>8</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="L21" s="1">
+        <v>21</v>
+      </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -1378,7 +1411,7 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>17</v>
@@ -1388,7 +1421,7 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1">
         <v>1.4</v>
@@ -1405,8 +1438,9 @@
       <c r="J22" s="1">
         <v>8</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="1">
+        <v>21</v>
+      </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -1424,7 +1458,7 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>18</v>
@@ -1434,7 +1468,7 @@
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1">
         <v>1.4</v>
@@ -1451,8 +1485,9 @@
       <c r="J23" s="1">
         <v>8</v>
       </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1">
+        <v>22</v>
+      </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -1470,7 +1505,7 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>19</v>
@@ -1480,7 +1515,7 @@
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1">
         <v>1.4</v>
@@ -1497,8 +1532,9 @@
       <c r="J24" s="1">
         <v>8</v>
       </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="L24" s="1">
+        <v>23</v>
+      </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -1516,7 +1552,7 @@
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
     </row>
-    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>20</v>
@@ -1526,7 +1562,7 @@
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1">
         <v>1.4</v>
@@ -1543,8 +1579,9 @@
       <c r="J25" s="1">
         <v>8</v>
       </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="L25" s="1">
+        <v>24</v>
+      </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -1562,7 +1599,7 @@
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
     </row>
-    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>21</v>
@@ -1572,7 +1609,7 @@
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F26" s="1">
         <v>1.4</v>
@@ -1589,8 +1626,9 @@
       <c r="J26" s="1">
         <v>9</v>
       </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="L26" s="1">
+        <v>25</v>
+      </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1608,7 +1646,7 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>22</v>
@@ -1617,7 +1655,7 @@
         <v>45</v>
       </c>
       <c r="E27" s="1">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F27" s="2">
         <v>1.5</v>
@@ -1634,8 +1672,9 @@
       <c r="J27" s="2">
         <v>9</v>
       </c>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="L27" s="1">
+        <v>25</v>
+      </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -1653,7 +1692,7 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>23</v>
@@ -1663,7 +1702,7 @@
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F28" s="2">
         <v>1.5</v>
@@ -1680,8 +1719,9 @@
       <c r="J28" s="1">
         <v>9</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
+      <c r="L28" s="1">
+        <v>26</v>
+      </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -1699,7 +1739,7 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>24</v>
@@ -1709,7 +1749,7 @@
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2">
         <v>1.5</v>
@@ -1726,8 +1766,9 @@
       <c r="J29" s="1">
         <v>9</v>
       </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="L29" s="1">
+        <v>27</v>
+      </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
@@ -1745,7 +1786,7 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>25</v>
@@ -1755,7 +1796,7 @@
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2">
         <v>1.5</v>
@@ -1772,8 +1813,9 @@
       <c r="J30" s="1">
         <v>10</v>
       </c>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="L30" s="1">
+        <v>28</v>
+      </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -1791,7 +1833,7 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
     </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1821,7 +1863,7 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1851,7 +1893,7 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1881,7 +1923,7 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
     </row>
-    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1911,7 +1953,7 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
     </row>
-    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1941,7 +1983,7 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
     </row>
-    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1971,7 +2013,7 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2001,7 +2043,7 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2031,7 +2073,7 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
     </row>
-    <row r="39" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2061,7 +2103,7 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
     </row>
-    <row r="40" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2091,7 +2133,7 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
     </row>
-    <row r="41" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2121,7 +2163,7 @@
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
     </row>
-    <row r="42" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2151,7 +2193,7 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
     </row>
-    <row r="43" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2181,7 +2223,7 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
     </row>
-    <row r="44" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2211,7 +2253,7 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
     </row>
-    <row r="45" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2241,7 +2283,7 @@
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
     </row>
-    <row r="46" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2271,7 +2313,7 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2301,7 +2343,7 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
     </row>
-    <row r="48" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2331,7 +2373,7 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
     </row>
-    <row r="49" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2361,7 +2403,7 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2391,7 +2433,7 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
     </row>
-    <row r="51" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2421,7 +2463,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2451,7 +2493,7 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
     </row>
-    <row r="53" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2481,7 +2523,7 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
     </row>
-    <row r="54" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2511,7 +2553,7 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
     </row>
-    <row r="55" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2541,7 +2583,7 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2571,7 +2613,7 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2601,7 +2643,7 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2631,7 +2673,7 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2661,7 +2703,7 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2691,7 +2733,7 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2721,7 +2763,7 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2751,7 +2793,7 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2781,7 +2823,7 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2811,7 +2853,7 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2841,7 +2883,7 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="66" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2871,7 +2913,7 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
     </row>
-    <row r="67" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2901,7 +2943,7 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
     </row>
-    <row r="68" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2931,7 +2973,7 @@
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
     </row>
-    <row r="69" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2961,7 +3003,7 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
     </row>
-    <row r="70" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2991,7 +3033,7 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3021,7 +3063,7 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3051,7 +3093,7 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
     </row>
-    <row r="73" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3081,7 +3123,7 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
     </row>
-    <row r="74" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3111,7 +3153,7 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
     </row>
-    <row r="75" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3141,7 +3183,7 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
     </row>
-    <row r="76" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3171,7 +3213,7 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
     </row>
-    <row r="77" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3201,7 +3243,7 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
     </row>
-    <row r="78" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3231,7 +3273,7 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
     </row>
-    <row r="79" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3261,7 +3303,7 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
     </row>
-    <row r="80" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3291,7 +3333,7 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
     </row>
-    <row r="81" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3321,7 +3363,7 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
     </row>
-    <row r="82" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3351,7 +3393,7 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
     </row>
-    <row r="83" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3381,7 +3423,7 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
     </row>
-    <row r="84" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3411,7 +3453,7 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
     </row>
-    <row r="85" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3441,7 +3483,7 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
     </row>
-    <row r="86" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3471,7 +3513,7 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
     </row>
-    <row r="87" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3501,7 +3543,7 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
     </row>
-    <row r="88" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3531,7 +3573,7 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
     </row>
-    <row r="89" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3561,7 +3603,7 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
     </row>
-    <row r="90" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3591,7 +3633,7 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
     </row>
-    <row r="91" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3621,7 +3663,7 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
     </row>
-    <row r="92" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3651,7 +3693,7 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
     </row>
-    <row r="93" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3681,7 +3723,7 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
     </row>
-    <row r="94" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3711,7 +3753,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3741,7 +3783,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3771,7 +3813,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3801,7 +3843,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3831,7 +3873,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3861,7 +3903,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3891,7 +3933,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3921,7 +3963,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3951,7 +3993,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3981,7 +4023,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4011,7 +4053,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4041,7 +4083,7 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
     </row>
-    <row r="106" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4071,7 +4113,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4101,7 +4143,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4131,7 +4173,7 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
     </row>
-    <row r="109" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4161,7 +4203,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4191,7 +4233,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4221,7 +4263,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4251,7 +4293,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4281,7 +4323,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4311,7 +4353,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4341,7 +4383,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4371,7 +4413,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4401,7 +4443,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4431,7 +4473,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4461,7 +4503,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4491,7 +4533,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4521,7 +4563,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4551,7 +4593,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4581,7 +4623,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4611,7 +4653,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4641,7 +4683,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4671,7 +4713,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4701,7 +4743,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4731,7 +4773,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4761,7 +4803,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4791,7 +4833,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4821,7 +4863,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4851,7 +4893,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4881,7 +4923,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4911,7 +4953,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4941,7 +4983,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4971,7 +5013,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5001,7 +5043,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5031,7 +5073,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5061,7 +5103,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5091,7 +5133,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5121,7 +5163,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5151,7 +5193,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5181,7 +5223,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5211,7 +5253,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5241,7 +5283,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5271,7 +5313,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5301,7 +5343,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5331,7 +5373,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5361,7 +5403,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5391,7 +5433,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5421,7 +5463,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5451,7 +5493,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5481,7 +5523,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5511,7 +5553,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5541,7 +5583,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5571,7 +5613,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5601,7 +5643,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5631,7 +5673,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5661,7 +5703,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5691,7 +5733,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5721,7 +5763,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5751,7 +5793,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5781,7 +5823,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5811,7 +5853,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5841,7 +5883,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5871,7 +5913,7 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
     </row>
-    <row r="167" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5901,7 +5943,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5931,7 +5973,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5961,7 +6003,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5991,7 +6033,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6021,7 +6063,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6051,7 +6093,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6081,7 +6123,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6111,7 +6153,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6141,7 +6183,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6171,7 +6213,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6201,7 +6243,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6231,7 +6273,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6261,7 +6303,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6291,7 +6333,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6321,7 +6363,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6351,7 +6393,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6381,7 +6423,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6411,7 +6453,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6441,7 +6483,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6471,7 +6513,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6501,7 +6543,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6531,7 +6573,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6561,7 +6603,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6591,7 +6633,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6621,7 +6663,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6651,7 +6693,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6681,7 +6723,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6711,7 +6753,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6741,7 +6783,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6771,7 +6813,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6801,7 +6843,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6831,7 +6873,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6861,7 +6903,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6891,7 +6933,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6921,7 +6963,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6951,7 +6993,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6981,7 +7023,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7011,7 +7053,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7041,7 +7083,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7071,7 +7113,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7101,7 +7143,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7131,7 +7173,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7161,7 +7203,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7191,7 +7233,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7221,7 +7263,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7251,7 +7293,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7281,7 +7323,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7311,7 +7353,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7341,7 +7383,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7371,7 +7413,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7401,7 +7443,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7431,7 +7473,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7461,7 +7503,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7491,7 +7533,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7521,7 +7563,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7551,7 +7593,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7581,7 +7623,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7611,7 +7653,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7641,7 +7683,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7671,7 +7713,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7701,7 +7743,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7731,7 +7773,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7761,7 +7803,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7791,7 +7833,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7821,7 +7863,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7851,7 +7893,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7881,7 +7923,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -7911,7 +7953,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7941,7 +7983,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -7971,7 +8013,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8001,7 +8043,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8031,7 +8073,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8061,7 +8103,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8091,7 +8133,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8121,7 +8163,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8151,7 +8193,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8181,7 +8223,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8211,7 +8253,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8241,7 +8283,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8271,7 +8313,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8301,7 +8343,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8331,7 +8373,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8361,7 +8403,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8391,7 +8433,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8421,7 +8463,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8451,7 +8493,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8481,7 +8523,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8511,7 +8553,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8541,7 +8583,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8571,7 +8613,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8601,7 +8643,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8631,7 +8673,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8661,7 +8703,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8691,7 +8733,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8721,7 +8763,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8751,7 +8793,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8781,7 +8823,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8811,7 +8853,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -8841,7 +8883,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -8871,7 +8913,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -8901,7 +8943,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -8931,7 +8973,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -8961,7 +9003,7 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
     </row>
-    <row r="270" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -8991,7 +9033,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9021,7 +9063,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9051,7 +9093,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9081,7 +9123,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9111,7 +9153,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
     </row>
-    <row r="275" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9141,7 +9183,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9171,7 +9213,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9201,7 +9243,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9231,7 +9273,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9261,7 +9303,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9291,7 +9333,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9321,7 +9363,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9351,7 +9393,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9381,7 +9423,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9411,7 +9453,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9441,7 +9483,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -9471,7 +9513,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -9501,7 +9543,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -9531,7 +9573,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -9561,7 +9603,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -9591,7 +9633,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -9621,7 +9663,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -9651,7 +9693,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -9681,7 +9723,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -9711,7 +9753,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -9741,7 +9783,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -9771,7 +9813,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -9801,7 +9843,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -9831,7 +9873,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -9861,7 +9903,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -9891,7 +9933,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -9921,7 +9963,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -9951,7 +9993,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -9981,7 +10023,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10011,7 +10053,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10041,7 +10083,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10071,7 +10113,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10101,7 +10143,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10131,7 +10173,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10161,7 +10203,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10191,7 +10233,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10221,7 +10263,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10251,7 +10293,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10281,7 +10323,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10311,7 +10353,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10341,7 +10383,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10371,7 +10413,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10401,7 +10443,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -10431,7 +10473,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -10461,7 +10503,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -10491,7 +10533,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -10521,7 +10563,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -10551,7 +10593,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -10581,7 +10623,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10611,7 +10653,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10641,7 +10683,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -10671,7 +10713,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -10701,7 +10743,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -10731,7 +10773,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -10761,7 +10803,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -10791,7 +10833,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -10821,7 +10863,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -10851,7 +10893,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -10881,7 +10923,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -10911,7 +10953,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -10941,7 +10983,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -10971,7 +11013,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11001,7 +11043,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11031,7 +11073,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11061,7 +11103,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11091,7 +11133,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11121,7 +11163,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11151,7 +11193,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11181,7 +11223,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11211,7 +11253,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11241,7 +11283,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11271,7 +11313,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11301,7 +11343,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11331,7 +11373,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11361,7 +11403,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11391,7 +11433,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11421,7 +11463,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11451,7 +11493,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -11481,7 +11523,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -11511,7 +11553,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -11541,7 +11583,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -11571,7 +11613,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -11601,7 +11643,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -11631,7 +11673,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -11661,7 +11703,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -11691,7 +11733,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -11721,7 +11763,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -11751,7 +11793,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -11781,7 +11823,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -11811,7 +11853,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -11841,7 +11883,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -11871,7 +11913,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -11901,7 +11943,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -11931,7 +11973,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -11961,7 +12003,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -11991,7 +12033,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12021,7 +12063,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12051,7 +12093,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12081,7 +12123,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12111,7 +12153,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12141,7 +12183,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12171,7 +12213,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12201,7 +12243,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12231,7 +12273,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12261,7 +12303,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12291,7 +12333,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12321,7 +12363,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12351,7 +12393,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12381,7 +12423,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12411,7 +12453,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12441,7 +12483,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12471,7 +12513,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12501,7 +12543,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12531,7 +12573,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -12561,7 +12603,7 @@
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
     </row>
-    <row r="390" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -12591,7 +12633,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -12621,7 +12663,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -12651,7 +12693,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -12681,7 +12723,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -12711,7 +12753,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -12741,7 +12783,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -12771,7 +12813,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -12801,7 +12843,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -12831,7 +12873,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -12861,7 +12903,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -12891,7 +12933,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -12921,7 +12963,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -12951,7 +12993,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -12981,7 +13023,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13011,7 +13053,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13041,7 +13083,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13071,7 +13113,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13101,7 +13143,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13131,7 +13173,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13161,7 +13203,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13191,7 +13233,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13221,7 +13263,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13251,7 +13293,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13281,7 +13323,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13311,7 +13353,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13341,7 +13383,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13371,7 +13413,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13401,7 +13443,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13431,7 +13473,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13461,7 +13503,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13491,7 +13533,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -13521,7 +13563,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -13551,7 +13593,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -13581,7 +13623,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -13611,7 +13653,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -13641,7 +13683,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -13671,7 +13713,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -13701,7 +13743,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -13731,7 +13773,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -13761,7 +13803,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -13791,7 +13833,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -13821,7 +13863,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -13851,7 +13893,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -13881,7 +13923,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -13911,7 +13953,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -13941,7 +13983,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -13971,7 +14013,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14001,7 +14043,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14031,7 +14073,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14061,7 +14103,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14091,7 +14133,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14121,7 +14163,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14151,7 +14193,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14181,7 +14223,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14211,7 +14253,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14241,7 +14283,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14271,7 +14313,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14301,7 +14343,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14331,7 +14373,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14361,7 +14403,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14391,7 +14433,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14421,7 +14463,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14451,7 +14493,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -14481,7 +14523,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -14511,7 +14553,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -14541,7 +14583,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -14571,7 +14613,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -14601,7 +14643,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -14631,7 +14673,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -14661,7 +14703,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -14691,7 +14733,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -14721,7 +14763,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -14751,7 +14793,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -14781,7 +14823,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -14811,7 +14853,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -14841,7 +14883,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -14871,7 +14913,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -14901,7 +14943,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -14931,7 +14973,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -14961,7 +15003,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -14991,7 +15033,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15021,7 +15063,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15051,7 +15093,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15081,7 +15123,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15111,7 +15153,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15141,7 +15183,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15171,7 +15213,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15201,7 +15243,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15231,7 +15273,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15261,7 +15303,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15291,7 +15333,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15321,7 +15363,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15351,7 +15393,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15381,7 +15423,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -15411,7 +15453,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -15441,7 +15483,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -15471,7 +15513,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -15501,7 +15543,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -15531,7 +15573,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -15561,7 +15603,7 @@
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
     </row>
-    <row r="490" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -15591,7 +15633,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -15621,7 +15663,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -15651,7 +15693,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -15681,7 +15723,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -15711,7 +15753,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -15741,7 +15783,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -15771,7 +15813,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -15801,7 +15843,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -15831,7 +15873,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -15861,7 +15903,7 @@
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
     </row>
-    <row r="500" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -15891,7 +15933,7 @@
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
     </row>
-    <row r="501" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -15921,7 +15963,7 @@
       <c r="AA501" s="1"/>
       <c r="AB501" s="1"/>
     </row>
-    <row r="502" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -15951,7 +15993,7 @@
       <c r="AA502" s="1"/>
       <c r="AB502" s="1"/>
     </row>
-    <row r="503" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -15981,7 +16023,7 @@
       <c r="AA503" s="1"/>
       <c r="AB503" s="1"/>
     </row>
-    <row r="504" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16011,7 +16053,7 @@
       <c r="AA504" s="1"/>
       <c r="AB504" s="1"/>
     </row>
-    <row r="505" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16041,7 +16083,7 @@
       <c r="AA505" s="1"/>
       <c r="AB505" s="1"/>
     </row>
-    <row r="506" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16071,7 +16113,7 @@
       <c r="AA506" s="1"/>
       <c r="AB506" s="1"/>
     </row>
-    <row r="507" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16101,7 +16143,7 @@
       <c r="AA507" s="1"/>
       <c r="AB507" s="1"/>
     </row>
-    <row r="508" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16131,7 +16173,7 @@
       <c r="AA508" s="1"/>
       <c r="AB508" s="1"/>
     </row>
-    <row r="509" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16161,7 +16203,7 @@
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
     </row>
-    <row r="510" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16191,7 +16233,7 @@
       <c r="AA510" s="1"/>
       <c r="AB510" s="1"/>
     </row>
-    <row r="511" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16221,7 +16263,7 @@
       <c r="AA511" s="1"/>
       <c r="AB511" s="1"/>
     </row>
-    <row r="512" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16251,7 +16293,7 @@
       <c r="AA512" s="1"/>
       <c r="AB512" s="1"/>
     </row>
-    <row r="513" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16281,7 +16323,7 @@
       <c r="AA513" s="1"/>
       <c r="AB513" s="1"/>
     </row>
-    <row r="514" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16311,7 +16353,7 @@
       <c r="AA514" s="1"/>
       <c r="AB514" s="1"/>
     </row>
-    <row r="515" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16341,7 +16383,7 @@
       <c r="AA515" s="1"/>
       <c r="AB515" s="1"/>
     </row>
-    <row r="516" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -16371,7 +16413,7 @@
       <c r="AA516" s="1"/>
       <c r="AB516" s="1"/>
     </row>
-    <row r="517" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -16401,7 +16443,7 @@
       <c r="AA517" s="1"/>
       <c r="AB517" s="1"/>
     </row>
-    <row r="518" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -16431,7 +16473,7 @@
       <c r="AA518" s="1"/>
       <c r="AB518" s="1"/>
     </row>
-    <row r="519" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -16461,7 +16503,7 @@
       <c r="AA519" s="1"/>
       <c r="AB519" s="1"/>
     </row>
-    <row r="520" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -16491,7 +16533,7 @@
       <c r="AA520" s="1"/>
       <c r="AB520" s="1"/>
     </row>
-    <row r="521" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -16521,7 +16563,7 @@
       <c r="AA521" s="1"/>
       <c r="AB521" s="1"/>
     </row>
-    <row r="522" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -16551,7 +16593,7 @@
       <c r="AA522" s="1"/>
       <c r="AB522" s="1"/>
     </row>
-    <row r="523" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -16581,7 +16623,7 @@
       <c r="AA523" s="1"/>
       <c r="AB523" s="1"/>
     </row>
-    <row r="524" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -16611,7 +16653,7 @@
       <c r="AA524" s="1"/>
       <c r="AB524" s="1"/>
     </row>
-    <row r="525" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -16641,7 +16683,7 @@
       <c r="AA525" s="1"/>
       <c r="AB525" s="1"/>
     </row>
-    <row r="526" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -16671,7 +16713,7 @@
       <c r="AA526" s="1"/>
       <c r="AB526" s="1"/>
     </row>
-    <row r="527" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -16701,7 +16743,7 @@
       <c r="AA527" s="1"/>
       <c r="AB527" s="1"/>
     </row>
-    <row r="528" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -16731,7 +16773,7 @@
       <c r="AA528" s="1"/>
       <c r="AB528" s="1"/>
     </row>
-    <row r="529" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -16761,7 +16803,7 @@
       <c r="AA529" s="1"/>
       <c r="AB529" s="1"/>
     </row>
-    <row r="530" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -16791,7 +16833,7 @@
       <c r="AA530" s="1"/>
       <c r="AB530" s="1"/>
     </row>
-    <row r="531" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -16821,7 +16863,7 @@
       <c r="AA531" s="1"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -16851,7 +16893,7 @@
       <c r="AA532" s="1"/>
       <c r="AB532" s="1"/>
     </row>
-    <row r="533" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -16881,7 +16923,7 @@
       <c r="AA533" s="1"/>
       <c r="AB533" s="1"/>
     </row>
-    <row r="534" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -16911,7 +16953,7 @@
       <c r="AA534" s="1"/>
       <c r="AB534" s="1"/>
     </row>
-    <row r="535" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -16941,7 +16983,7 @@
       <c r="AA535" s="1"/>
       <c r="AB535" s="1"/>
     </row>
-    <row r="536" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -16971,7 +17013,7 @@
       <c r="AA536" s="1"/>
       <c r="AB536" s="1"/>
     </row>
-    <row r="537" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17001,7 +17043,7 @@
       <c r="AA537" s="1"/>
       <c r="AB537" s="1"/>
     </row>
-    <row r="538" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17031,7 +17073,7 @@
       <c r="AA538" s="1"/>
       <c r="AB538" s="1"/>
     </row>
-    <row r="539" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17061,7 +17103,7 @@
       <c r="AA539" s="1"/>
       <c r="AB539" s="1"/>
     </row>
-    <row r="540" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17091,7 +17133,7 @@
       <c r="AA540" s="1"/>
       <c r="AB540" s="1"/>
     </row>
-    <row r="541" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17121,7 +17163,7 @@
       <c r="AA541" s="1"/>
       <c r="AB541" s="1"/>
     </row>
-    <row r="542" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17151,7 +17193,7 @@
       <c r="AA542" s="1"/>
       <c r="AB542" s="1"/>
     </row>
-    <row r="543" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17181,7 +17223,7 @@
       <c r="AA543" s="1"/>
       <c r="AB543" s="1"/>
     </row>
-    <row r="544" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17211,7 +17253,7 @@
       <c r="AA544" s="1"/>
       <c r="AB544" s="1"/>
     </row>
-    <row r="545" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17241,7 +17283,7 @@
       <c r="AA545" s="1"/>
       <c r="AB545" s="1"/>
     </row>
-    <row r="546" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -17271,7 +17313,7 @@
       <c r="AA546" s="1"/>
       <c r="AB546" s="1"/>
     </row>
-    <row r="547" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -17301,7 +17343,7 @@
       <c r="AA547" s="1"/>
       <c r="AB547" s="1"/>
     </row>
-    <row r="548" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -17331,7 +17373,7 @@
       <c r="AA548" s="1"/>
       <c r="AB548" s="1"/>
     </row>
-    <row r="549" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -17361,7 +17403,7 @@
       <c r="AA549" s="1"/>
       <c r="AB549" s="1"/>
     </row>
-    <row r="550" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -17391,7 +17433,7 @@
       <c r="AA550" s="1"/>
       <c r="AB550" s="1"/>
     </row>
-    <row r="551" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -17421,7 +17463,7 @@
       <c r="AA551" s="1"/>
       <c r="AB551" s="1"/>
     </row>
-    <row r="552" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -17451,7 +17493,7 @@
       <c r="AA552" s="1"/>
       <c r="AB552" s="1"/>
     </row>
-    <row r="553" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -17481,7 +17523,7 @@
       <c r="AA553" s="1"/>
       <c r="AB553" s="1"/>
     </row>
-    <row r="554" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -17511,7 +17553,7 @@
       <c r="AA554" s="1"/>
       <c r="AB554" s="1"/>
     </row>
-    <row r="555" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -17541,7 +17583,7 @@
       <c r="AA555" s="1"/>
       <c r="AB555" s="1"/>
     </row>
-    <row r="556" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -17571,7 +17613,7 @@
       <c r="AA556" s="1"/>
       <c r="AB556" s="1"/>
     </row>
-    <row r="557" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -17601,7 +17643,7 @@
       <c r="AA557" s="1"/>
       <c r="AB557" s="1"/>
     </row>
-    <row r="558" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -17631,7 +17673,7 @@
       <c r="AA558" s="1"/>
       <c r="AB558" s="1"/>
     </row>
-    <row r="559" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -17661,7 +17703,7 @@
       <c r="AA559" s="1"/>
       <c r="AB559" s="1"/>
     </row>
-    <row r="560" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -17691,7 +17733,7 @@
       <c r="AA560" s="1"/>
       <c r="AB560" s="1"/>
     </row>
-    <row r="561" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -17721,7 +17763,7 @@
       <c r="AA561" s="1"/>
       <c r="AB561" s="1"/>
     </row>
-    <row r="562" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -17751,7 +17793,7 @@
       <c r="AA562" s="1"/>
       <c r="AB562" s="1"/>
     </row>
-    <row r="563" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -17781,7 +17823,7 @@
       <c r="AA563" s="1"/>
       <c r="AB563" s="1"/>
     </row>
-    <row r="564" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -17811,7 +17853,7 @@
       <c r="AA564" s="1"/>
       <c r="AB564" s="1"/>
     </row>
-    <row r="565" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -17841,7 +17883,7 @@
       <c r="AA565" s="1"/>
       <c r="AB565" s="1"/>
     </row>
-    <row r="566" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -17871,7 +17913,7 @@
       <c r="AA566" s="1"/>
       <c r="AB566" s="1"/>
     </row>
-    <row r="567" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -17901,7 +17943,7 @@
       <c r="AA567" s="1"/>
       <c r="AB567" s="1"/>
     </row>
-    <row r="568" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -17931,7 +17973,7 @@
       <c r="AA568" s="1"/>
       <c r="AB568" s="1"/>
     </row>
-    <row r="569" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -17961,7 +18003,7 @@
       <c r="AA569" s="1"/>
       <c r="AB569" s="1"/>
     </row>
-    <row r="570" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -17991,7 +18033,7 @@
       <c r="AA570" s="1"/>
       <c r="AB570" s="1"/>
     </row>
-    <row r="571" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18021,7 +18063,7 @@
       <c r="AA571" s="1"/>
       <c r="AB571" s="1"/>
     </row>
-    <row r="572" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18051,7 +18093,7 @@
       <c r="AA572" s="1"/>
       <c r="AB572" s="1"/>
     </row>
-    <row r="573" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18081,7 +18123,7 @@
       <c r="AA573" s="1"/>
       <c r="AB573" s="1"/>
     </row>
-    <row r="574" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18111,7 +18153,7 @@
       <c r="AA574" s="1"/>
       <c r="AB574" s="1"/>
     </row>
-    <row r="575" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18141,7 +18183,7 @@
       <c r="AA575" s="1"/>
       <c r="AB575" s="1"/>
     </row>
-    <row r="576" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18171,7 +18213,7 @@
       <c r="AA576" s="1"/>
       <c r="AB576" s="1"/>
     </row>
-    <row r="577" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18201,7 +18243,7 @@
       <c r="AA577" s="1"/>
       <c r="AB577" s="1"/>
     </row>
-    <row r="578" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -18231,7 +18273,7 @@
       <c r="AA578" s="1"/>
       <c r="AB578" s="1"/>
     </row>
-    <row r="579" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -18261,7 +18303,7 @@
       <c r="AA579" s="1"/>
       <c r="AB579" s="1"/>
     </row>
-    <row r="580" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -18291,7 +18333,7 @@
       <c r="AA580" s="1"/>
       <c r="AB580" s="1"/>
     </row>
-    <row r="581" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -18321,7 +18363,7 @@
       <c r="AA581" s="1"/>
       <c r="AB581" s="1"/>
     </row>
-    <row r="582" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -18351,7 +18393,7 @@
       <c r="AA582" s="1"/>
       <c r="AB582" s="1"/>
     </row>
-    <row r="583" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -18381,7 +18423,7 @@
       <c r="AA583" s="1"/>
       <c r="AB583" s="1"/>
     </row>
-    <row r="584" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -18411,7 +18453,7 @@
       <c r="AA584" s="1"/>
       <c r="AB584" s="1"/>
     </row>
-    <row r="585" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -18441,7 +18483,7 @@
       <c r="AA585" s="1"/>
       <c r="AB585" s="1"/>
     </row>
-    <row r="586" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -18471,7 +18513,7 @@
       <c r="AA586" s="1"/>
       <c r="AB586" s="1"/>
     </row>
-    <row r="587" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -18501,7 +18543,7 @@
       <c r="AA587" s="1"/>
       <c r="AB587" s="1"/>
     </row>
-    <row r="588" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -18531,7 +18573,7 @@
       <c r="AA588" s="1"/>
       <c r="AB588" s="1"/>
     </row>
-    <row r="589" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -18561,7 +18603,7 @@
       <c r="AA589" s="1"/>
       <c r="AB589" s="1"/>
     </row>
-    <row r="590" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -18591,7 +18633,7 @@
       <c r="AA590" s="1"/>
       <c r="AB590" s="1"/>
     </row>
-    <row r="591" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -18621,7 +18663,7 @@
       <c r="AA591" s="1"/>
       <c r="AB591" s="1"/>
     </row>
-    <row r="592" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -18651,7 +18693,7 @@
       <c r="AA592" s="1"/>
       <c r="AB592" s="1"/>
     </row>
-    <row r="593" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -18681,7 +18723,7 @@
       <c r="AA593" s="1"/>
       <c r="AB593" s="1"/>
     </row>
-    <row r="594" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -18711,7 +18753,7 @@
       <c r="AA594" s="1"/>
       <c r="AB594" s="1"/>
     </row>
-    <row r="595" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -18741,7 +18783,7 @@
       <c r="AA595" s="1"/>
       <c r="AB595" s="1"/>
     </row>
-    <row r="596" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -18771,7 +18813,7 @@
       <c r="AA596" s="1"/>
       <c r="AB596" s="1"/>
     </row>
-    <row r="597" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -18801,7 +18843,7 @@
       <c r="AA597" s="1"/>
       <c r="AB597" s="1"/>
     </row>
-    <row r="598" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -18831,7 +18873,7 @@
       <c r="AA598" s="1"/>
       <c r="AB598" s="1"/>
     </row>
-    <row r="599" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -18861,7 +18903,7 @@
       <c r="AA599" s="1"/>
       <c r="AB599" s="1"/>
     </row>
-    <row r="600" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -18891,7 +18933,7 @@
       <c r="AA600" s="1"/>
       <c r="AB600" s="1"/>
     </row>
-    <row r="601" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -18921,7 +18963,7 @@
       <c r="AA601" s="1"/>
       <c r="AB601" s="1"/>
     </row>
-    <row r="602" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -18951,7 +18993,7 @@
       <c r="AA602" s="1"/>
       <c r="AB602" s="1"/>
     </row>
-    <row r="603" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -18981,7 +19023,7 @@
       <c r="AA603" s="1"/>
       <c r="AB603" s="1"/>
     </row>
-    <row r="604" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19011,7 +19053,7 @@
       <c r="AA604" s="1"/>
       <c r="AB604" s="1"/>
     </row>
-    <row r="605" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19041,7 +19083,7 @@
       <c r="AA605" s="1"/>
       <c r="AB605" s="1"/>
     </row>
-    <row r="606" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19071,7 +19113,7 @@
       <c r="AA606" s="1"/>
       <c r="AB606" s="1"/>
     </row>
-    <row r="607" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19101,7 +19143,7 @@
       <c r="AA607" s="1"/>
       <c r="AB607" s="1"/>
     </row>
-    <row r="608" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19131,7 +19173,7 @@
       <c r="AA608" s="1"/>
       <c r="AB608" s="1"/>
     </row>
-    <row r="609" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -19161,7 +19203,7 @@
       <c r="AA609" s="1"/>
       <c r="AB609" s="1"/>
     </row>
-    <row r="610" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -19191,7 +19233,7 @@
       <c r="AA610" s="1"/>
       <c r="AB610" s="1"/>
     </row>
-    <row r="611" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -19221,7 +19263,7 @@
       <c r="AA611" s="1"/>
       <c r="AB611" s="1"/>
     </row>
-    <row r="612" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -19251,7 +19293,7 @@
       <c r="AA612" s="1"/>
       <c r="AB612" s="1"/>
     </row>
-    <row r="613" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -19281,7 +19323,7 @@
       <c r="AA613" s="1"/>
       <c r="AB613" s="1"/>
     </row>
-    <row r="614" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -19311,7 +19353,7 @@
       <c r="AA614" s="1"/>
       <c r="AB614" s="1"/>
     </row>
-    <row r="615" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -19341,7 +19383,7 @@
       <c r="AA615" s="1"/>
       <c r="AB615" s="1"/>
     </row>
-    <row r="616" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -19371,7 +19413,7 @@
       <c r="AA616" s="1"/>
       <c r="AB616" s="1"/>
     </row>
-    <row r="617" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -19401,7 +19443,7 @@
       <c r="AA617" s="1"/>
       <c r="AB617" s="1"/>
     </row>
-    <row r="618" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -19431,7 +19473,7 @@
       <c r="AA618" s="1"/>
       <c r="AB618" s="1"/>
     </row>
-    <row r="619" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -19461,7 +19503,7 @@
       <c r="AA619" s="1"/>
       <c r="AB619" s="1"/>
     </row>
-    <row r="620" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -19491,7 +19533,7 @@
       <c r="AA620" s="1"/>
       <c r="AB620" s="1"/>
     </row>
-    <row r="621" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -19521,7 +19563,7 @@
       <c r="AA621" s="1"/>
       <c r="AB621" s="1"/>
     </row>
-    <row r="622" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -19551,7 +19593,7 @@
       <c r="AA622" s="1"/>
       <c r="AB622" s="1"/>
     </row>
-    <row r="623" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -19581,7 +19623,7 @@
       <c r="AA623" s="1"/>
       <c r="AB623" s="1"/>
     </row>
-    <row r="624" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -19611,7 +19653,7 @@
       <c r="AA624" s="1"/>
       <c r="AB624" s="1"/>
     </row>
-    <row r="625" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -19641,7 +19683,7 @@
       <c r="AA625" s="1"/>
       <c r="AB625" s="1"/>
     </row>
-    <row r="626" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -19671,7 +19713,7 @@
       <c r="AA626" s="1"/>
       <c r="AB626" s="1"/>
     </row>
-    <row r="627" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -19701,7 +19743,7 @@
       <c r="AA627" s="1"/>
       <c r="AB627" s="1"/>
     </row>
-    <row r="628" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -19731,7 +19773,7 @@
       <c r="AA628" s="1"/>
       <c r="AB628" s="1"/>
     </row>
-    <row r="629" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -19761,7 +19803,7 @@
       <c r="AA629" s="1"/>
       <c r="AB629" s="1"/>
     </row>
-    <row r="630" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -19791,7 +19833,7 @@
       <c r="AA630" s="1"/>
       <c r="AB630" s="1"/>
     </row>
-    <row r="631" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -19821,7 +19863,7 @@
       <c r="AA631" s="1"/>
       <c r="AB631" s="1"/>
     </row>
-    <row r="632" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -19851,7 +19893,7 @@
       <c r="AA632" s="1"/>
       <c r="AB632" s="1"/>
     </row>
-    <row r="633" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -19881,7 +19923,7 @@
       <c r="AA633" s="1"/>
       <c r="AB633" s="1"/>
     </row>
-    <row r="634" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -19911,7 +19953,7 @@
       <c r="AA634" s="1"/>
       <c r="AB634" s="1"/>
     </row>
-    <row r="635" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -19941,7 +19983,7 @@
       <c r="AA635" s="1"/>
       <c r="AB635" s="1"/>
     </row>
-    <row r="636" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -19971,7 +20013,7 @@
       <c r="AA636" s="1"/>
       <c r="AB636" s="1"/>
     </row>
-    <row r="637" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20001,7 +20043,7 @@
       <c r="AA637" s="1"/>
       <c r="AB637" s="1"/>
     </row>
-    <row r="638" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20031,7 +20073,7 @@
       <c r="AA638" s="1"/>
       <c r="AB638" s="1"/>
     </row>
-    <row r="639" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20061,7 +20103,7 @@
       <c r="AA639" s="1"/>
       <c r="AB639" s="1"/>
     </row>
-    <row r="640" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20091,7 +20133,7 @@
       <c r="AA640" s="1"/>
       <c r="AB640" s="1"/>
     </row>
-    <row r="641" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -20121,7 +20163,7 @@
       <c r="AA641" s="1"/>
       <c r="AB641" s="1"/>
     </row>
-    <row r="642" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -20151,7 +20193,7 @@
       <c r="AA642" s="1"/>
       <c r="AB642" s="1"/>
     </row>
-    <row r="643" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -20181,7 +20223,7 @@
       <c r="AA643" s="1"/>
       <c r="AB643" s="1"/>
     </row>
-    <row r="644" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -20211,7 +20253,7 @@
       <c r="AA644" s="1"/>
       <c r="AB644" s="1"/>
     </row>
-    <row r="645" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -20241,7 +20283,7 @@
       <c r="AA645" s="1"/>
       <c r="AB645" s="1"/>
     </row>
-    <row r="646" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -20271,7 +20313,7 @@
       <c r="AA646" s="1"/>
       <c r="AB646" s="1"/>
     </row>
-    <row r="647" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -20301,7 +20343,7 @@
       <c r="AA647" s="1"/>
       <c r="AB647" s="1"/>
     </row>
-    <row r="648" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -20331,7 +20373,7 @@
       <c r="AA648" s="1"/>
       <c r="AB648" s="1"/>
     </row>
-    <row r="649" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -20361,7 +20403,7 @@
       <c r="AA649" s="1"/>
       <c r="AB649" s="1"/>
     </row>
-    <row r="650" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -20391,7 +20433,7 @@
       <c r="AA650" s="1"/>
       <c r="AB650" s="1"/>
     </row>
-    <row r="651" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -20421,7 +20463,7 @@
       <c r="AA651" s="1"/>
       <c r="AB651" s="1"/>
     </row>
-    <row r="652" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -20451,7 +20493,7 @@
       <c r="AA652" s="1"/>
       <c r="AB652" s="1"/>
     </row>
-    <row r="653" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -20481,7 +20523,7 @@
       <c r="AA653" s="1"/>
       <c r="AB653" s="1"/>
     </row>
-    <row r="654" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -20511,7 +20553,7 @@
       <c r="AA654" s="1"/>
       <c r="AB654" s="1"/>
     </row>
-    <row r="655" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -20541,7 +20583,7 @@
       <c r="AA655" s="1"/>
       <c r="AB655" s="1"/>
     </row>
-    <row r="656" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -20571,7 +20613,7 @@
       <c r="AA656" s="1"/>
       <c r="AB656" s="1"/>
     </row>
-    <row r="657" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -20601,7 +20643,7 @@
       <c r="AA657" s="1"/>
       <c r="AB657" s="1"/>
     </row>
-    <row r="658" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -20631,7 +20673,7 @@
       <c r="AA658" s="1"/>
       <c r="AB658" s="1"/>
     </row>
-    <row r="659" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -20661,7 +20703,7 @@
       <c r="AA659" s="1"/>
       <c r="AB659" s="1"/>
     </row>
-    <row r="660" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -20691,7 +20733,7 @@
       <c r="AA660" s="1"/>
       <c r="AB660" s="1"/>
     </row>
-    <row r="661" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -20721,7 +20763,7 @@
       <c r="AA661" s="1"/>
       <c r="AB661" s="1"/>
     </row>
-    <row r="662" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -20751,7 +20793,7 @@
       <c r="AA662" s="1"/>
       <c r="AB662" s="1"/>
     </row>
-    <row r="663" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -20781,7 +20823,7 @@
       <c r="AA663" s="1"/>
       <c r="AB663" s="1"/>
     </row>
-    <row r="664" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -20811,7 +20853,7 @@
       <c r="AA664" s="1"/>
       <c r="AB664" s="1"/>
     </row>
-    <row r="665" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -20841,7 +20883,7 @@
       <c r="AA665" s="1"/>
       <c r="AB665" s="1"/>
     </row>
-    <row r="666" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -20871,7 +20913,7 @@
       <c r="AA666" s="1"/>
       <c r="AB666" s="1"/>
     </row>
-    <row r="667" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -20901,7 +20943,7 @@
       <c r="AA667" s="1"/>
       <c r="AB667" s="1"/>
     </row>
-    <row r="668" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -20931,7 +20973,7 @@
       <c r="AA668" s="1"/>
       <c r="AB668" s="1"/>
     </row>
-    <row r="669" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -20961,7 +21003,7 @@
       <c r="AA669" s="1"/>
       <c r="AB669" s="1"/>
     </row>
-    <row r="670" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -20991,7 +21033,7 @@
       <c r="AA670" s="1"/>
       <c r="AB670" s="1"/>
     </row>
-    <row r="671" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21021,7 +21063,7 @@
       <c r="AA671" s="1"/>
       <c r="AB671" s="1"/>
     </row>
-    <row r="672" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -21051,7 +21093,7 @@
       <c r="AA672" s="1"/>
       <c r="AB672" s="1"/>
     </row>
-    <row r="673" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -21081,7 +21123,7 @@
       <c r="AA673" s="1"/>
       <c r="AB673" s="1"/>
     </row>
-    <row r="674" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -21111,7 +21153,7 @@
       <c r="AA674" s="1"/>
       <c r="AB674" s="1"/>
     </row>
-    <row r="675" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -21141,7 +21183,7 @@
       <c r="AA675" s="1"/>
       <c r="AB675" s="1"/>
     </row>
-    <row r="676" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -21171,7 +21213,7 @@
       <c r="AA676" s="1"/>
       <c r="AB676" s="1"/>
     </row>
-    <row r="677" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -21201,7 +21243,7 @@
       <c r="AA677" s="1"/>
       <c r="AB677" s="1"/>
     </row>
-    <row r="678" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -21231,7 +21273,7 @@
       <c r="AA678" s="1"/>
       <c r="AB678" s="1"/>
     </row>
-    <row r="679" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -21261,7 +21303,7 @@
       <c r="AA679" s="1"/>
       <c r="AB679" s="1"/>
     </row>
-    <row r="680" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -21291,7 +21333,7 @@
       <c r="AA680" s="1"/>
       <c r="AB680" s="1"/>
     </row>
-    <row r="681" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -21321,7 +21363,7 @@
       <c r="AA681" s="1"/>
       <c r="AB681" s="1"/>
     </row>
-    <row r="682" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -21351,7 +21393,7 @@
       <c r="AA682" s="1"/>
       <c r="AB682" s="1"/>
     </row>
-    <row r="683" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -21381,7 +21423,7 @@
       <c r="AA683" s="1"/>
       <c r="AB683" s="1"/>
     </row>
-    <row r="684" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -21411,7 +21453,7 @@
       <c r="AA684" s="1"/>
       <c r="AB684" s="1"/>
     </row>
-    <row r="685" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -21441,7 +21483,7 @@
       <c r="AA685" s="1"/>
       <c r="AB685" s="1"/>
     </row>
-    <row r="686" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -21471,7 +21513,7 @@
       <c r="AA686" s="1"/>
       <c r="AB686" s="1"/>
     </row>
-    <row r="687" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -21501,7 +21543,7 @@
       <c r="AA687" s="1"/>
       <c r="AB687" s="1"/>
     </row>
-    <row r="688" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -21531,7 +21573,7 @@
       <c r="AA688" s="1"/>
       <c r="AB688" s="1"/>
     </row>
-    <row r="689" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -21561,7 +21603,7 @@
       <c r="AA689" s="1"/>
       <c r="AB689" s="1"/>
     </row>
-    <row r="690" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -21591,7 +21633,7 @@
       <c r="AA690" s="1"/>
       <c r="AB690" s="1"/>
     </row>
-    <row r="691" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -21621,7 +21663,7 @@
       <c r="AA691" s="1"/>
       <c r="AB691" s="1"/>
     </row>
-    <row r="692" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -21651,7 +21693,7 @@
       <c r="AA692" s="1"/>
       <c r="AB692" s="1"/>
     </row>
-    <row r="693" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -21681,7 +21723,7 @@
       <c r="AA693" s="1"/>
       <c r="AB693" s="1"/>
     </row>
-    <row r="694" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -21711,7 +21753,7 @@
       <c r="AA694" s="1"/>
       <c r="AB694" s="1"/>
     </row>
-    <row r="695" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -21741,7 +21783,7 @@
       <c r="AA695" s="1"/>
       <c r="AB695" s="1"/>
     </row>
-    <row r="696" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -21771,7 +21813,7 @@
       <c r="AA696" s="1"/>
       <c r="AB696" s="1"/>
     </row>
-    <row r="697" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -21801,7 +21843,7 @@
       <c r="AA697" s="1"/>
       <c r="AB697" s="1"/>
     </row>
-    <row r="698" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -21831,7 +21873,7 @@
       <c r="AA698" s="1"/>
       <c r="AB698" s="1"/>
     </row>
-    <row r="699" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -21861,7 +21903,7 @@
       <c r="AA699" s="1"/>
       <c r="AB699" s="1"/>
     </row>
-    <row r="700" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -21891,7 +21933,7 @@
       <c r="AA700" s="1"/>
       <c r="AB700" s="1"/>
     </row>
-    <row r="701" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -21921,7 +21963,7 @@
       <c r="AA701" s="1"/>
       <c r="AB701" s="1"/>
     </row>
-    <row r="702" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -21951,7 +21993,7 @@
       <c r="AA702" s="1"/>
       <c r="AB702" s="1"/>
     </row>
-    <row r="703" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -21981,7 +22023,7 @@
       <c r="AA703" s="1"/>
       <c r="AB703" s="1"/>
     </row>
-    <row r="704" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -22011,7 +22053,7 @@
       <c r="AA704" s="1"/>
       <c r="AB704" s="1"/>
     </row>
-    <row r="705" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -22041,7 +22083,7 @@
       <c r="AA705" s="1"/>
       <c r="AB705" s="1"/>
     </row>
-    <row r="706" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -22071,7 +22113,7 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
-    <row r="707" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -22101,7 +22143,7 @@
       <c r="AA707" s="1"/>
       <c r="AB707" s="1"/>
     </row>
-    <row r="708" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -22131,7 +22173,7 @@
       <c r="AA708" s="1"/>
       <c r="AB708" s="1"/>
     </row>
-    <row r="709" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -22161,7 +22203,7 @@
       <c r="AA709" s="1"/>
       <c r="AB709" s="1"/>
     </row>
-    <row r="710" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -22191,7 +22233,7 @@
       <c r="AA710" s="1"/>
       <c r="AB710" s="1"/>
     </row>
-    <row r="711" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -22221,7 +22263,7 @@
       <c r="AA711" s="1"/>
       <c r="AB711" s="1"/>
     </row>
-    <row r="712" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -22251,7 +22293,7 @@
       <c r="AA712" s="1"/>
       <c r="AB712" s="1"/>
     </row>
-    <row r="713" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -22281,7 +22323,7 @@
       <c r="AA713" s="1"/>
       <c r="AB713" s="1"/>
     </row>
-    <row r="714" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -22311,7 +22353,7 @@
       <c r="AA714" s="1"/>
       <c r="AB714" s="1"/>
     </row>
-    <row r="715" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -22341,7 +22383,7 @@
       <c r="AA715" s="1"/>
       <c r="AB715" s="1"/>
     </row>
-    <row r="716" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -22371,7 +22413,7 @@
       <c r="AA716" s="1"/>
       <c r="AB716" s="1"/>
     </row>
-    <row r="717" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -22401,7 +22443,7 @@
       <c r="AA717" s="1"/>
       <c r="AB717" s="1"/>
     </row>
-    <row r="718" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -22431,7 +22473,7 @@
       <c r="AA718" s="1"/>
       <c r="AB718" s="1"/>
     </row>
-    <row r="719" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -22461,7 +22503,7 @@
       <c r="AA719" s="1"/>
       <c r="AB719" s="1"/>
     </row>
-    <row r="720" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -22491,7 +22533,7 @@
       <c r="AA720" s="1"/>
       <c r="AB720" s="1"/>
     </row>
-    <row r="721" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -22521,7 +22563,7 @@
       <c r="AA721" s="1"/>
       <c r="AB721" s="1"/>
     </row>
-    <row r="722" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -22551,7 +22593,7 @@
       <c r="AA722" s="1"/>
       <c r="AB722" s="1"/>
     </row>
-    <row r="723" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -22581,7 +22623,7 @@
       <c r="AA723" s="1"/>
       <c r="AB723" s="1"/>
     </row>
-    <row r="724" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -22611,7 +22653,7 @@
       <c r="AA724" s="1"/>
       <c r="AB724" s="1"/>
     </row>
-    <row r="725" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -22641,7 +22683,7 @@
       <c r="AA725" s="1"/>
       <c r="AB725" s="1"/>
     </row>
-    <row r="726" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -22671,7 +22713,7 @@
       <c r="AA726" s="1"/>
       <c r="AB726" s="1"/>
     </row>
-    <row r="727" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -22701,7 +22743,7 @@
       <c r="AA727" s="1"/>
       <c r="AB727" s="1"/>
     </row>
-    <row r="728" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -22731,7 +22773,7 @@
       <c r="AA728" s="1"/>
       <c r="AB728" s="1"/>
     </row>
-    <row r="729" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -22761,7 +22803,7 @@
       <c r="AA729" s="1"/>
       <c r="AB729" s="1"/>
     </row>
-    <row r="730" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -22791,7 +22833,7 @@
       <c r="AA730" s="1"/>
       <c r="AB730" s="1"/>
     </row>
-    <row r="731" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -22821,7 +22863,7 @@
       <c r="AA731" s="1"/>
       <c r="AB731" s="1"/>
     </row>
-    <row r="732" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -22851,7 +22893,7 @@
       <c r="AA732" s="1"/>
       <c r="AB732" s="1"/>
     </row>
-    <row r="733" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -22881,7 +22923,7 @@
       <c r="AA733" s="1"/>
       <c r="AB733" s="1"/>
     </row>
-    <row r="734" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -22911,7 +22953,7 @@
       <c r="AA734" s="1"/>
       <c r="AB734" s="1"/>
     </row>
-    <row r="735" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -22941,7 +22983,7 @@
       <c r="AA735" s="1"/>
       <c r="AB735" s="1"/>
     </row>
-    <row r="736" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -22971,7 +23013,7 @@
       <c r="AA736" s="1"/>
       <c r="AB736" s="1"/>
     </row>
-    <row r="737" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -23001,7 +23043,7 @@
       <c r="AA737" s="1"/>
       <c r="AB737" s="1"/>
     </row>
-    <row r="738" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -23031,7 +23073,7 @@
       <c r="AA738" s="1"/>
       <c r="AB738" s="1"/>
     </row>
-    <row r="739" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -23061,7 +23103,7 @@
       <c r="AA739" s="1"/>
       <c r="AB739" s="1"/>
     </row>
-    <row r="740" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -23091,7 +23133,7 @@
       <c r="AA740" s="1"/>
       <c r="AB740" s="1"/>
     </row>
-    <row r="741" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -23121,7 +23163,7 @@
       <c r="AA741" s="1"/>
       <c r="AB741" s="1"/>
     </row>
-    <row r="742" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -23151,7 +23193,7 @@
       <c r="AA742" s="1"/>
       <c r="AB742" s="1"/>
     </row>
-    <row r="743" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -23181,7 +23223,7 @@
       <c r="AA743" s="1"/>
       <c r="AB743" s="1"/>
     </row>
-    <row r="744" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -23211,7 +23253,7 @@
       <c r="AA744" s="1"/>
       <c r="AB744" s="1"/>
     </row>
-    <row r="745" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -23241,7 +23283,7 @@
       <c r="AA745" s="1"/>
       <c r="AB745" s="1"/>
     </row>
-    <row r="746" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -23271,7 +23313,7 @@
       <c r="AA746" s="1"/>
       <c r="AB746" s="1"/>
     </row>
-    <row r="747" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -23301,7 +23343,7 @@
       <c r="AA747" s="1"/>
       <c r="AB747" s="1"/>
     </row>
-    <row r="748" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -23331,7 +23373,7 @@
       <c r="AA748" s="1"/>
       <c r="AB748" s="1"/>
     </row>
-    <row r="749" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -23361,7 +23403,7 @@
       <c r="AA749" s="1"/>
       <c r="AB749" s="1"/>
     </row>
-    <row r="750" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -23391,7 +23433,7 @@
       <c r="AA750" s="1"/>
       <c r="AB750" s="1"/>
     </row>
-    <row r="751" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -23421,7 +23463,7 @@
       <c r="AA751" s="1"/>
       <c r="AB751" s="1"/>
     </row>
-    <row r="752" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -23451,7 +23493,7 @@
       <c r="AA752" s="1"/>
       <c r="AB752" s="1"/>
     </row>
-    <row r="753" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -23481,7 +23523,7 @@
       <c r="AA753" s="1"/>
       <c r="AB753" s="1"/>
     </row>
-    <row r="754" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -23511,7 +23553,7 @@
       <c r="AA754" s="1"/>
       <c r="AB754" s="1"/>
     </row>
-    <row r="755" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -23541,7 +23583,7 @@
       <c r="AA755" s="1"/>
       <c r="AB755" s="1"/>
     </row>
-    <row r="756" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -23571,7 +23613,7 @@
       <c r="AA756" s="1"/>
       <c r="AB756" s="1"/>
     </row>
-    <row r="757" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -23601,7 +23643,7 @@
       <c r="AA757" s="1"/>
       <c r="AB757" s="1"/>
     </row>
-    <row r="758" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -23631,7 +23673,7 @@
       <c r="AA758" s="1"/>
       <c r="AB758" s="1"/>
     </row>
-    <row r="759" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -23661,7 +23703,7 @@
       <c r="AA759" s="1"/>
       <c r="AB759" s="1"/>
     </row>
-    <row r="760" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -23691,7 +23733,7 @@
       <c r="AA760" s="1"/>
       <c r="AB760" s="1"/>
     </row>
-    <row r="761" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -23721,7 +23763,7 @@
       <c r="AA761" s="1"/>
       <c r="AB761" s="1"/>
     </row>
-    <row r="762" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -23751,7 +23793,7 @@
       <c r="AA762" s="1"/>
       <c r="AB762" s="1"/>
     </row>
-    <row r="763" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -23781,7 +23823,7 @@
       <c r="AA763" s="1"/>
       <c r="AB763" s="1"/>
     </row>
-    <row r="764" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -23811,7 +23853,7 @@
       <c r="AA764" s="1"/>
       <c r="AB764" s="1"/>
     </row>
-    <row r="765" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -23841,7 +23883,7 @@
       <c r="AA765" s="1"/>
       <c r="AB765" s="1"/>
     </row>
-    <row r="766" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -23871,7 +23913,7 @@
       <c r="AA766" s="1"/>
       <c r="AB766" s="1"/>
     </row>
-    <row r="767" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -23901,7 +23943,7 @@
       <c r="AA767" s="1"/>
       <c r="AB767" s="1"/>
     </row>
-    <row r="768" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -23931,7 +23973,7 @@
       <c r="AA768" s="1"/>
       <c r="AB768" s="1"/>
     </row>
-    <row r="769" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -23961,7 +24003,7 @@
       <c r="AA769" s="1"/>
       <c r="AB769" s="1"/>
     </row>
-    <row r="770" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -23991,7 +24033,7 @@
       <c r="AA770" s="1"/>
       <c r="AB770" s="1"/>
     </row>
-    <row r="771" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -24021,7 +24063,7 @@
       <c r="AA771" s="1"/>
       <c r="AB771" s="1"/>
     </row>
-    <row r="772" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -24051,7 +24093,7 @@
       <c r="AA772" s="1"/>
       <c r="AB772" s="1"/>
     </row>
-    <row r="773" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -24081,7 +24123,7 @@
       <c r="AA773" s="1"/>
       <c r="AB773" s="1"/>
     </row>
-    <row r="774" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -24111,7 +24153,7 @@
       <c r="AA774" s="1"/>
       <c r="AB774" s="1"/>
     </row>
-    <row r="775" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -24141,7 +24183,7 @@
       <c r="AA775" s="1"/>
       <c r="AB775" s="1"/>
     </row>
-    <row r="776" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -24171,7 +24213,7 @@
       <c r="AA776" s="1"/>
       <c r="AB776" s="1"/>
     </row>
-    <row r="777" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -24201,7 +24243,7 @@
       <c r="AA777" s="1"/>
       <c r="AB777" s="1"/>
     </row>
-    <row r="778" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -24231,7 +24273,7 @@
       <c r="AA778" s="1"/>
       <c r="AB778" s="1"/>
     </row>
-    <row r="779" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -24261,7 +24303,7 @@
       <c r="AA779" s="1"/>
       <c r="AB779" s="1"/>
     </row>
-    <row r="780" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -24291,7 +24333,7 @@
       <c r="AA780" s="1"/>
       <c r="AB780" s="1"/>
     </row>
-    <row r="781" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -24321,7 +24363,7 @@
       <c r="AA781" s="1"/>
       <c r="AB781" s="1"/>
     </row>
-    <row r="782" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -24351,7 +24393,7 @@
       <c r="AA782" s="1"/>
       <c r="AB782" s="1"/>
     </row>
-    <row r="783" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -24381,7 +24423,7 @@
       <c r="AA783" s="1"/>
       <c r="AB783" s="1"/>
     </row>
-    <row r="784" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -24411,7 +24453,7 @@
       <c r="AA784" s="1"/>
       <c r="AB784" s="1"/>
     </row>
-    <row r="785" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -24441,7 +24483,7 @@
       <c r="AA785" s="1"/>
       <c r="AB785" s="1"/>
     </row>
-    <row r="786" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -24471,7 +24513,7 @@
       <c r="AA786" s="1"/>
       <c r="AB786" s="1"/>
     </row>
-    <row r="787" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -24501,7 +24543,7 @@
       <c r="AA787" s="1"/>
       <c r="AB787" s="1"/>
     </row>
-    <row r="788" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -24531,7 +24573,7 @@
       <c r="AA788" s="1"/>
       <c r="AB788" s="1"/>
     </row>
-    <row r="789" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -24561,7 +24603,7 @@
       <c r="AA789" s="1"/>
       <c r="AB789" s="1"/>
     </row>
-    <row r="790" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -24591,7 +24633,7 @@
       <c r="AA790" s="1"/>
       <c r="AB790" s="1"/>
     </row>
-    <row r="791" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -24621,7 +24663,7 @@
       <c r="AA791" s="1"/>
       <c r="AB791" s="1"/>
     </row>
-    <row r="792" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -24651,7 +24693,7 @@
       <c r="AA792" s="1"/>
       <c r="AB792" s="1"/>
     </row>
-    <row r="793" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -24681,7 +24723,7 @@
       <c r="AA793" s="1"/>
       <c r="AB793" s="1"/>
     </row>
-    <row r="794" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -24711,7 +24753,7 @@
       <c r="AA794" s="1"/>
       <c r="AB794" s="1"/>
     </row>
-    <row r="795" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -24741,7 +24783,7 @@
       <c r="AA795" s="1"/>
       <c r="AB795" s="1"/>
     </row>
-    <row r="796" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -24771,7 +24813,7 @@
       <c r="AA796" s="1"/>
       <c r="AB796" s="1"/>
     </row>
-    <row r="797" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -24801,7 +24843,7 @@
       <c r="AA797" s="1"/>
       <c r="AB797" s="1"/>
     </row>
-    <row r="798" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -24831,7 +24873,7 @@
       <c r="AA798" s="1"/>
       <c r="AB798" s="1"/>
     </row>
-    <row r="799" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -24861,7 +24903,7 @@
       <c r="AA799" s="1"/>
       <c r="AB799" s="1"/>
     </row>
-    <row r="800" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -24891,7 +24933,7 @@
       <c r="AA800" s="1"/>
       <c r="AB800" s="1"/>
     </row>
-    <row r="801" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -24921,7 +24963,7 @@
       <c r="AA801" s="1"/>
       <c r="AB801" s="1"/>
     </row>
-    <row r="802" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -24951,7 +24993,7 @@
       <c r="AA802" s="1"/>
       <c r="AB802" s="1"/>
     </row>
-    <row r="803" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -24981,7 +25023,7 @@
       <c r="AA803" s="1"/>
       <c r="AB803" s="1"/>
     </row>
-    <row r="804" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -25011,7 +25053,7 @@
       <c r="AA804" s="1"/>
       <c r="AB804" s="1"/>
     </row>
-    <row r="805" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -25041,7 +25083,7 @@
       <c r="AA805" s="1"/>
       <c r="AB805" s="1"/>
     </row>
-    <row r="806" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -25071,7 +25113,7 @@
       <c r="AA806" s="1"/>
       <c r="AB806" s="1"/>
     </row>
-    <row r="807" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -25101,7 +25143,7 @@
       <c r="AA807" s="1"/>
       <c r="AB807" s="1"/>
     </row>
-    <row r="808" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -25131,7 +25173,7 @@
       <c r="AA808" s="1"/>
       <c r="AB808" s="1"/>
     </row>
-    <row r="809" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -25161,7 +25203,7 @@
       <c r="AA809" s="1"/>
       <c r="AB809" s="1"/>
     </row>
-    <row r="810" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -25191,7 +25233,7 @@
       <c r="AA810" s="1"/>
       <c r="AB810" s="1"/>
     </row>
-    <row r="811" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -25221,7 +25263,7 @@
       <c r="AA811" s="1"/>
       <c r="AB811" s="1"/>
     </row>
-    <row r="812" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -25251,7 +25293,7 @@
       <c r="AA812" s="1"/>
       <c r="AB812" s="1"/>
     </row>
-    <row r="813" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -25281,7 +25323,7 @@
       <c r="AA813" s="1"/>
       <c r="AB813" s="1"/>
     </row>
-    <row r="814" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -25311,7 +25353,7 @@
       <c r="AA814" s="1"/>
       <c r="AB814" s="1"/>
     </row>
-    <row r="815" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -25341,7 +25383,7 @@
       <c r="AA815" s="1"/>
       <c r="AB815" s="1"/>
     </row>
-    <row r="816" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -25371,7 +25413,7 @@
       <c r="AA816" s="1"/>
       <c r="AB816" s="1"/>
     </row>
-    <row r="817" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -25401,7 +25443,7 @@
       <c r="AA817" s="1"/>
       <c r="AB817" s="1"/>
     </row>
-    <row r="818" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -25431,7 +25473,7 @@
       <c r="AA818" s="1"/>
       <c r="AB818" s="1"/>
     </row>
-    <row r="819" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -25461,7 +25503,7 @@
       <c r="AA819" s="1"/>
       <c r="AB819" s="1"/>
     </row>
-    <row r="820" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -25491,7 +25533,7 @@
       <c r="AA820" s="1"/>
       <c r="AB820" s="1"/>
     </row>
-    <row r="821" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -25521,7 +25563,7 @@
       <c r="AA821" s="1"/>
       <c r="AB821" s="1"/>
     </row>
-    <row r="822" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -25551,7 +25593,7 @@
       <c r="AA822" s="1"/>
       <c r="AB822" s="1"/>
     </row>
-    <row r="823" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -25581,7 +25623,7 @@
       <c r="AA823" s="1"/>
       <c r="AB823" s="1"/>
     </row>
-    <row r="824" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -25611,7 +25653,7 @@
       <c r="AA824" s="1"/>
       <c r="AB824" s="1"/>
     </row>
-    <row r="825" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -25641,7 +25683,7 @@
       <c r="AA825" s="1"/>
       <c r="AB825" s="1"/>
     </row>
-    <row r="826" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -25671,7 +25713,7 @@
       <c r="AA826" s="1"/>
       <c r="AB826" s="1"/>
     </row>
-    <row r="827" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -25701,7 +25743,7 @@
       <c r="AA827" s="1"/>
       <c r="AB827" s="1"/>
     </row>
-    <row r="828" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -25731,7 +25773,7 @@
       <c r="AA828" s="1"/>
       <c r="AB828" s="1"/>
     </row>
-    <row r="829" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -25761,7 +25803,7 @@
       <c r="AA829" s="1"/>
       <c r="AB829" s="1"/>
     </row>
-    <row r="830" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -25791,7 +25833,7 @@
       <c r="AA830" s="1"/>
       <c r="AB830" s="1"/>
     </row>
-    <row r="831" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -25821,7 +25863,7 @@
       <c r="AA831" s="1"/>
       <c r="AB831" s="1"/>
     </row>
-    <row r="832" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -25851,7 +25893,7 @@
       <c r="AA832" s="1"/>
       <c r="AB832" s="1"/>
     </row>
-    <row r="833" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -25881,7 +25923,7 @@
       <c r="AA833" s="1"/>
       <c r="AB833" s="1"/>
     </row>
-    <row r="834" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -25911,7 +25953,7 @@
       <c r="AA834" s="1"/>
       <c r="AB834" s="1"/>
     </row>
-    <row r="835" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -25941,7 +25983,7 @@
       <c r="AA835" s="1"/>
       <c r="AB835" s="1"/>
     </row>
-    <row r="836" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -25971,7 +26013,7 @@
       <c r="AA836" s="1"/>
       <c r="AB836" s="1"/>
     </row>
-    <row r="837" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -26001,7 +26043,7 @@
       <c r="AA837" s="1"/>
       <c r="AB837" s="1"/>
     </row>
-    <row r="838" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -26031,7 +26073,7 @@
       <c r="AA838" s="1"/>
       <c r="AB838" s="1"/>
     </row>
-    <row r="839" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -26061,7 +26103,7 @@
       <c r="AA839" s="1"/>
       <c r="AB839" s="1"/>
     </row>
-    <row r="840" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -26091,7 +26133,7 @@
       <c r="AA840" s="1"/>
       <c r="AB840" s="1"/>
     </row>
-    <row r="841" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -26121,7 +26163,7 @@
       <c r="AA841" s="1"/>
       <c r="AB841" s="1"/>
     </row>
-    <row r="842" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -26151,7 +26193,7 @@
       <c r="AA842" s="1"/>
       <c r="AB842" s="1"/>
     </row>
-    <row r="843" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -26181,7 +26223,7 @@
       <c r="AA843" s="1"/>
       <c r="AB843" s="1"/>
     </row>
-    <row r="844" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -26211,7 +26253,7 @@
       <c r="AA844" s="1"/>
       <c r="AB844" s="1"/>
     </row>
-    <row r="845" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -26241,7 +26283,7 @@
       <c r="AA845" s="1"/>
       <c r="AB845" s="1"/>
     </row>
-    <row r="846" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -26271,7 +26313,7 @@
       <c r="AA846" s="1"/>
       <c r="AB846" s="1"/>
     </row>
-    <row r="847" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -26301,7 +26343,7 @@
       <c r="AA847" s="1"/>
       <c r="AB847" s="1"/>
     </row>
-    <row r="848" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -26331,7 +26373,7 @@
       <c r="AA848" s="1"/>
       <c r="AB848" s="1"/>
     </row>
-    <row r="849" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -26361,7 +26403,7 @@
       <c r="AA849" s="1"/>
       <c r="AB849" s="1"/>
     </row>
-    <row r="850" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -26391,7 +26433,7 @@
       <c r="AA850" s="1"/>
       <c r="AB850" s="1"/>
     </row>
-    <row r="851" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -26421,7 +26463,7 @@
       <c r="AA851" s="1"/>
       <c r="AB851" s="1"/>
     </row>
-    <row r="852" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -26451,7 +26493,7 @@
       <c r="AA852" s="1"/>
       <c r="AB852" s="1"/>
     </row>
-    <row r="853" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -26481,7 +26523,7 @@
       <c r="AA853" s="1"/>
       <c r="AB853" s="1"/>
     </row>
-    <row r="854" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -26511,7 +26553,7 @@
       <c r="AA854" s="1"/>
       <c r="AB854" s="1"/>
     </row>
-    <row r="855" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -26541,7 +26583,7 @@
       <c r="AA855" s="1"/>
       <c r="AB855" s="1"/>
     </row>
-    <row r="856" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -26571,7 +26613,7 @@
       <c r="AA856" s="1"/>
       <c r="AB856" s="1"/>
     </row>
-    <row r="857" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -26601,7 +26643,7 @@
       <c r="AA857" s="1"/>
       <c r="AB857" s="1"/>
     </row>
-    <row r="858" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -26631,7 +26673,7 @@
       <c r="AA858" s="1"/>
       <c r="AB858" s="1"/>
     </row>
-    <row r="859" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -26661,7 +26703,7 @@
       <c r="AA859" s="1"/>
       <c r="AB859" s="1"/>
     </row>
-    <row r="860" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -26691,7 +26733,7 @@
       <c r="AA860" s="1"/>
       <c r="AB860" s="1"/>
     </row>
-    <row r="861" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -26721,7 +26763,7 @@
       <c r="AA861" s="1"/>
       <c r="AB861" s="1"/>
     </row>
-    <row r="862" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -26751,7 +26793,7 @@
       <c r="AA862" s="1"/>
       <c r="AB862" s="1"/>
     </row>
-    <row r="863" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -26781,7 +26823,7 @@
       <c r="AA863" s="1"/>
       <c r="AB863" s="1"/>
     </row>
-    <row r="864" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -26811,7 +26853,7 @@
       <c r="AA864" s="1"/>
       <c r="AB864" s="1"/>
     </row>
-    <row r="865" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -26841,7 +26883,7 @@
       <c r="AA865" s="1"/>
       <c r="AB865" s="1"/>
     </row>
-    <row r="866" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -26871,7 +26913,7 @@
       <c r="AA866" s="1"/>
       <c r="AB866" s="1"/>
     </row>
-    <row r="867" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -26901,7 +26943,7 @@
       <c r="AA867" s="1"/>
       <c r="AB867" s="1"/>
     </row>
-    <row r="868" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -26931,7 +26973,7 @@
       <c r="AA868" s="1"/>
       <c r="AB868" s="1"/>
     </row>
-    <row r="869" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -26961,7 +27003,7 @@
       <c r="AA869" s="1"/>
       <c r="AB869" s="1"/>
     </row>
-    <row r="870" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -26991,7 +27033,7 @@
       <c r="AA870" s="1"/>
       <c r="AB870" s="1"/>
     </row>
-    <row r="871" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -27021,7 +27063,7 @@
       <c r="AA871" s="1"/>
       <c r="AB871" s="1"/>
     </row>
-    <row r="872" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -27051,7 +27093,7 @@
       <c r="AA872" s="1"/>
       <c r="AB872" s="1"/>
     </row>
-    <row r="873" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -27081,7 +27123,7 @@
       <c r="AA873" s="1"/>
       <c r="AB873" s="1"/>
     </row>
-    <row r="874" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -27111,7 +27153,7 @@
       <c r="AA874" s="1"/>
       <c r="AB874" s="1"/>
     </row>
-    <row r="875" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -27141,7 +27183,7 @@
       <c r="AA875" s="1"/>
       <c r="AB875" s="1"/>
     </row>
-    <row r="876" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -27171,7 +27213,7 @@
       <c r="AA876" s="1"/>
       <c r="AB876" s="1"/>
     </row>
-    <row r="877" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -27201,7 +27243,7 @@
       <c r="AA877" s="1"/>
       <c r="AB877" s="1"/>
     </row>
-    <row r="878" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -27231,7 +27273,7 @@
       <c r="AA878" s="1"/>
       <c r="AB878" s="1"/>
     </row>
-    <row r="879" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -27261,7 +27303,7 @@
       <c r="AA879" s="1"/>
       <c r="AB879" s="1"/>
     </row>
-    <row r="880" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -27291,7 +27333,7 @@
       <c r="AA880" s="1"/>
       <c r="AB880" s="1"/>
     </row>
-    <row r="881" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -27321,7 +27363,7 @@
       <c r="AA881" s="1"/>
       <c r="AB881" s="1"/>
     </row>
-    <row r="882" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -27351,7 +27393,7 @@
       <c r="AA882" s="1"/>
       <c r="AB882" s="1"/>
     </row>
-    <row r="883" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -27381,7 +27423,7 @@
       <c r="AA883" s="1"/>
       <c r="AB883" s="1"/>
     </row>
-    <row r="884" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -27411,7 +27453,7 @@
       <c r="AA884" s="1"/>
       <c r="AB884" s="1"/>
     </row>
-    <row r="885" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -27441,7 +27483,7 @@
       <c r="AA885" s="1"/>
       <c r="AB885" s="1"/>
     </row>
-    <row r="886" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -27471,7 +27513,7 @@
       <c r="AA886" s="1"/>
       <c r="AB886" s="1"/>
     </row>
-    <row r="887" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -27501,7 +27543,7 @@
       <c r="AA887" s="1"/>
       <c r="AB887" s="1"/>
     </row>
-    <row r="888" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -27531,7 +27573,7 @@
       <c r="AA888" s="1"/>
       <c r="AB888" s="1"/>
     </row>
-    <row r="889" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -27561,7 +27603,7 @@
       <c r="AA889" s="1"/>
       <c r="AB889" s="1"/>
     </row>
-    <row r="890" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -27591,7 +27633,7 @@
       <c r="AA890" s="1"/>
       <c r="AB890" s="1"/>
     </row>
-    <row r="891" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -27621,7 +27663,7 @@
       <c r="AA891" s="1"/>
       <c r="AB891" s="1"/>
     </row>
-    <row r="892" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -27651,7 +27693,7 @@
       <c r="AA892" s="1"/>
       <c r="AB892" s="1"/>
     </row>
-    <row r="893" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -27681,7 +27723,7 @@
       <c r="AA893" s="1"/>
       <c r="AB893" s="1"/>
     </row>
-    <row r="894" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -27711,7 +27753,7 @@
       <c r="AA894" s="1"/>
       <c r="AB894" s="1"/>
     </row>
-    <row r="895" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -27741,7 +27783,7 @@
       <c r="AA895" s="1"/>
       <c r="AB895" s="1"/>
     </row>
-    <row r="896" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -27771,7 +27813,7 @@
       <c r="AA896" s="1"/>
       <c r="AB896" s="1"/>
     </row>
-    <row r="897" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -27801,7 +27843,7 @@
       <c r="AA897" s="1"/>
       <c r="AB897" s="1"/>
     </row>
-    <row r="898" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -27831,7 +27873,7 @@
       <c r="AA898" s="1"/>
       <c r="AB898" s="1"/>
     </row>
-    <row r="899" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -27861,7 +27903,7 @@
       <c r="AA899" s="1"/>
       <c r="AB899" s="1"/>
     </row>
-    <row r="900" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -27891,7 +27933,7 @@
       <c r="AA900" s="1"/>
       <c r="AB900" s="1"/>
     </row>
-    <row r="901" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -27921,7 +27963,7 @@
       <c r="AA901" s="1"/>
       <c r="AB901" s="1"/>
     </row>
-    <row r="902" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -27951,7 +27993,7 @@
       <c r="AA902" s="1"/>
       <c r="AB902" s="1"/>
     </row>
-    <row r="903" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -27981,7 +28023,7 @@
       <c r="AA903" s="1"/>
       <c r="AB903" s="1"/>
     </row>
-    <row r="904" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -28011,7 +28053,7 @@
       <c r="AA904" s="1"/>
       <c r="AB904" s="1"/>
     </row>
-    <row r="905" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -28041,7 +28083,7 @@
       <c r="AA905" s="1"/>
       <c r="AB905" s="1"/>
     </row>
-    <row r="906" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -28071,7 +28113,7 @@
       <c r="AA906" s="1"/>
       <c r="AB906" s="1"/>
     </row>
-    <row r="907" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -28101,7 +28143,7 @@
       <c r="AA907" s="1"/>
       <c r="AB907" s="1"/>
     </row>
-    <row r="908" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -28131,7 +28173,7 @@
       <c r="AA908" s="1"/>
       <c r="AB908" s="1"/>
     </row>
-    <row r="909" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -28161,7 +28203,7 @@
       <c r="AA909" s="1"/>
       <c r="AB909" s="1"/>
     </row>
-    <row r="910" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -28191,7 +28233,7 @@
       <c r="AA910" s="1"/>
       <c r="AB910" s="1"/>
     </row>
-    <row r="911" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -28221,7 +28263,7 @@
       <c r="AA911" s="1"/>
       <c r="AB911" s="1"/>
     </row>
-    <row r="912" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -28251,7 +28293,7 @@
       <c r="AA912" s="1"/>
       <c r="AB912" s="1"/>
     </row>
-    <row r="913" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -28281,7 +28323,7 @@
       <c r="AA913" s="1"/>
       <c r="AB913" s="1"/>
     </row>
-    <row r="914" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -28311,7 +28353,7 @@
       <c r="AA914" s="1"/>
       <c r="AB914" s="1"/>
     </row>
-    <row r="915" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -28341,7 +28383,7 @@
       <c r="AA915" s="1"/>
       <c r="AB915" s="1"/>
     </row>
-    <row r="916" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -28371,7 +28413,7 @@
       <c r="AA916" s="1"/>
       <c r="AB916" s="1"/>
     </row>
-    <row r="917" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -28401,7 +28443,7 @@
       <c r="AA917" s="1"/>
       <c r="AB917" s="1"/>
     </row>
-    <row r="918" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -28431,7 +28473,7 @@
       <c r="AA918" s="1"/>
       <c r="AB918" s="1"/>
     </row>
-    <row r="919" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -28461,7 +28503,7 @@
       <c r="AA919" s="1"/>
       <c r="AB919" s="1"/>
     </row>
-    <row r="920" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -28491,7 +28533,7 @@
       <c r="AA920" s="1"/>
       <c r="AB920" s="1"/>
     </row>
-    <row r="921" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -28521,7 +28563,7 @@
       <c r="AA921" s="1"/>
       <c r="AB921" s="1"/>
     </row>
-    <row r="922" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -28551,7 +28593,7 @@
       <c r="AA922" s="1"/>
       <c r="AB922" s="1"/>
     </row>
-    <row r="923" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -28581,7 +28623,7 @@
       <c r="AA923" s="1"/>
       <c r="AB923" s="1"/>
     </row>
-    <row r="924" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -28611,7 +28653,7 @@
       <c r="AA924" s="1"/>
       <c r="AB924" s="1"/>
     </row>
-    <row r="925" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -28641,7 +28683,7 @@
       <c r="AA925" s="1"/>
       <c r="AB925" s="1"/>
     </row>
-    <row r="926" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -28671,7 +28713,7 @@
       <c r="AA926" s="1"/>
       <c r="AB926" s="1"/>
     </row>
-    <row r="927" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -28701,7 +28743,7 @@
       <c r="AA927" s="1"/>
       <c r="AB927" s="1"/>
     </row>
-    <row r="928" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -28731,7 +28773,7 @@
       <c r="AA928" s="1"/>
       <c r="AB928" s="1"/>
     </row>
-    <row r="929" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -28761,7 +28803,7 @@
       <c r="AA929" s="1"/>
       <c r="AB929" s="1"/>
     </row>
-    <row r="930" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -28791,7 +28833,7 @@
       <c r="AA930" s="1"/>
       <c r="AB930" s="1"/>
     </row>
-    <row r="931" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -28821,7 +28863,7 @@
       <c r="AA931" s="1"/>
       <c r="AB931" s="1"/>
     </row>
-    <row r="932" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -28851,7 +28893,7 @@
       <c r="AA932" s="1"/>
       <c r="AB932" s="1"/>
     </row>
-    <row r="933" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -28881,7 +28923,7 @@
       <c r="AA933" s="1"/>
       <c r="AB933" s="1"/>
     </row>
-    <row r="934" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -28911,7 +28953,7 @@
       <c r="AA934" s="1"/>
       <c r="AB934" s="1"/>
     </row>
-    <row r="935" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -28941,7 +28983,7 @@
       <c r="AA935" s="1"/>
       <c r="AB935" s="1"/>
     </row>
-    <row r="936" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -28971,7 +29013,7 @@
       <c r="AA936" s="1"/>
       <c r="AB936" s="1"/>
     </row>
-    <row r="937" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -29001,7 +29043,7 @@
       <c r="AA937" s="1"/>
       <c r="AB937" s="1"/>
     </row>
-    <row r="938" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -29031,7 +29073,7 @@
       <c r="AA938" s="1"/>
       <c r="AB938" s="1"/>
     </row>
-    <row r="939" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -29061,7 +29103,7 @@
       <c r="AA939" s="1"/>
       <c r="AB939" s="1"/>
     </row>
-    <row r="940" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -29091,7 +29133,7 @@
       <c r="AA940" s="1"/>
       <c r="AB940" s="1"/>
     </row>
-    <row r="941" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -29121,7 +29163,7 @@
       <c r="AA941" s="1"/>
       <c r="AB941" s="1"/>
     </row>
-    <row r="942" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -29151,7 +29193,7 @@
       <c r="AA942" s="1"/>
       <c r="AB942" s="1"/>
     </row>
-    <row r="943" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -29181,7 +29223,7 @@
       <c r="AA943" s="1"/>
       <c r="AB943" s="1"/>
     </row>
-    <row r="944" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -29211,7 +29253,7 @@
       <c r="AA944" s="1"/>
       <c r="AB944" s="1"/>
     </row>
-    <row r="945" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -29241,7 +29283,7 @@
       <c r="AA945" s="1"/>
       <c r="AB945" s="1"/>
     </row>
-    <row r="946" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -29271,7 +29313,7 @@
       <c r="AA946" s="1"/>
       <c r="AB946" s="1"/>
     </row>
-    <row r="947" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -29301,7 +29343,7 @@
       <c r="AA947" s="1"/>
       <c r="AB947" s="1"/>
     </row>
-    <row r="948" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -29331,7 +29373,7 @@
       <c r="AA948" s="1"/>
       <c r="AB948" s="1"/>
     </row>
-    <row r="949" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -29361,7 +29403,7 @@
       <c r="AA949" s="1"/>
       <c r="AB949" s="1"/>
     </row>
-    <row r="950" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -29391,7 +29433,7 @@
       <c r="AA950" s="1"/>
       <c r="AB950" s="1"/>
     </row>
-    <row r="951" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -29421,7 +29463,7 @@
       <c r="AA951" s="1"/>
       <c r="AB951" s="1"/>
     </row>
-    <row r="952" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -29451,7 +29493,7 @@
       <c r="AA952" s="1"/>
       <c r="AB952" s="1"/>
     </row>
-    <row r="953" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -29481,7 +29523,7 @@
       <c r="AA953" s="1"/>
       <c r="AB953" s="1"/>
     </row>
-    <row r="954" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -29511,7 +29553,7 @@
       <c r="AA954" s="1"/>
       <c r="AB954" s="1"/>
     </row>
-    <row r="955" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -29541,7 +29583,7 @@
       <c r="AA955" s="1"/>
       <c r="AB955" s="1"/>
     </row>
-    <row r="956" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -29571,7 +29613,7 @@
       <c r="AA956" s="1"/>
       <c r="AB956" s="1"/>
     </row>
-    <row r="957" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -29601,7 +29643,7 @@
       <c r="AA957" s="1"/>
       <c r="AB957" s="1"/>
     </row>
-    <row r="958" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -29631,7 +29673,7 @@
       <c r="AA958" s="1"/>
       <c r="AB958" s="1"/>
     </row>
-    <row r="959" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -29661,7 +29703,7 @@
       <c r="AA959" s="1"/>
       <c r="AB959" s="1"/>
     </row>
-    <row r="960" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -29691,7 +29733,7 @@
       <c r="AA960" s="1"/>
       <c r="AB960" s="1"/>
     </row>
-    <row r="961" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -29721,7 +29763,7 @@
       <c r="AA961" s="1"/>
       <c r="AB961" s="1"/>
     </row>
-    <row r="962" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -29751,7 +29793,7 @@
       <c r="AA962" s="1"/>
       <c r="AB962" s="1"/>
     </row>
-    <row r="963" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -29781,7 +29823,7 @@
       <c r="AA963" s="1"/>
       <c r="AB963" s="1"/>
     </row>
-    <row r="964" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -29811,7 +29853,7 @@
       <c r="AA964" s="1"/>
       <c r="AB964" s="1"/>
     </row>
-    <row r="965" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -29841,7 +29883,7 @@
       <c r="AA965" s="1"/>
       <c r="AB965" s="1"/>
     </row>
-    <row r="966" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -29871,7 +29913,7 @@
       <c r="AA966" s="1"/>
       <c r="AB966" s="1"/>
     </row>
-    <row r="967" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -29901,7 +29943,7 @@
       <c r="AA967" s="1"/>
       <c r="AB967" s="1"/>
     </row>
-    <row r="968" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -29931,7 +29973,7 @@
       <c r="AA968" s="1"/>
       <c r="AB968" s="1"/>
     </row>
-    <row r="969" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -29961,7 +30003,7 @@
       <c r="AA969" s="1"/>
       <c r="AB969" s="1"/>
     </row>
-    <row r="970" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -29991,7 +30033,7 @@
       <c r="AA970" s="1"/>
       <c r="AB970" s="1"/>
     </row>
-    <row r="971" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -30021,7 +30063,7 @@
       <c r="AA971" s="1"/>
       <c r="AB971" s="1"/>
     </row>
-    <row r="972" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -30051,7 +30093,7 @@
       <c r="AA972" s="1"/>
       <c r="AB972" s="1"/>
     </row>
-    <row r="973" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -30081,7 +30123,7 @@
       <c r="AA973" s="1"/>
       <c r="AB973" s="1"/>
     </row>
-    <row r="974" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -30111,7 +30153,7 @@
       <c r="AA974" s="1"/>
       <c r="AB974" s="1"/>
     </row>
-    <row r="975" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -30141,7 +30183,7 @@
       <c r="AA975" s="1"/>
       <c r="AB975" s="1"/>
     </row>
-    <row r="976" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -30171,7 +30213,7 @@
       <c r="AA976" s="1"/>
       <c r="AB976" s="1"/>
     </row>
-    <row r="977" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -30201,7 +30243,7 @@
       <c r="AA977" s="1"/>
       <c r="AB977" s="1"/>
     </row>
-    <row r="978" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -30231,7 +30273,7 @@
       <c r="AA978" s="1"/>
       <c r="AB978" s="1"/>
     </row>
-    <row r="979" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -30261,7 +30303,7 @@
       <c r="AA979" s="1"/>
       <c r="AB979" s="1"/>
     </row>
-    <row r="980" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -30291,7 +30333,7 @@
       <c r="AA980" s="1"/>
       <c r="AB980" s="1"/>
     </row>
-    <row r="981" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -30321,7 +30363,7 @@
       <c r="AA981" s="1"/>
       <c r="AB981" s="1"/>
     </row>
-    <row r="982" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -30351,7 +30393,7 @@
       <c r="AA982" s="1"/>
       <c r="AB982" s="1"/>
     </row>
-    <row r="983" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -30381,7 +30423,7 @@
       <c r="AA983" s="1"/>
       <c r="AB983" s="1"/>
     </row>
-    <row r="984" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -30411,7 +30453,7 @@
       <c r="AA984" s="1"/>
       <c r="AB984" s="1"/>
     </row>
-    <row r="985" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -30441,7 +30483,7 @@
       <c r="AA985" s="1"/>
       <c r="AB985" s="1"/>
     </row>
-    <row r="986" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -30471,7 +30513,7 @@
       <c r="AA986" s="1"/>
       <c r="AB986" s="1"/>
     </row>
-    <row r="987" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -30501,7 +30543,7 @@
       <c r="AA987" s="1"/>
       <c r="AB987" s="1"/>
     </row>
-    <row r="988" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -30531,7 +30573,7 @@
       <c r="AA988" s="1"/>
       <c r="AB988" s="1"/>
     </row>
-    <row r="989" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -30561,7 +30603,7 @@
       <c r="AA989" s="1"/>
       <c r="AB989" s="1"/>
     </row>
-    <row r="990" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -30591,7 +30633,7 @@
       <c r="AA990" s="1"/>
       <c r="AB990" s="1"/>
     </row>
-    <row r="991" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -30621,7 +30663,7 @@
       <c r="AA991" s="1"/>
       <c r="AB991" s="1"/>
     </row>
-    <row r="992" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -30651,7 +30693,7 @@
       <c r="AA992" s="1"/>
       <c r="AB992" s="1"/>
     </row>
-    <row r="993" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -30681,7 +30723,7 @@
       <c r="AA993" s="1"/>
       <c r="AB993" s="1"/>
     </row>
-    <row r="994" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -30711,7 +30753,7 @@
       <c r="AA994" s="1"/>
       <c r="AB994" s="1"/>
     </row>
-    <row r="995" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -30741,7 +30783,7 @@
       <c r="AA995" s="1"/>
       <c r="AB995" s="1"/>
     </row>
-    <row r="996" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -30771,7 +30813,7 @@
       <c r="AA996" s="1"/>
       <c r="AB996" s="1"/>
     </row>
-    <row r="997" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -30801,7 +30843,7 @@
       <c r="AA997" s="1"/>
       <c r="AB997" s="1"/>
     </row>
-    <row r="998" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -30831,7 +30873,7 @@
       <c r="AA998" s="1"/>
       <c r="AB998" s="1"/>
     </row>
-    <row r="999" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -30861,7 +30903,7 @@
       <c r="AA999" s="1"/>
       <c r="AB999" s="1"/>
     </row>
-    <row r="1000" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -30891,7 +30933,7 @@
       <c r="AA1000" s="1"/>
       <c r="AB1000" s="1"/>
     </row>
-    <row r="1001" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA39B26-EF7C-48D5-BE5F-7E0B9DF2214E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6169A1-2239-468E-AF59-9B163DCFA05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" s="4">
         <v>5</v>
@@ -695,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4">
         <v>6</v>
@@ -740,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="4">
         <v>7</v>
@@ -785,7 +785,7 @@
         <v>1.5</v>
       </c>
       <c r="J8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4">
         <v>8</v>
@@ -830,7 +830,7 @@
         <v>1.5</v>
       </c>
       <c r="J9" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L9" s="1">
         <v>9</v>
@@ -875,7 +875,7 @@
         <v>1.5</v>
       </c>
       <c r="J10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10" s="1">
         <v>10</v>
@@ -920,7 +920,7 @@
         <v>1.5</v>
       </c>
       <c r="J11" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="1">
         <v>11</v>
@@ -966,7 +966,7 @@
         <v>1.5</v>
       </c>
       <c r="J12" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12" s="1">
         <v>12</v>
@@ -1013,7 +1013,7 @@
         <v>1.5</v>
       </c>
       <c r="J13" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" s="1">
         <v>13</v>
@@ -1060,7 +1060,7 @@
         <v>2</v>
       </c>
       <c r="J14" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L14" s="1">
         <v>14</v>
@@ -1107,7 +1107,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L15" s="1">
         <v>15</v>
@@ -1154,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L16" s="1">
         <v>16</v>

--- a/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6169A1-2239-468E-AF59-9B163DCFA05C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D3BD39-2C44-4D3D-BC55-FB099BDC72E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -631,7 +631,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>9000</v>
+        <v>30000</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>

--- a/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D3BD39-2C44-4D3D-BC55-FB099BDC72E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20268DD-A193-4451-B890-71144D9590B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,6 +181,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -631,7 +632,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>

--- a/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20268DD-A193-4451-B890-71144D9590B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5834CCF-665E-450B-AE51-D88FCC76B714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MilestoneParam" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t>TerPointInc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PriceMulti</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -240,7 +244,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -457,15 +461,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AB1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="22.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,7 +500,9 @@
       <c r="J1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -515,7 +521,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -546,7 +552,9 @@
       <c r="J2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -565,7 +573,7 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -594,7 +602,7 @@
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -623,7 +631,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>0</v>
@@ -652,9 +660,10 @@
       <c r="J5" s="1">
         <v>5</v>
       </c>
-      <c r="L5" s="4">
-        <v>5</v>
+      <c r="K5" s="1">
+        <v>2</v>
       </c>
+      <c r="L5" s="4"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -672,7 +681,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1</v>
@@ -698,9 +707,10 @@
       <c r="J6" s="1">
         <v>5</v>
       </c>
-      <c r="L6" s="4">
-        <v>6</v>
+      <c r="K6" s="1">
+        <v>2</v>
       </c>
+      <c r="L6" s="4"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -717,7 +727,7 @@
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
@@ -743,9 +753,10 @@
       <c r="J7" s="1">
         <v>5</v>
       </c>
-      <c r="L7" s="4">
-        <v>7</v>
+      <c r="K7" s="1">
+        <v>2</v>
       </c>
+      <c r="L7" s="4"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -762,7 +773,7 @@
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
@@ -788,9 +799,10 @@
       <c r="J8" s="1">
         <v>5</v>
       </c>
-      <c r="L8" s="4">
-        <v>8</v>
+      <c r="K8" s="1">
+        <v>2</v>
       </c>
+      <c r="L8" s="4"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -807,7 +819,7 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
@@ -833,9 +845,10 @@
       <c r="J9" s="1">
         <v>6</v>
       </c>
-      <c r="L9" s="1">
-        <v>9</v>
+      <c r="K9" s="1">
+        <v>2</v>
       </c>
+      <c r="L9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -852,7 +865,7 @@
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
     </row>
-    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>5</v>
@@ -878,9 +891,10 @@
       <c r="J10" s="1">
         <v>6</v>
       </c>
-      <c r="L10" s="1">
-        <v>10</v>
+      <c r="K10" s="1">
+        <v>2</v>
       </c>
+      <c r="L10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -897,7 +911,7 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>6</v>
@@ -923,9 +937,10 @@
       <c r="J11" s="1">
         <v>6</v>
       </c>
-      <c r="L11" s="1">
-        <v>11</v>
+      <c r="K11" s="1">
+        <v>2</v>
       </c>
+      <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -943,7 +958,7 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>7</v>
@@ -969,9 +984,10 @@
       <c r="J12" s="1">
         <v>6</v>
       </c>
-      <c r="L12" s="1">
-        <v>12</v>
+      <c r="K12" s="1">
+        <v>2</v>
       </c>
+      <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -989,7 +1005,7 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
     </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>8</v>
@@ -1016,9 +1032,10 @@
       <c r="J13" s="1">
         <v>6</v>
       </c>
-      <c r="L13" s="1">
-        <v>13</v>
+      <c r="K13" s="1">
+        <v>2</v>
       </c>
+      <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1036,7 +1053,7 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
     </row>
-    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>9</v>
@@ -1063,9 +1080,10 @@
       <c r="J14" s="1">
         <v>7</v>
       </c>
-      <c r="L14" s="1">
-        <v>14</v>
+      <c r="K14" s="1">
+        <v>2</v>
       </c>
+      <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1083,7 +1101,7 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>10</v>
@@ -1110,9 +1128,10 @@
       <c r="J15" s="1">
         <v>7</v>
       </c>
-      <c r="L15" s="1">
-        <v>15</v>
+      <c r="K15" s="1">
+        <v>2</v>
       </c>
+      <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1130,7 +1149,7 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
     </row>
-    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>11</v>
@@ -1157,9 +1176,10 @@
       <c r="J16" s="1">
         <v>7</v>
       </c>
-      <c r="L16" s="1">
-        <v>16</v>
+      <c r="K16" s="1">
+        <v>2</v>
       </c>
+      <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1177,7 +1197,7 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>12</v>
@@ -1204,9 +1224,10 @@
       <c r="J17" s="1">
         <v>7</v>
       </c>
-      <c r="L17" s="1">
-        <v>17</v>
+      <c r="K17" s="1">
+        <v>2</v>
       </c>
+      <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1224,7 +1245,7 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
@@ -1251,9 +1272,10 @@
       <c r="J18" s="1">
         <v>7</v>
       </c>
-      <c r="L18" s="2">
-        <v>18</v>
+      <c r="K18" s="1">
+        <v>2</v>
       </c>
+      <c r="L18" s="2"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1271,7 +1293,7 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>14</v>
@@ -1298,9 +1320,10 @@
       <c r="J19" s="1">
         <v>7</v>
       </c>
-      <c r="L19" s="1">
-        <v>19</v>
+      <c r="K19" s="1">
+        <v>2</v>
       </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1318,7 +1341,7 @@
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
     </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>15</v>
@@ -1345,9 +1368,10 @@
       <c r="J20" s="1">
         <v>8</v>
       </c>
-      <c r="L20" s="1">
-        <v>20</v>
+      <c r="K20" s="1">
+        <v>2</v>
       </c>
+      <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -1365,7 +1389,7 @@
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
     </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>16</v>
@@ -1392,9 +1416,10 @@
       <c r="J21" s="1">
         <v>8</v>
       </c>
-      <c r="L21" s="1">
-        <v>21</v>
+      <c r="K21" s="1">
+        <v>2</v>
       </c>
+      <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -1412,7 +1437,7 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>17</v>
@@ -1439,9 +1464,10 @@
       <c r="J22" s="1">
         <v>8</v>
       </c>
-      <c r="L22" s="1">
-        <v>21</v>
+      <c r="K22" s="1">
+        <v>2</v>
       </c>
+      <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -1459,7 +1485,7 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>18</v>
@@ -1486,9 +1512,10 @@
       <c r="J23" s="1">
         <v>8</v>
       </c>
-      <c r="L23" s="1">
-        <v>22</v>
+      <c r="K23" s="1">
+        <v>2</v>
       </c>
+      <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -1506,7 +1533,7 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>19</v>
@@ -1533,9 +1560,10 @@
       <c r="J24" s="1">
         <v>8</v>
       </c>
-      <c r="L24" s="1">
-        <v>23</v>
+      <c r="K24" s="1">
+        <v>2</v>
       </c>
+      <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -1553,7 +1581,7 @@
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
     </row>
-    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>20</v>
@@ -1580,9 +1608,10 @@
       <c r="J25" s="1">
         <v>8</v>
       </c>
-      <c r="L25" s="1">
-        <v>24</v>
+      <c r="K25" s="1">
+        <v>2</v>
       </c>
+      <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -1600,7 +1629,7 @@
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
     </row>
-    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>21</v>
@@ -1627,9 +1656,10 @@
       <c r="J26" s="1">
         <v>9</v>
       </c>
-      <c r="L26" s="1">
-        <v>25</v>
+      <c r="K26" s="1">
+        <v>2</v>
       </c>
+      <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1647,7 +1677,7 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>22</v>
@@ -1673,9 +1703,10 @@
       <c r="J27" s="2">
         <v>9</v>
       </c>
-      <c r="L27" s="1">
-        <v>25</v>
+      <c r="K27" s="1">
+        <v>2</v>
       </c>
+      <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -1693,7 +1724,7 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>23</v>
@@ -1720,9 +1751,10 @@
       <c r="J28" s="1">
         <v>9</v>
       </c>
-      <c r="L28" s="1">
-        <v>26</v>
+      <c r="K28" s="1">
+        <v>2</v>
       </c>
+      <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -1740,7 +1772,7 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>24</v>
@@ -1767,9 +1799,10 @@
       <c r="J29" s="1">
         <v>9</v>
       </c>
-      <c r="L29" s="1">
-        <v>27</v>
+      <c r="K29" s="1">
+        <v>2</v>
       </c>
+      <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
@@ -1787,7 +1820,7 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>25</v>
@@ -1814,9 +1847,10 @@
       <c r="J30" s="1">
         <v>10</v>
       </c>
-      <c r="L30" s="1">
-        <v>28</v>
+      <c r="K30" s="1">
+        <v>2</v>
       </c>
+      <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -1834,7 +1868,7 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
     </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1864,7 +1898,7 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1894,7 +1928,7 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1924,7 +1958,7 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
     </row>
-    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1954,7 +1988,7 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
     </row>
-    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1984,7 +2018,7 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
     </row>
-    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2014,7 +2048,7 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2044,7 +2078,7 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2074,7 +2108,7 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
     </row>
-    <row r="39" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2104,7 +2138,7 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
     </row>
-    <row r="40" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2134,7 +2168,7 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
     </row>
-    <row r="41" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2164,7 +2198,7 @@
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
     </row>
-    <row r="42" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2194,7 +2228,7 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
     </row>
-    <row r="43" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2224,7 +2258,7 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
     </row>
-    <row r="44" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2254,7 +2288,7 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
     </row>
-    <row r="45" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2284,7 +2318,7 @@
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
     </row>
-    <row r="46" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2314,7 +2348,7 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2344,7 +2378,7 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
     </row>
-    <row r="48" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2374,7 +2408,7 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
     </row>
-    <row r="49" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2404,7 +2438,7 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2434,7 +2468,7 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
     </row>
-    <row r="51" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2464,7 +2498,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2494,7 +2528,7 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
     </row>
-    <row r="53" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2524,7 +2558,7 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
     </row>
-    <row r="54" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2554,7 +2588,7 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
     </row>
-    <row r="55" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2584,7 +2618,7 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2614,7 +2648,7 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2644,7 +2678,7 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2674,7 +2708,7 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2704,7 +2738,7 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2734,7 +2768,7 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2764,7 +2798,7 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2794,7 +2828,7 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2824,7 +2858,7 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2854,7 +2888,7 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2884,7 +2918,7 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="66" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2914,7 +2948,7 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
     </row>
-    <row r="67" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2944,7 +2978,7 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
     </row>
-    <row r="68" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2974,7 +3008,7 @@
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
     </row>
-    <row r="69" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3004,7 +3038,7 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
     </row>
-    <row r="70" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3034,7 +3068,7 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3064,7 +3098,7 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3094,7 +3128,7 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
     </row>
-    <row r="73" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3124,7 +3158,7 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
     </row>
-    <row r="74" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3154,7 +3188,7 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
     </row>
-    <row r="75" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3184,7 +3218,7 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
     </row>
-    <row r="76" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3214,7 +3248,7 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
     </row>
-    <row r="77" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3244,7 +3278,7 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
     </row>
-    <row r="78" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3274,7 +3308,7 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
     </row>
-    <row r="79" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3304,7 +3338,7 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
     </row>
-    <row r="80" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3334,7 +3368,7 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
     </row>
-    <row r="81" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3364,7 +3398,7 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
     </row>
-    <row r="82" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3394,7 +3428,7 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
     </row>
-    <row r="83" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3424,7 +3458,7 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
     </row>
-    <row r="84" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3454,7 +3488,7 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
     </row>
-    <row r="85" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3484,7 +3518,7 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
     </row>
-    <row r="86" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3514,7 +3548,7 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
     </row>
-    <row r="87" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3544,7 +3578,7 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
     </row>
-    <row r="88" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3574,7 +3608,7 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
     </row>
-    <row r="89" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3604,7 +3638,7 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
     </row>
-    <row r="90" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3634,7 +3668,7 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
     </row>
-    <row r="91" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3664,7 +3698,7 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
     </row>
-    <row r="92" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3694,7 +3728,7 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
     </row>
-    <row r="93" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3724,7 +3758,7 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
     </row>
-    <row r="94" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3754,7 +3788,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3784,7 +3818,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3814,7 +3848,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3844,7 +3878,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3874,7 +3908,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3904,7 +3938,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3934,7 +3968,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3964,7 +3998,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3994,7 +4028,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4024,7 +4058,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4054,7 +4088,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4084,7 +4118,7 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
     </row>
-    <row r="106" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4114,7 +4148,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4144,7 +4178,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4174,7 +4208,7 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
     </row>
-    <row r="109" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4204,7 +4238,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4234,7 +4268,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4264,7 +4298,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4294,7 +4328,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4324,7 +4358,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4354,7 +4388,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4384,7 +4418,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4414,7 +4448,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4444,7 +4478,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4474,7 +4508,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4504,7 +4538,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4534,7 +4568,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4564,7 +4598,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4594,7 +4628,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4624,7 +4658,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4654,7 +4688,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4684,7 +4718,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4714,7 +4748,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4744,7 +4778,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4774,7 +4808,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4804,7 +4838,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4834,7 +4868,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4864,7 +4898,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4894,7 +4928,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4924,7 +4958,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4954,7 +4988,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4984,7 +5018,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5014,7 +5048,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5044,7 +5078,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5074,7 +5108,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5104,7 +5138,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5134,7 +5168,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5164,7 +5198,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5194,7 +5228,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5224,7 +5258,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5254,7 +5288,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5284,7 +5318,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5314,7 +5348,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5344,7 +5378,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5374,7 +5408,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5404,7 +5438,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5434,7 +5468,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5464,7 +5498,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5494,7 +5528,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5524,7 +5558,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5554,7 +5588,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5584,7 +5618,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5614,7 +5648,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5644,7 +5678,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5674,7 +5708,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5704,7 +5738,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5734,7 +5768,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5764,7 +5798,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5794,7 +5828,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5824,7 +5858,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5854,7 +5888,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5884,7 +5918,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5914,7 +5948,7 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
     </row>
-    <row r="167" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5944,7 +5978,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5974,7 +6008,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6004,7 +6038,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6034,7 +6068,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6064,7 +6098,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6094,7 +6128,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6124,7 +6158,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6154,7 +6188,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6184,7 +6218,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6214,7 +6248,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6244,7 +6278,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6274,7 +6308,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6304,7 +6338,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6334,7 +6368,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6364,7 +6398,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6394,7 +6428,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6424,7 +6458,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6454,7 +6488,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6484,7 +6518,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6514,7 +6548,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6544,7 +6578,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6574,7 +6608,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6604,7 +6638,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6634,7 +6668,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6664,7 +6698,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6694,7 +6728,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6724,7 +6758,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6754,7 +6788,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6784,7 +6818,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6814,7 +6848,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6844,7 +6878,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6874,7 +6908,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6904,7 +6938,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6934,7 +6968,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6964,7 +6998,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6994,7 +7028,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7024,7 +7058,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7054,7 +7088,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7084,7 +7118,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7114,7 +7148,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7144,7 +7178,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7174,7 +7208,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7204,7 +7238,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7234,7 +7268,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7264,7 +7298,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7294,7 +7328,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7324,7 +7358,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7354,7 +7388,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7384,7 +7418,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7414,7 +7448,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7444,7 +7478,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7474,7 +7508,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7504,7 +7538,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7534,7 +7568,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7564,7 +7598,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7594,7 +7628,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7624,7 +7658,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7654,7 +7688,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7684,7 +7718,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7714,7 +7748,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7744,7 +7778,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7774,7 +7808,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7804,7 +7838,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7834,7 +7868,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7864,7 +7898,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7894,7 +7928,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7924,7 +7958,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -7954,7 +7988,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7984,7 +8018,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8014,7 +8048,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8044,7 +8078,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8074,7 +8108,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8104,7 +8138,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8134,7 +8168,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8164,7 +8198,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8194,7 +8228,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8224,7 +8258,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8254,7 +8288,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8284,7 +8318,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8314,7 +8348,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8344,7 +8378,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8374,7 +8408,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8404,7 +8438,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8434,7 +8468,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8464,7 +8498,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8494,7 +8528,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8524,7 +8558,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8554,7 +8588,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8584,7 +8618,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8614,7 +8648,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8644,7 +8678,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8674,7 +8708,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8704,7 +8738,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8734,7 +8768,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8764,7 +8798,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8794,7 +8828,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8824,7 +8858,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8854,7 +8888,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -8884,7 +8918,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -8914,7 +8948,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -8944,7 +8978,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -8974,7 +9008,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9004,7 +9038,7 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
     </row>
-    <row r="270" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9034,7 +9068,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9064,7 +9098,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9094,7 +9128,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9124,7 +9158,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9154,7 +9188,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
     </row>
-    <row r="275" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9184,7 +9218,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9214,7 +9248,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9244,7 +9278,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9274,7 +9308,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9304,7 +9338,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9334,7 +9368,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9364,7 +9398,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9394,7 +9428,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9424,7 +9458,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9454,7 +9488,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9484,7 +9518,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -9514,7 +9548,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -9544,7 +9578,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -9574,7 +9608,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -9604,7 +9638,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -9634,7 +9668,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -9664,7 +9698,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -9694,7 +9728,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -9724,7 +9758,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -9754,7 +9788,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -9784,7 +9818,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -9814,7 +9848,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -9844,7 +9878,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -9874,7 +9908,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -9904,7 +9938,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -9934,7 +9968,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -9964,7 +9998,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -9994,7 +10028,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10024,7 +10058,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10054,7 +10088,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10084,7 +10118,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10114,7 +10148,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10144,7 +10178,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10174,7 +10208,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10204,7 +10238,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10234,7 +10268,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10264,7 +10298,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10294,7 +10328,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10324,7 +10358,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10354,7 +10388,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10384,7 +10418,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10414,7 +10448,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10444,7 +10478,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -10474,7 +10508,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -10504,7 +10538,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -10534,7 +10568,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -10564,7 +10598,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -10594,7 +10628,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -10624,7 +10658,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10654,7 +10688,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10684,7 +10718,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -10714,7 +10748,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -10744,7 +10778,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -10774,7 +10808,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -10804,7 +10838,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -10834,7 +10868,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -10864,7 +10898,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -10894,7 +10928,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -10924,7 +10958,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -10954,7 +10988,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -10984,7 +11018,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11014,7 +11048,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11044,7 +11078,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11074,7 +11108,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11104,7 +11138,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11134,7 +11168,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11164,7 +11198,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11194,7 +11228,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11224,7 +11258,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11254,7 +11288,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11284,7 +11318,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11314,7 +11348,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11344,7 +11378,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11374,7 +11408,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11404,7 +11438,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11434,7 +11468,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11464,7 +11498,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11494,7 +11528,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -11524,7 +11558,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -11554,7 +11588,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -11584,7 +11618,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -11614,7 +11648,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -11644,7 +11678,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -11674,7 +11708,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -11704,7 +11738,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -11734,7 +11768,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -11764,7 +11798,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -11794,7 +11828,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -11824,7 +11858,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -11854,7 +11888,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -11884,7 +11918,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -11914,7 +11948,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -11944,7 +11978,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -11974,7 +12008,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12004,7 +12038,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12034,7 +12068,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12064,7 +12098,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12094,7 +12128,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12124,7 +12158,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12154,7 +12188,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12184,7 +12218,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12214,7 +12248,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12244,7 +12278,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12274,7 +12308,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12304,7 +12338,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12334,7 +12368,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12364,7 +12398,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12394,7 +12428,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12424,7 +12458,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12454,7 +12488,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12484,7 +12518,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12514,7 +12548,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12544,7 +12578,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12574,7 +12608,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -12604,7 +12638,7 @@
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
     </row>
-    <row r="390" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -12634,7 +12668,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -12664,7 +12698,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -12694,7 +12728,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -12724,7 +12758,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -12754,7 +12788,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -12784,7 +12818,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -12814,7 +12848,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -12844,7 +12878,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -12874,7 +12908,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -12904,7 +12938,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -12934,7 +12968,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -12964,7 +12998,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -12994,7 +13028,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13024,7 +13058,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13054,7 +13088,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13084,7 +13118,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13114,7 +13148,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13144,7 +13178,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13174,7 +13208,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13204,7 +13238,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13234,7 +13268,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13264,7 +13298,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13294,7 +13328,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13324,7 +13358,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13354,7 +13388,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13384,7 +13418,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13414,7 +13448,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13444,7 +13478,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13474,7 +13508,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13504,7 +13538,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13534,7 +13568,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -13564,7 +13598,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -13594,7 +13628,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -13624,7 +13658,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -13654,7 +13688,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -13684,7 +13718,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -13714,7 +13748,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -13744,7 +13778,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -13774,7 +13808,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -13804,7 +13838,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -13834,7 +13868,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -13864,7 +13898,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -13894,7 +13928,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -13924,7 +13958,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -13954,7 +13988,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -13984,7 +14018,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14014,7 +14048,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14044,7 +14078,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14074,7 +14108,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14104,7 +14138,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14134,7 +14168,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14164,7 +14198,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14194,7 +14228,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14224,7 +14258,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14254,7 +14288,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14284,7 +14318,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14314,7 +14348,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14344,7 +14378,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14374,7 +14408,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14404,7 +14438,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14434,7 +14468,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14464,7 +14498,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14494,7 +14528,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -14524,7 +14558,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -14554,7 +14588,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -14584,7 +14618,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -14614,7 +14648,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -14644,7 +14678,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -14674,7 +14708,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -14704,7 +14738,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -14734,7 +14768,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -14764,7 +14798,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -14794,7 +14828,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -14824,7 +14858,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -14854,7 +14888,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -14884,7 +14918,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -14914,7 +14948,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -14944,7 +14978,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -14974,7 +15008,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15004,7 +15038,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15034,7 +15068,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15064,7 +15098,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15094,7 +15128,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15124,7 +15158,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15154,7 +15188,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15184,7 +15218,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15214,7 +15248,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15244,7 +15278,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15274,7 +15308,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15304,7 +15338,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15334,7 +15368,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15364,7 +15398,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15394,7 +15428,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15424,7 +15458,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -15454,7 +15488,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -15484,7 +15518,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -15514,7 +15548,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -15544,7 +15578,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -15574,7 +15608,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -15604,7 +15638,7 @@
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
     </row>
-    <row r="490" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -15634,7 +15668,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -15664,7 +15698,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -15694,7 +15728,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -15724,7 +15758,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -15754,7 +15788,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -15784,7 +15818,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -15814,7 +15848,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -15844,7 +15878,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -15874,7 +15908,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -15904,7 +15938,7 @@
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
     </row>
-    <row r="500" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -15934,7 +15968,7 @@
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
     </row>
-    <row r="501" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -15964,7 +15998,7 @@
       <c r="AA501" s="1"/>
       <c r="AB501" s="1"/>
     </row>
-    <row r="502" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -15994,7 +16028,7 @@
       <c r="AA502" s="1"/>
       <c r="AB502" s="1"/>
     </row>
-    <row r="503" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16024,7 +16058,7 @@
       <c r="AA503" s="1"/>
       <c r="AB503" s="1"/>
     </row>
-    <row r="504" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16054,7 +16088,7 @@
       <c r="AA504" s="1"/>
       <c r="AB504" s="1"/>
     </row>
-    <row r="505" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16084,7 +16118,7 @@
       <c r="AA505" s="1"/>
       <c r="AB505" s="1"/>
     </row>
-    <row r="506" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16114,7 +16148,7 @@
       <c r="AA506" s="1"/>
       <c r="AB506" s="1"/>
     </row>
-    <row r="507" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16144,7 +16178,7 @@
       <c r="AA507" s="1"/>
       <c r="AB507" s="1"/>
     </row>
-    <row r="508" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16174,7 +16208,7 @@
       <c r="AA508" s="1"/>
       <c r="AB508" s="1"/>
     </row>
-    <row r="509" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16204,7 +16238,7 @@
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
     </row>
-    <row r="510" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16234,7 +16268,7 @@
       <c r="AA510" s="1"/>
       <c r="AB510" s="1"/>
     </row>
-    <row r="511" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16264,7 +16298,7 @@
       <c r="AA511" s="1"/>
       <c r="AB511" s="1"/>
     </row>
-    <row r="512" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16294,7 +16328,7 @@
       <c r="AA512" s="1"/>
       <c r="AB512" s="1"/>
     </row>
-    <row r="513" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16324,7 +16358,7 @@
       <c r="AA513" s="1"/>
       <c r="AB513" s="1"/>
     </row>
-    <row r="514" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16354,7 +16388,7 @@
       <c r="AA514" s="1"/>
       <c r="AB514" s="1"/>
     </row>
-    <row r="515" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16384,7 +16418,7 @@
       <c r="AA515" s="1"/>
       <c r="AB515" s="1"/>
     </row>
-    <row r="516" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -16414,7 +16448,7 @@
       <c r="AA516" s="1"/>
       <c r="AB516" s="1"/>
     </row>
-    <row r="517" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -16444,7 +16478,7 @@
       <c r="AA517" s="1"/>
       <c r="AB517" s="1"/>
     </row>
-    <row r="518" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -16474,7 +16508,7 @@
       <c r="AA518" s="1"/>
       <c r="AB518" s="1"/>
     </row>
-    <row r="519" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -16504,7 +16538,7 @@
       <c r="AA519" s="1"/>
       <c r="AB519" s="1"/>
     </row>
-    <row r="520" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -16534,7 +16568,7 @@
       <c r="AA520" s="1"/>
       <c r="AB520" s="1"/>
     </row>
-    <row r="521" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -16564,7 +16598,7 @@
       <c r="AA521" s="1"/>
       <c r="AB521" s="1"/>
     </row>
-    <row r="522" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -16594,7 +16628,7 @@
       <c r="AA522" s="1"/>
       <c r="AB522" s="1"/>
     </row>
-    <row r="523" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -16624,7 +16658,7 @@
       <c r="AA523" s="1"/>
       <c r="AB523" s="1"/>
     </row>
-    <row r="524" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -16654,7 +16688,7 @@
       <c r="AA524" s="1"/>
       <c r="AB524" s="1"/>
     </row>
-    <row r="525" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -16684,7 +16718,7 @@
       <c r="AA525" s="1"/>
       <c r="AB525" s="1"/>
     </row>
-    <row r="526" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -16714,7 +16748,7 @@
       <c r="AA526" s="1"/>
       <c r="AB526" s="1"/>
     </row>
-    <row r="527" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -16744,7 +16778,7 @@
       <c r="AA527" s="1"/>
       <c r="AB527" s="1"/>
     </row>
-    <row r="528" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -16774,7 +16808,7 @@
       <c r="AA528" s="1"/>
       <c r="AB528" s="1"/>
     </row>
-    <row r="529" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -16804,7 +16838,7 @@
       <c r="AA529" s="1"/>
       <c r="AB529" s="1"/>
     </row>
-    <row r="530" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -16834,7 +16868,7 @@
       <c r="AA530" s="1"/>
       <c r="AB530" s="1"/>
     </row>
-    <row r="531" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -16864,7 +16898,7 @@
       <c r="AA531" s="1"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -16894,7 +16928,7 @@
       <c r="AA532" s="1"/>
       <c r="AB532" s="1"/>
     </row>
-    <row r="533" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -16924,7 +16958,7 @@
       <c r="AA533" s="1"/>
       <c r="AB533" s="1"/>
     </row>
-    <row r="534" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -16954,7 +16988,7 @@
       <c r="AA534" s="1"/>
       <c r="AB534" s="1"/>
     </row>
-    <row r="535" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -16984,7 +17018,7 @@
       <c r="AA535" s="1"/>
       <c r="AB535" s="1"/>
     </row>
-    <row r="536" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17014,7 +17048,7 @@
       <c r="AA536" s="1"/>
       <c r="AB536" s="1"/>
     </row>
-    <row r="537" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17044,7 +17078,7 @@
       <c r="AA537" s="1"/>
       <c r="AB537" s="1"/>
     </row>
-    <row r="538" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17074,7 +17108,7 @@
       <c r="AA538" s="1"/>
       <c r="AB538" s="1"/>
     </row>
-    <row r="539" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17104,7 +17138,7 @@
       <c r="AA539" s="1"/>
       <c r="AB539" s="1"/>
     </row>
-    <row r="540" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17134,7 +17168,7 @@
       <c r="AA540" s="1"/>
       <c r="AB540" s="1"/>
     </row>
-    <row r="541" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17164,7 +17198,7 @@
       <c r="AA541" s="1"/>
       <c r="AB541" s="1"/>
     </row>
-    <row r="542" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17194,7 +17228,7 @@
       <c r="AA542" s="1"/>
       <c r="AB542" s="1"/>
     </row>
-    <row r="543" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17224,7 +17258,7 @@
       <c r="AA543" s="1"/>
       <c r="AB543" s="1"/>
     </row>
-    <row r="544" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17254,7 +17288,7 @@
       <c r="AA544" s="1"/>
       <c r="AB544" s="1"/>
     </row>
-    <row r="545" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17284,7 +17318,7 @@
       <c r="AA545" s="1"/>
       <c r="AB545" s="1"/>
     </row>
-    <row r="546" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -17314,7 +17348,7 @@
       <c r="AA546" s="1"/>
       <c r="AB546" s="1"/>
     </row>
-    <row r="547" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -17344,7 +17378,7 @@
       <c r="AA547" s="1"/>
       <c r="AB547" s="1"/>
     </row>
-    <row r="548" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -17374,7 +17408,7 @@
       <c r="AA548" s="1"/>
       <c r="AB548" s="1"/>
     </row>
-    <row r="549" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -17404,7 +17438,7 @@
       <c r="AA549" s="1"/>
       <c r="AB549" s="1"/>
     </row>
-    <row r="550" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -17434,7 +17468,7 @@
       <c r="AA550" s="1"/>
       <c r="AB550" s="1"/>
     </row>
-    <row r="551" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -17464,7 +17498,7 @@
       <c r="AA551" s="1"/>
       <c r="AB551" s="1"/>
     </row>
-    <row r="552" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -17494,7 +17528,7 @@
       <c r="AA552" s="1"/>
       <c r="AB552" s="1"/>
     </row>
-    <row r="553" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -17524,7 +17558,7 @@
       <c r="AA553" s="1"/>
       <c r="AB553" s="1"/>
     </row>
-    <row r="554" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -17554,7 +17588,7 @@
       <c r="AA554" s="1"/>
       <c r="AB554" s="1"/>
     </row>
-    <row r="555" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -17584,7 +17618,7 @@
       <c r="AA555" s="1"/>
       <c r="AB555" s="1"/>
     </row>
-    <row r="556" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -17614,7 +17648,7 @@
       <c r="AA556" s="1"/>
       <c r="AB556" s="1"/>
     </row>
-    <row r="557" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -17644,7 +17678,7 @@
       <c r="AA557" s="1"/>
       <c r="AB557" s="1"/>
     </row>
-    <row r="558" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -17674,7 +17708,7 @@
       <c r="AA558" s="1"/>
       <c r="AB558" s="1"/>
     </row>
-    <row r="559" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -17704,7 +17738,7 @@
       <c r="AA559" s="1"/>
       <c r="AB559" s="1"/>
     </row>
-    <row r="560" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -17734,7 +17768,7 @@
       <c r="AA560" s="1"/>
       <c r="AB560" s="1"/>
     </row>
-    <row r="561" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -17764,7 +17798,7 @@
       <c r="AA561" s="1"/>
       <c r="AB561" s="1"/>
     </row>
-    <row r="562" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -17794,7 +17828,7 @@
       <c r="AA562" s="1"/>
       <c r="AB562" s="1"/>
     </row>
-    <row r="563" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -17824,7 +17858,7 @@
       <c r="AA563" s="1"/>
       <c r="AB563" s="1"/>
     </row>
-    <row r="564" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -17854,7 +17888,7 @@
       <c r="AA564" s="1"/>
       <c r="AB564" s="1"/>
     </row>
-    <row r="565" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -17884,7 +17918,7 @@
       <c r="AA565" s="1"/>
       <c r="AB565" s="1"/>
     </row>
-    <row r="566" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -17914,7 +17948,7 @@
       <c r="AA566" s="1"/>
       <c r="AB566" s="1"/>
     </row>
-    <row r="567" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -17944,7 +17978,7 @@
       <c r="AA567" s="1"/>
       <c r="AB567" s="1"/>
     </row>
-    <row r="568" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -17974,7 +18008,7 @@
       <c r="AA568" s="1"/>
       <c r="AB568" s="1"/>
     </row>
-    <row r="569" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18004,7 +18038,7 @@
       <c r="AA569" s="1"/>
       <c r="AB569" s="1"/>
     </row>
-    <row r="570" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18034,7 +18068,7 @@
       <c r="AA570" s="1"/>
       <c r="AB570" s="1"/>
     </row>
-    <row r="571" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18064,7 +18098,7 @@
       <c r="AA571" s="1"/>
       <c r="AB571" s="1"/>
     </row>
-    <row r="572" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18094,7 +18128,7 @@
       <c r="AA572" s="1"/>
       <c r="AB572" s="1"/>
     </row>
-    <row r="573" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18124,7 +18158,7 @@
       <c r="AA573" s="1"/>
       <c r="AB573" s="1"/>
     </row>
-    <row r="574" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18154,7 +18188,7 @@
       <c r="AA574" s="1"/>
       <c r="AB574" s="1"/>
     </row>
-    <row r="575" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18184,7 +18218,7 @@
       <c r="AA575" s="1"/>
       <c r="AB575" s="1"/>
     </row>
-    <row r="576" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18214,7 +18248,7 @@
       <c r="AA576" s="1"/>
       <c r="AB576" s="1"/>
     </row>
-    <row r="577" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18244,7 +18278,7 @@
       <c r="AA577" s="1"/>
       <c r="AB577" s="1"/>
     </row>
-    <row r="578" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -18274,7 +18308,7 @@
       <c r="AA578" s="1"/>
       <c r="AB578" s="1"/>
     </row>
-    <row r="579" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -18304,7 +18338,7 @@
       <c r="AA579" s="1"/>
       <c r="AB579" s="1"/>
     </row>
-    <row r="580" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -18334,7 +18368,7 @@
       <c r="AA580" s="1"/>
       <c r="AB580" s="1"/>
     </row>
-    <row r="581" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -18364,7 +18398,7 @@
       <c r="AA581" s="1"/>
       <c r="AB581" s="1"/>
     </row>
-    <row r="582" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -18394,7 +18428,7 @@
       <c r="AA582" s="1"/>
       <c r="AB582" s="1"/>
     </row>
-    <row r="583" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -18424,7 +18458,7 @@
       <c r="AA583" s="1"/>
       <c r="AB583" s="1"/>
     </row>
-    <row r="584" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -18454,7 +18488,7 @@
       <c r="AA584" s="1"/>
       <c r="AB584" s="1"/>
     </row>
-    <row r="585" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -18484,7 +18518,7 @@
       <c r="AA585" s="1"/>
       <c r="AB585" s="1"/>
     </row>
-    <row r="586" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -18514,7 +18548,7 @@
       <c r="AA586" s="1"/>
       <c r="AB586" s="1"/>
     </row>
-    <row r="587" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -18544,7 +18578,7 @@
       <c r="AA587" s="1"/>
       <c r="AB587" s="1"/>
     </row>
-    <row r="588" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -18574,7 +18608,7 @@
       <c r="AA588" s="1"/>
       <c r="AB588" s="1"/>
     </row>
-    <row r="589" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -18604,7 +18638,7 @@
       <c r="AA589" s="1"/>
       <c r="AB589" s="1"/>
     </row>
-    <row r="590" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -18634,7 +18668,7 @@
       <c r="AA590" s="1"/>
       <c r="AB590" s="1"/>
     </row>
-    <row r="591" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -18664,7 +18698,7 @@
       <c r="AA591" s="1"/>
       <c r="AB591" s="1"/>
     </row>
-    <row r="592" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -18694,7 +18728,7 @@
       <c r="AA592" s="1"/>
       <c r="AB592" s="1"/>
     </row>
-    <row r="593" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -18724,7 +18758,7 @@
       <c r="AA593" s="1"/>
       <c r="AB593" s="1"/>
     </row>
-    <row r="594" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -18754,7 +18788,7 @@
       <c r="AA594" s="1"/>
       <c r="AB594" s="1"/>
     </row>
-    <row r="595" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -18784,7 +18818,7 @@
       <c r="AA595" s="1"/>
       <c r="AB595" s="1"/>
     </row>
-    <row r="596" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -18814,7 +18848,7 @@
       <c r="AA596" s="1"/>
       <c r="AB596" s="1"/>
     </row>
-    <row r="597" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -18844,7 +18878,7 @@
       <c r="AA597" s="1"/>
       <c r="AB597" s="1"/>
     </row>
-    <row r="598" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -18874,7 +18908,7 @@
       <c r="AA598" s="1"/>
       <c r="AB598" s="1"/>
     </row>
-    <row r="599" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -18904,7 +18938,7 @@
       <c r="AA599" s="1"/>
       <c r="AB599" s="1"/>
     </row>
-    <row r="600" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -18934,7 +18968,7 @@
       <c r="AA600" s="1"/>
       <c r="AB600" s="1"/>
     </row>
-    <row r="601" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -18964,7 +18998,7 @@
       <c r="AA601" s="1"/>
       <c r="AB601" s="1"/>
     </row>
-    <row r="602" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -18994,7 +19028,7 @@
       <c r="AA602" s="1"/>
       <c r="AB602" s="1"/>
     </row>
-    <row r="603" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19024,7 +19058,7 @@
       <c r="AA603" s="1"/>
       <c r="AB603" s="1"/>
     </row>
-    <row r="604" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19054,7 +19088,7 @@
       <c r="AA604" s="1"/>
       <c r="AB604" s="1"/>
     </row>
-    <row r="605" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19084,7 +19118,7 @@
       <c r="AA605" s="1"/>
       <c r="AB605" s="1"/>
     </row>
-    <row r="606" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19114,7 +19148,7 @@
       <c r="AA606" s="1"/>
       <c r="AB606" s="1"/>
     </row>
-    <row r="607" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19144,7 +19178,7 @@
       <c r="AA607" s="1"/>
       <c r="AB607" s="1"/>
     </row>
-    <row r="608" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19174,7 +19208,7 @@
       <c r="AA608" s="1"/>
       <c r="AB608" s="1"/>
     </row>
-    <row r="609" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -19204,7 +19238,7 @@
       <c r="AA609" s="1"/>
       <c r="AB609" s="1"/>
     </row>
-    <row r="610" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -19234,7 +19268,7 @@
       <c r="AA610" s="1"/>
       <c r="AB610" s="1"/>
     </row>
-    <row r="611" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -19264,7 +19298,7 @@
       <c r="AA611" s="1"/>
       <c r="AB611" s="1"/>
     </row>
-    <row r="612" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -19294,7 +19328,7 @@
       <c r="AA612" s="1"/>
       <c r="AB612" s="1"/>
     </row>
-    <row r="613" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -19324,7 +19358,7 @@
       <c r="AA613" s="1"/>
       <c r="AB613" s="1"/>
     </row>
-    <row r="614" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -19354,7 +19388,7 @@
       <c r="AA614" s="1"/>
       <c r="AB614" s="1"/>
     </row>
-    <row r="615" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -19384,7 +19418,7 @@
       <c r="AA615" s="1"/>
       <c r="AB615" s="1"/>
     </row>
-    <row r="616" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -19414,7 +19448,7 @@
       <c r="AA616" s="1"/>
       <c r="AB616" s="1"/>
     </row>
-    <row r="617" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -19444,7 +19478,7 @@
       <c r="AA617" s="1"/>
       <c r="AB617" s="1"/>
     </row>
-    <row r="618" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -19474,7 +19508,7 @@
       <c r="AA618" s="1"/>
       <c r="AB618" s="1"/>
     </row>
-    <row r="619" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -19504,7 +19538,7 @@
       <c r="AA619" s="1"/>
       <c r="AB619" s="1"/>
     </row>
-    <row r="620" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -19534,7 +19568,7 @@
       <c r="AA620" s="1"/>
       <c r="AB620" s="1"/>
     </row>
-    <row r="621" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -19564,7 +19598,7 @@
       <c r="AA621" s="1"/>
       <c r="AB621" s="1"/>
     </row>
-    <row r="622" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -19594,7 +19628,7 @@
       <c r="AA622" s="1"/>
       <c r="AB622" s="1"/>
     </row>
-    <row r="623" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -19624,7 +19658,7 @@
       <c r="AA623" s="1"/>
       <c r="AB623" s="1"/>
     </row>
-    <row r="624" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -19654,7 +19688,7 @@
       <c r="AA624" s="1"/>
       <c r="AB624" s="1"/>
     </row>
-    <row r="625" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -19684,7 +19718,7 @@
       <c r="AA625" s="1"/>
       <c r="AB625" s="1"/>
     </row>
-    <row r="626" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -19714,7 +19748,7 @@
       <c r="AA626" s="1"/>
       <c r="AB626" s="1"/>
     </row>
-    <row r="627" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -19744,7 +19778,7 @@
       <c r="AA627" s="1"/>
       <c r="AB627" s="1"/>
     </row>
-    <row r="628" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -19774,7 +19808,7 @@
       <c r="AA628" s="1"/>
       <c r="AB628" s="1"/>
     </row>
-    <row r="629" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -19804,7 +19838,7 @@
       <c r="AA629" s="1"/>
       <c r="AB629" s="1"/>
     </row>
-    <row r="630" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -19834,7 +19868,7 @@
       <c r="AA630" s="1"/>
       <c r="AB630" s="1"/>
     </row>
-    <row r="631" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -19864,7 +19898,7 @@
       <c r="AA631" s="1"/>
       <c r="AB631" s="1"/>
     </row>
-    <row r="632" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -19894,7 +19928,7 @@
       <c r="AA632" s="1"/>
       <c r="AB632" s="1"/>
     </row>
-    <row r="633" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -19924,7 +19958,7 @@
       <c r="AA633" s="1"/>
       <c r="AB633" s="1"/>
     </row>
-    <row r="634" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -19954,7 +19988,7 @@
       <c r="AA634" s="1"/>
       <c r="AB634" s="1"/>
     </row>
-    <row r="635" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -19984,7 +20018,7 @@
       <c r="AA635" s="1"/>
       <c r="AB635" s="1"/>
     </row>
-    <row r="636" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20014,7 +20048,7 @@
       <c r="AA636" s="1"/>
       <c r="AB636" s="1"/>
     </row>
-    <row r="637" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20044,7 +20078,7 @@
       <c r="AA637" s="1"/>
       <c r="AB637" s="1"/>
     </row>
-    <row r="638" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20074,7 +20108,7 @@
       <c r="AA638" s="1"/>
       <c r="AB638" s="1"/>
     </row>
-    <row r="639" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20104,7 +20138,7 @@
       <c r="AA639" s="1"/>
       <c r="AB639" s="1"/>
     </row>
-    <row r="640" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20134,7 +20168,7 @@
       <c r="AA640" s="1"/>
       <c r="AB640" s="1"/>
     </row>
-    <row r="641" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -20164,7 +20198,7 @@
       <c r="AA641" s="1"/>
       <c r="AB641" s="1"/>
     </row>
-    <row r="642" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -20194,7 +20228,7 @@
       <c r="AA642" s="1"/>
       <c r="AB642" s="1"/>
     </row>
-    <row r="643" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -20224,7 +20258,7 @@
       <c r="AA643" s="1"/>
       <c r="AB643" s="1"/>
     </row>
-    <row r="644" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -20254,7 +20288,7 @@
       <c r="AA644" s="1"/>
       <c r="AB644" s="1"/>
     </row>
-    <row r="645" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -20284,7 +20318,7 @@
       <c r="AA645" s="1"/>
       <c r="AB645" s="1"/>
     </row>
-    <row r="646" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -20314,7 +20348,7 @@
       <c r="AA646" s="1"/>
       <c r="AB646" s="1"/>
     </row>
-    <row r="647" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -20344,7 +20378,7 @@
       <c r="AA647" s="1"/>
       <c r="AB647" s="1"/>
     </row>
-    <row r="648" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -20374,7 +20408,7 @@
       <c r="AA648" s="1"/>
       <c r="AB648" s="1"/>
     </row>
-    <row r="649" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -20404,7 +20438,7 @@
       <c r="AA649" s="1"/>
       <c r="AB649" s="1"/>
     </row>
-    <row r="650" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -20434,7 +20468,7 @@
       <c r="AA650" s="1"/>
       <c r="AB650" s="1"/>
     </row>
-    <row r="651" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -20464,7 +20498,7 @@
       <c r="AA651" s="1"/>
       <c r="AB651" s="1"/>
     </row>
-    <row r="652" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -20494,7 +20528,7 @@
       <c r="AA652" s="1"/>
       <c r="AB652" s="1"/>
     </row>
-    <row r="653" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -20524,7 +20558,7 @@
       <c r="AA653" s="1"/>
       <c r="AB653" s="1"/>
     </row>
-    <row r="654" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -20554,7 +20588,7 @@
       <c r="AA654" s="1"/>
       <c r="AB654" s="1"/>
     </row>
-    <row r="655" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -20584,7 +20618,7 @@
       <c r="AA655" s="1"/>
       <c r="AB655" s="1"/>
     </row>
-    <row r="656" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -20614,7 +20648,7 @@
       <c r="AA656" s="1"/>
       <c r="AB656" s="1"/>
     </row>
-    <row r="657" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -20644,7 +20678,7 @@
       <c r="AA657" s="1"/>
       <c r="AB657" s="1"/>
     </row>
-    <row r="658" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -20674,7 +20708,7 @@
       <c r="AA658" s="1"/>
       <c r="AB658" s="1"/>
     </row>
-    <row r="659" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -20704,7 +20738,7 @@
       <c r="AA659" s="1"/>
       <c r="AB659" s="1"/>
     </row>
-    <row r="660" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -20734,7 +20768,7 @@
       <c r="AA660" s="1"/>
       <c r="AB660" s="1"/>
     </row>
-    <row r="661" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -20764,7 +20798,7 @@
       <c r="AA661" s="1"/>
       <c r="AB661" s="1"/>
     </row>
-    <row r="662" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -20794,7 +20828,7 @@
       <c r="AA662" s="1"/>
       <c r="AB662" s="1"/>
     </row>
-    <row r="663" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -20824,7 +20858,7 @@
       <c r="AA663" s="1"/>
       <c r="AB663" s="1"/>
     </row>
-    <row r="664" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -20854,7 +20888,7 @@
       <c r="AA664" s="1"/>
       <c r="AB664" s="1"/>
     </row>
-    <row r="665" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -20884,7 +20918,7 @@
       <c r="AA665" s="1"/>
       <c r="AB665" s="1"/>
     </row>
-    <row r="666" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -20914,7 +20948,7 @@
       <c r="AA666" s="1"/>
       <c r="AB666" s="1"/>
     </row>
-    <row r="667" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -20944,7 +20978,7 @@
       <c r="AA667" s="1"/>
       <c r="AB667" s="1"/>
     </row>
-    <row r="668" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -20974,7 +21008,7 @@
       <c r="AA668" s="1"/>
       <c r="AB668" s="1"/>
     </row>
-    <row r="669" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21004,7 +21038,7 @@
       <c r="AA669" s="1"/>
       <c r="AB669" s="1"/>
     </row>
-    <row r="670" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21034,7 +21068,7 @@
       <c r="AA670" s="1"/>
       <c r="AB670" s="1"/>
     </row>
-    <row r="671" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21064,7 +21098,7 @@
       <c r="AA671" s="1"/>
       <c r="AB671" s="1"/>
     </row>
-    <row r="672" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -21094,7 +21128,7 @@
       <c r="AA672" s="1"/>
       <c r="AB672" s="1"/>
     </row>
-    <row r="673" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -21124,7 +21158,7 @@
       <c r="AA673" s="1"/>
       <c r="AB673" s="1"/>
     </row>
-    <row r="674" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -21154,7 +21188,7 @@
       <c r="AA674" s="1"/>
       <c r="AB674" s="1"/>
     </row>
-    <row r="675" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -21184,7 +21218,7 @@
       <c r="AA675" s="1"/>
       <c r="AB675" s="1"/>
     </row>
-    <row r="676" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -21214,7 +21248,7 @@
       <c r="AA676" s="1"/>
       <c r="AB676" s="1"/>
     </row>
-    <row r="677" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -21244,7 +21278,7 @@
       <c r="AA677" s="1"/>
       <c r="AB677" s="1"/>
     </row>
-    <row r="678" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -21274,7 +21308,7 @@
       <c r="AA678" s="1"/>
       <c r="AB678" s="1"/>
     </row>
-    <row r="679" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -21304,7 +21338,7 @@
       <c r="AA679" s="1"/>
       <c r="AB679" s="1"/>
     </row>
-    <row r="680" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -21334,7 +21368,7 @@
       <c r="AA680" s="1"/>
       <c r="AB680" s="1"/>
     </row>
-    <row r="681" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -21364,7 +21398,7 @@
       <c r="AA681" s="1"/>
       <c r="AB681" s="1"/>
     </row>
-    <row r="682" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -21394,7 +21428,7 @@
       <c r="AA682" s="1"/>
       <c r="AB682" s="1"/>
     </row>
-    <row r="683" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -21424,7 +21458,7 @@
       <c r="AA683" s="1"/>
       <c r="AB683" s="1"/>
     </row>
-    <row r="684" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -21454,7 +21488,7 @@
       <c r="AA684" s="1"/>
       <c r="AB684" s="1"/>
     </row>
-    <row r="685" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -21484,7 +21518,7 @@
       <c r="AA685" s="1"/>
       <c r="AB685" s="1"/>
     </row>
-    <row r="686" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -21514,7 +21548,7 @@
       <c r="AA686" s="1"/>
       <c r="AB686" s="1"/>
     </row>
-    <row r="687" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -21544,7 +21578,7 @@
       <c r="AA687" s="1"/>
       <c r="AB687" s="1"/>
     </row>
-    <row r="688" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -21574,7 +21608,7 @@
       <c r="AA688" s="1"/>
       <c r="AB688" s="1"/>
     </row>
-    <row r="689" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -21604,7 +21638,7 @@
       <c r="AA689" s="1"/>
       <c r="AB689" s="1"/>
     </row>
-    <row r="690" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -21634,7 +21668,7 @@
       <c r="AA690" s="1"/>
       <c r="AB690" s="1"/>
     </row>
-    <row r="691" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -21664,7 +21698,7 @@
       <c r="AA691" s="1"/>
       <c r="AB691" s="1"/>
     </row>
-    <row r="692" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -21694,7 +21728,7 @@
       <c r="AA692" s="1"/>
       <c r="AB692" s="1"/>
     </row>
-    <row r="693" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -21724,7 +21758,7 @@
       <c r="AA693" s="1"/>
       <c r="AB693" s="1"/>
     </row>
-    <row r="694" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -21754,7 +21788,7 @@
       <c r="AA694" s="1"/>
       <c r="AB694" s="1"/>
     </row>
-    <row r="695" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -21784,7 +21818,7 @@
       <c r="AA695" s="1"/>
       <c r="AB695" s="1"/>
     </row>
-    <row r="696" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -21814,7 +21848,7 @@
       <c r="AA696" s="1"/>
       <c r="AB696" s="1"/>
     </row>
-    <row r="697" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -21844,7 +21878,7 @@
       <c r="AA697" s="1"/>
       <c r="AB697" s="1"/>
     </row>
-    <row r="698" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -21874,7 +21908,7 @@
       <c r="AA698" s="1"/>
       <c r="AB698" s="1"/>
     </row>
-    <row r="699" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -21904,7 +21938,7 @@
       <c r="AA699" s="1"/>
       <c r="AB699" s="1"/>
     </row>
-    <row r="700" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -21934,7 +21968,7 @@
       <c r="AA700" s="1"/>
       <c r="AB700" s="1"/>
     </row>
-    <row r="701" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -21964,7 +21998,7 @@
       <c r="AA701" s="1"/>
       <c r="AB701" s="1"/>
     </row>
-    <row r="702" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -21994,7 +22028,7 @@
       <c r="AA702" s="1"/>
       <c r="AB702" s="1"/>
     </row>
-    <row r="703" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -22024,7 +22058,7 @@
       <c r="AA703" s="1"/>
       <c r="AB703" s="1"/>
     </row>
-    <row r="704" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -22054,7 +22088,7 @@
       <c r="AA704" s="1"/>
       <c r="AB704" s="1"/>
     </row>
-    <row r="705" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -22084,7 +22118,7 @@
       <c r="AA705" s="1"/>
       <c r="AB705" s="1"/>
     </row>
-    <row r="706" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -22114,7 +22148,7 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
-    <row r="707" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -22144,7 +22178,7 @@
       <c r="AA707" s="1"/>
       <c r="AB707" s="1"/>
     </row>
-    <row r="708" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -22174,7 +22208,7 @@
       <c r="AA708" s="1"/>
       <c r="AB708" s="1"/>
     </row>
-    <row r="709" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -22204,7 +22238,7 @@
       <c r="AA709" s="1"/>
       <c r="AB709" s="1"/>
     </row>
-    <row r="710" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -22234,7 +22268,7 @@
       <c r="AA710" s="1"/>
       <c r="AB710" s="1"/>
     </row>
-    <row r="711" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -22264,7 +22298,7 @@
       <c r="AA711" s="1"/>
       <c r="AB711" s="1"/>
     </row>
-    <row r="712" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -22294,7 +22328,7 @@
       <c r="AA712" s="1"/>
       <c r="AB712" s="1"/>
     </row>
-    <row r="713" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -22324,7 +22358,7 @@
       <c r="AA713" s="1"/>
       <c r="AB713" s="1"/>
     </row>
-    <row r="714" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -22354,7 +22388,7 @@
       <c r="AA714" s="1"/>
       <c r="AB714" s="1"/>
     </row>
-    <row r="715" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -22384,7 +22418,7 @@
       <c r="AA715" s="1"/>
       <c r="AB715" s="1"/>
     </row>
-    <row r="716" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -22414,7 +22448,7 @@
       <c r="AA716" s="1"/>
       <c r="AB716" s="1"/>
     </row>
-    <row r="717" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -22444,7 +22478,7 @@
       <c r="AA717" s="1"/>
       <c r="AB717" s="1"/>
     </row>
-    <row r="718" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -22474,7 +22508,7 @@
       <c r="AA718" s="1"/>
       <c r="AB718" s="1"/>
     </row>
-    <row r="719" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -22504,7 +22538,7 @@
       <c r="AA719" s="1"/>
       <c r="AB719" s="1"/>
     </row>
-    <row r="720" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -22534,7 +22568,7 @@
       <c r="AA720" s="1"/>
       <c r="AB720" s="1"/>
     </row>
-    <row r="721" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -22564,7 +22598,7 @@
       <c r="AA721" s="1"/>
       <c r="AB721" s="1"/>
     </row>
-    <row r="722" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -22594,7 +22628,7 @@
       <c r="AA722" s="1"/>
       <c r="AB722" s="1"/>
     </row>
-    <row r="723" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -22624,7 +22658,7 @@
       <c r="AA723" s="1"/>
       <c r="AB723" s="1"/>
     </row>
-    <row r="724" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -22654,7 +22688,7 @@
       <c r="AA724" s="1"/>
       <c r="AB724" s="1"/>
     </row>
-    <row r="725" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -22684,7 +22718,7 @@
       <c r="AA725" s="1"/>
       <c r="AB725" s="1"/>
     </row>
-    <row r="726" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -22714,7 +22748,7 @@
       <c r="AA726" s="1"/>
       <c r="AB726" s="1"/>
     </row>
-    <row r="727" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -22744,7 +22778,7 @@
       <c r="AA727" s="1"/>
       <c r="AB727" s="1"/>
     </row>
-    <row r="728" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -22774,7 +22808,7 @@
       <c r="AA728" s="1"/>
       <c r="AB728" s="1"/>
     </row>
-    <row r="729" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -22804,7 +22838,7 @@
       <c r="AA729" s="1"/>
       <c r="AB729" s="1"/>
     </row>
-    <row r="730" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -22834,7 +22868,7 @@
       <c r="AA730" s="1"/>
       <c r="AB730" s="1"/>
     </row>
-    <row r="731" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -22864,7 +22898,7 @@
       <c r="AA731" s="1"/>
       <c r="AB731" s="1"/>
     </row>
-    <row r="732" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -22894,7 +22928,7 @@
       <c r="AA732" s="1"/>
       <c r="AB732" s="1"/>
     </row>
-    <row r="733" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -22924,7 +22958,7 @@
       <c r="AA733" s="1"/>
       <c r="AB733" s="1"/>
     </row>
-    <row r="734" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -22954,7 +22988,7 @@
       <c r="AA734" s="1"/>
       <c r="AB734" s="1"/>
     </row>
-    <row r="735" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -22984,7 +23018,7 @@
       <c r="AA735" s="1"/>
       <c r="AB735" s="1"/>
     </row>
-    <row r="736" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -23014,7 +23048,7 @@
       <c r="AA736" s="1"/>
       <c r="AB736" s="1"/>
     </row>
-    <row r="737" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -23044,7 +23078,7 @@
       <c r="AA737" s="1"/>
       <c r="AB737" s="1"/>
     </row>
-    <row r="738" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -23074,7 +23108,7 @@
       <c r="AA738" s="1"/>
       <c r="AB738" s="1"/>
     </row>
-    <row r="739" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -23104,7 +23138,7 @@
       <c r="AA739" s="1"/>
       <c r="AB739" s="1"/>
     </row>
-    <row r="740" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -23134,7 +23168,7 @@
       <c r="AA740" s="1"/>
       <c r="AB740" s="1"/>
     </row>
-    <row r="741" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -23164,7 +23198,7 @@
       <c r="AA741" s="1"/>
       <c r="AB741" s="1"/>
     </row>
-    <row r="742" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -23194,7 +23228,7 @@
       <c r="AA742" s="1"/>
       <c r="AB742" s="1"/>
     </row>
-    <row r="743" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -23224,7 +23258,7 @@
       <c r="AA743" s="1"/>
       <c r="AB743" s="1"/>
     </row>
-    <row r="744" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -23254,7 +23288,7 @@
       <c r="AA744" s="1"/>
       <c r="AB744" s="1"/>
     </row>
-    <row r="745" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -23284,7 +23318,7 @@
       <c r="AA745" s="1"/>
       <c r="AB745" s="1"/>
     </row>
-    <row r="746" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -23314,7 +23348,7 @@
       <c r="AA746" s="1"/>
       <c r="AB746" s="1"/>
     </row>
-    <row r="747" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -23344,7 +23378,7 @@
       <c r="AA747" s="1"/>
       <c r="AB747" s="1"/>
     </row>
-    <row r="748" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -23374,7 +23408,7 @@
       <c r="AA748" s="1"/>
       <c r="AB748" s="1"/>
     </row>
-    <row r="749" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -23404,7 +23438,7 @@
       <c r="AA749" s="1"/>
       <c r="AB749" s="1"/>
     </row>
-    <row r="750" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -23434,7 +23468,7 @@
       <c r="AA750" s="1"/>
       <c r="AB750" s="1"/>
     </row>
-    <row r="751" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -23464,7 +23498,7 @@
       <c r="AA751" s="1"/>
       <c r="AB751" s="1"/>
     </row>
-    <row r="752" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -23494,7 +23528,7 @@
       <c r="AA752" s="1"/>
       <c r="AB752" s="1"/>
     </row>
-    <row r="753" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -23524,7 +23558,7 @@
       <c r="AA753" s="1"/>
       <c r="AB753" s="1"/>
     </row>
-    <row r="754" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -23554,7 +23588,7 @@
       <c r="AA754" s="1"/>
       <c r="AB754" s="1"/>
     </row>
-    <row r="755" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -23584,7 +23618,7 @@
       <c r="AA755" s="1"/>
       <c r="AB755" s="1"/>
     </row>
-    <row r="756" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -23614,7 +23648,7 @@
       <c r="AA756" s="1"/>
       <c r="AB756" s="1"/>
     </row>
-    <row r="757" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -23644,7 +23678,7 @@
       <c r="AA757" s="1"/>
       <c r="AB757" s="1"/>
     </row>
-    <row r="758" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -23674,7 +23708,7 @@
       <c r="AA758" s="1"/>
       <c r="AB758" s="1"/>
     </row>
-    <row r="759" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -23704,7 +23738,7 @@
       <c r="AA759" s="1"/>
       <c r="AB759" s="1"/>
     </row>
-    <row r="760" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -23734,7 +23768,7 @@
       <c r="AA760" s="1"/>
       <c r="AB760" s="1"/>
     </row>
-    <row r="761" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -23764,7 +23798,7 @@
       <c r="AA761" s="1"/>
       <c r="AB761" s="1"/>
     </row>
-    <row r="762" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -23794,7 +23828,7 @@
       <c r="AA762" s="1"/>
       <c r="AB762" s="1"/>
     </row>
-    <row r="763" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -23824,7 +23858,7 @@
       <c r="AA763" s="1"/>
       <c r="AB763" s="1"/>
     </row>
-    <row r="764" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -23854,7 +23888,7 @@
       <c r="AA764" s="1"/>
       <c r="AB764" s="1"/>
     </row>
-    <row r="765" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -23884,7 +23918,7 @@
       <c r="AA765" s="1"/>
       <c r="AB765" s="1"/>
     </row>
-    <row r="766" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -23914,7 +23948,7 @@
       <c r="AA766" s="1"/>
       <c r="AB766" s="1"/>
     </row>
-    <row r="767" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -23944,7 +23978,7 @@
       <c r="AA767" s="1"/>
       <c r="AB767" s="1"/>
     </row>
-    <row r="768" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -23974,7 +24008,7 @@
       <c r="AA768" s="1"/>
       <c r="AB768" s="1"/>
     </row>
-    <row r="769" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -24004,7 +24038,7 @@
       <c r="AA769" s="1"/>
       <c r="AB769" s="1"/>
     </row>
-    <row r="770" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -24034,7 +24068,7 @@
       <c r="AA770" s="1"/>
       <c r="AB770" s="1"/>
     </row>
-    <row r="771" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -24064,7 +24098,7 @@
       <c r="AA771" s="1"/>
       <c r="AB771" s="1"/>
     </row>
-    <row r="772" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -24094,7 +24128,7 @@
       <c r="AA772" s="1"/>
       <c r="AB772" s="1"/>
     </row>
-    <row r="773" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -24124,7 +24158,7 @@
       <c r="AA773" s="1"/>
       <c r="AB773" s="1"/>
     </row>
-    <row r="774" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -24154,7 +24188,7 @@
       <c r="AA774" s="1"/>
       <c r="AB774" s="1"/>
     </row>
-    <row r="775" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -24184,7 +24218,7 @@
       <c r="AA775" s="1"/>
       <c r="AB775" s="1"/>
     </row>
-    <row r="776" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -24214,7 +24248,7 @@
       <c r="AA776" s="1"/>
       <c r="AB776" s="1"/>
     </row>
-    <row r="777" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -24244,7 +24278,7 @@
       <c r="AA777" s="1"/>
       <c r="AB777" s="1"/>
     </row>
-    <row r="778" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -24274,7 +24308,7 @@
       <c r="AA778" s="1"/>
       <c r="AB778" s="1"/>
     </row>
-    <row r="779" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -24304,7 +24338,7 @@
       <c r="AA779" s="1"/>
       <c r="AB779" s="1"/>
     </row>
-    <row r="780" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -24334,7 +24368,7 @@
       <c r="AA780" s="1"/>
       <c r="AB780" s="1"/>
     </row>
-    <row r="781" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -24364,7 +24398,7 @@
       <c r="AA781" s="1"/>
       <c r="AB781" s="1"/>
     </row>
-    <row r="782" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -24394,7 +24428,7 @@
       <c r="AA782" s="1"/>
       <c r="AB782" s="1"/>
     </row>
-    <row r="783" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -24424,7 +24458,7 @@
       <c r="AA783" s="1"/>
       <c r="AB783" s="1"/>
     </row>
-    <row r="784" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -24454,7 +24488,7 @@
       <c r="AA784" s="1"/>
       <c r="AB784" s="1"/>
     </row>
-    <row r="785" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -24484,7 +24518,7 @@
       <c r="AA785" s="1"/>
       <c r="AB785" s="1"/>
     </row>
-    <row r="786" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -24514,7 +24548,7 @@
       <c r="AA786" s="1"/>
       <c r="AB786" s="1"/>
     </row>
-    <row r="787" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -24544,7 +24578,7 @@
       <c r="AA787" s="1"/>
       <c r="AB787" s="1"/>
     </row>
-    <row r="788" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -24574,7 +24608,7 @@
       <c r="AA788" s="1"/>
       <c r="AB788" s="1"/>
     </row>
-    <row r="789" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -24604,7 +24638,7 @@
       <c r="AA789" s="1"/>
       <c r="AB789" s="1"/>
     </row>
-    <row r="790" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -24634,7 +24668,7 @@
       <c r="AA790" s="1"/>
       <c r="AB790" s="1"/>
     </row>
-    <row r="791" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -24664,7 +24698,7 @@
       <c r="AA791" s="1"/>
       <c r="AB791" s="1"/>
     </row>
-    <row r="792" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -24694,7 +24728,7 @@
       <c r="AA792" s="1"/>
       <c r="AB792" s="1"/>
     </row>
-    <row r="793" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -24724,7 +24758,7 @@
       <c r="AA793" s="1"/>
       <c r="AB793" s="1"/>
     </row>
-    <row r="794" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -24754,7 +24788,7 @@
       <c r="AA794" s="1"/>
       <c r="AB794" s="1"/>
     </row>
-    <row r="795" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -24784,7 +24818,7 @@
       <c r="AA795" s="1"/>
       <c r="AB795" s="1"/>
     </row>
-    <row r="796" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -24814,7 +24848,7 @@
       <c r="AA796" s="1"/>
       <c r="AB796" s="1"/>
     </row>
-    <row r="797" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -24844,7 +24878,7 @@
       <c r="AA797" s="1"/>
       <c r="AB797" s="1"/>
     </row>
-    <row r="798" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -24874,7 +24908,7 @@
       <c r="AA798" s="1"/>
       <c r="AB798" s="1"/>
     </row>
-    <row r="799" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -24904,7 +24938,7 @@
       <c r="AA799" s="1"/>
       <c r="AB799" s="1"/>
     </row>
-    <row r="800" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -24934,7 +24968,7 @@
       <c r="AA800" s="1"/>
       <c r="AB800" s="1"/>
     </row>
-    <row r="801" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -24964,7 +24998,7 @@
       <c r="AA801" s="1"/>
       <c r="AB801" s="1"/>
     </row>
-    <row r="802" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -24994,7 +25028,7 @@
       <c r="AA802" s="1"/>
       <c r="AB802" s="1"/>
     </row>
-    <row r="803" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -25024,7 +25058,7 @@
       <c r="AA803" s="1"/>
       <c r="AB803" s="1"/>
     </row>
-    <row r="804" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -25054,7 +25088,7 @@
       <c r="AA804" s="1"/>
       <c r="AB804" s="1"/>
     </row>
-    <row r="805" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -25084,7 +25118,7 @@
       <c r="AA805" s="1"/>
       <c r="AB805" s="1"/>
     </row>
-    <row r="806" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -25114,7 +25148,7 @@
       <c r="AA806" s="1"/>
       <c r="AB806" s="1"/>
     </row>
-    <row r="807" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -25144,7 +25178,7 @@
       <c r="AA807" s="1"/>
       <c r="AB807" s="1"/>
     </row>
-    <row r="808" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -25174,7 +25208,7 @@
       <c r="AA808" s="1"/>
       <c r="AB808" s="1"/>
     </row>
-    <row r="809" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -25204,7 +25238,7 @@
       <c r="AA809" s="1"/>
       <c r="AB809" s="1"/>
     </row>
-    <row r="810" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -25234,7 +25268,7 @@
       <c r="AA810" s="1"/>
       <c r="AB810" s="1"/>
     </row>
-    <row r="811" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -25264,7 +25298,7 @@
       <c r="AA811" s="1"/>
       <c r="AB811" s="1"/>
     </row>
-    <row r="812" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -25294,7 +25328,7 @@
       <c r="AA812" s="1"/>
       <c r="AB812" s="1"/>
     </row>
-    <row r="813" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -25324,7 +25358,7 @@
       <c r="AA813" s="1"/>
       <c r="AB813" s="1"/>
     </row>
-    <row r="814" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -25354,7 +25388,7 @@
       <c r="AA814" s="1"/>
       <c r="AB814" s="1"/>
     </row>
-    <row r="815" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -25384,7 +25418,7 @@
       <c r="AA815" s="1"/>
       <c r="AB815" s="1"/>
     </row>
-    <row r="816" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -25414,7 +25448,7 @@
       <c r="AA816" s="1"/>
       <c r="AB816" s="1"/>
     </row>
-    <row r="817" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -25444,7 +25478,7 @@
       <c r="AA817" s="1"/>
       <c r="AB817" s="1"/>
     </row>
-    <row r="818" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -25474,7 +25508,7 @@
       <c r="AA818" s="1"/>
       <c r="AB818" s="1"/>
     </row>
-    <row r="819" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -25504,7 +25538,7 @@
       <c r="AA819" s="1"/>
       <c r="AB819" s="1"/>
     </row>
-    <row r="820" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -25534,7 +25568,7 @@
       <c r="AA820" s="1"/>
       <c r="AB820" s="1"/>
     </row>
-    <row r="821" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -25564,7 +25598,7 @@
       <c r="AA821" s="1"/>
       <c r="AB821" s="1"/>
     </row>
-    <row r="822" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -25594,7 +25628,7 @@
       <c r="AA822" s="1"/>
       <c r="AB822" s="1"/>
     </row>
-    <row r="823" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -25624,7 +25658,7 @@
       <c r="AA823" s="1"/>
       <c r="AB823" s="1"/>
     </row>
-    <row r="824" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -25654,7 +25688,7 @@
       <c r="AA824" s="1"/>
       <c r="AB824" s="1"/>
     </row>
-    <row r="825" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -25684,7 +25718,7 @@
       <c r="AA825" s="1"/>
       <c r="AB825" s="1"/>
     </row>
-    <row r="826" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -25714,7 +25748,7 @@
       <c r="AA826" s="1"/>
       <c r="AB826" s="1"/>
     </row>
-    <row r="827" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -25744,7 +25778,7 @@
       <c r="AA827" s="1"/>
       <c r="AB827" s="1"/>
     </row>
-    <row r="828" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -25774,7 +25808,7 @@
       <c r="AA828" s="1"/>
       <c r="AB828" s="1"/>
     </row>
-    <row r="829" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -25804,7 +25838,7 @@
       <c r="AA829" s="1"/>
       <c r="AB829" s="1"/>
     </row>
-    <row r="830" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -25834,7 +25868,7 @@
       <c r="AA830" s="1"/>
       <c r="AB830" s="1"/>
     </row>
-    <row r="831" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -25864,7 +25898,7 @@
       <c r="AA831" s="1"/>
       <c r="AB831" s="1"/>
     </row>
-    <row r="832" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -25894,7 +25928,7 @@
       <c r="AA832" s="1"/>
       <c r="AB832" s="1"/>
     </row>
-    <row r="833" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -25924,7 +25958,7 @@
       <c r="AA833" s="1"/>
       <c r="AB833" s="1"/>
     </row>
-    <row r="834" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -25954,7 +25988,7 @@
       <c r="AA834" s="1"/>
       <c r="AB834" s="1"/>
     </row>
-    <row r="835" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -25984,7 +26018,7 @@
       <c r="AA835" s="1"/>
       <c r="AB835" s="1"/>
     </row>
-    <row r="836" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -26014,7 +26048,7 @@
       <c r="AA836" s="1"/>
       <c r="AB836" s="1"/>
     </row>
-    <row r="837" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -26044,7 +26078,7 @@
       <c r="AA837" s="1"/>
       <c r="AB837" s="1"/>
     </row>
-    <row r="838" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -26074,7 +26108,7 @@
       <c r="AA838" s="1"/>
       <c r="AB838" s="1"/>
     </row>
-    <row r="839" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -26104,7 +26138,7 @@
       <c r="AA839" s="1"/>
       <c r="AB839" s="1"/>
     </row>
-    <row r="840" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -26134,7 +26168,7 @@
       <c r="AA840" s="1"/>
       <c r="AB840" s="1"/>
     </row>
-    <row r="841" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -26164,7 +26198,7 @@
       <c r="AA841" s="1"/>
       <c r="AB841" s="1"/>
     </row>
-    <row r="842" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -26194,7 +26228,7 @@
       <c r="AA842" s="1"/>
       <c r="AB842" s="1"/>
     </row>
-    <row r="843" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -26224,7 +26258,7 @@
       <c r="AA843" s="1"/>
       <c r="AB843" s="1"/>
     </row>
-    <row r="844" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -26254,7 +26288,7 @@
       <c r="AA844" s="1"/>
       <c r="AB844" s="1"/>
     </row>
-    <row r="845" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -26284,7 +26318,7 @@
       <c r="AA845" s="1"/>
       <c r="AB845" s="1"/>
     </row>
-    <row r="846" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -26314,7 +26348,7 @@
       <c r="AA846" s="1"/>
       <c r="AB846" s="1"/>
     </row>
-    <row r="847" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -26344,7 +26378,7 @@
       <c r="AA847" s="1"/>
       <c r="AB847" s="1"/>
     </row>
-    <row r="848" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -26374,7 +26408,7 @@
       <c r="AA848" s="1"/>
       <c r="AB848" s="1"/>
     </row>
-    <row r="849" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -26404,7 +26438,7 @@
       <c r="AA849" s="1"/>
       <c r="AB849" s="1"/>
     </row>
-    <row r="850" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -26434,7 +26468,7 @@
       <c r="AA850" s="1"/>
       <c r="AB850" s="1"/>
     </row>
-    <row r="851" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -26464,7 +26498,7 @@
       <c r="AA851" s="1"/>
       <c r="AB851" s="1"/>
     </row>
-    <row r="852" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -26494,7 +26528,7 @@
       <c r="AA852" s="1"/>
       <c r="AB852" s="1"/>
     </row>
-    <row r="853" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -26524,7 +26558,7 @@
       <c r="AA853" s="1"/>
       <c r="AB853" s="1"/>
     </row>
-    <row r="854" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -26554,7 +26588,7 @@
       <c r="AA854" s="1"/>
       <c r="AB854" s="1"/>
     </row>
-    <row r="855" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -26584,7 +26618,7 @@
       <c r="AA855" s="1"/>
       <c r="AB855" s="1"/>
     </row>
-    <row r="856" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -26614,7 +26648,7 @@
       <c r="AA856" s="1"/>
       <c r="AB856" s="1"/>
     </row>
-    <row r="857" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -26644,7 +26678,7 @@
       <c r="AA857" s="1"/>
       <c r="AB857" s="1"/>
     </row>
-    <row r="858" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -26674,7 +26708,7 @@
       <c r="AA858" s="1"/>
       <c r="AB858" s="1"/>
     </row>
-    <row r="859" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -26704,7 +26738,7 @@
       <c r="AA859" s="1"/>
       <c r="AB859" s="1"/>
     </row>
-    <row r="860" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -26734,7 +26768,7 @@
       <c r="AA860" s="1"/>
       <c r="AB860" s="1"/>
     </row>
-    <row r="861" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -26764,7 +26798,7 @@
       <c r="AA861" s="1"/>
       <c r="AB861" s="1"/>
     </row>
-    <row r="862" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -26794,7 +26828,7 @@
       <c r="AA862" s="1"/>
       <c r="AB862" s="1"/>
     </row>
-    <row r="863" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -26824,7 +26858,7 @@
       <c r="AA863" s="1"/>
       <c r="AB863" s="1"/>
     </row>
-    <row r="864" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -26854,7 +26888,7 @@
       <c r="AA864" s="1"/>
       <c r="AB864" s="1"/>
     </row>
-    <row r="865" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -26884,7 +26918,7 @@
       <c r="AA865" s="1"/>
       <c r="AB865" s="1"/>
     </row>
-    <row r="866" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -26914,7 +26948,7 @@
       <c r="AA866" s="1"/>
       <c r="AB866" s="1"/>
     </row>
-    <row r="867" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -26944,7 +26978,7 @@
       <c r="AA867" s="1"/>
       <c r="AB867" s="1"/>
     </row>
-    <row r="868" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -26974,7 +27008,7 @@
       <c r="AA868" s="1"/>
       <c r="AB868" s="1"/>
     </row>
-    <row r="869" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -27004,7 +27038,7 @@
       <c r="AA869" s="1"/>
       <c r="AB869" s="1"/>
     </row>
-    <row r="870" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -27034,7 +27068,7 @@
       <c r="AA870" s="1"/>
       <c r="AB870" s="1"/>
     </row>
-    <row r="871" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -27064,7 +27098,7 @@
       <c r="AA871" s="1"/>
       <c r="AB871" s="1"/>
     </row>
-    <row r="872" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -27094,7 +27128,7 @@
       <c r="AA872" s="1"/>
       <c r="AB872" s="1"/>
     </row>
-    <row r="873" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -27124,7 +27158,7 @@
       <c r="AA873" s="1"/>
       <c r="AB873" s="1"/>
     </row>
-    <row r="874" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -27154,7 +27188,7 @@
       <c r="AA874" s="1"/>
       <c r="AB874" s="1"/>
     </row>
-    <row r="875" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -27184,7 +27218,7 @@
       <c r="AA875" s="1"/>
       <c r="AB875" s="1"/>
     </row>
-    <row r="876" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -27214,7 +27248,7 @@
       <c r="AA876" s="1"/>
       <c r="AB876" s="1"/>
     </row>
-    <row r="877" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -27244,7 +27278,7 @@
       <c r="AA877" s="1"/>
       <c r="AB877" s="1"/>
     </row>
-    <row r="878" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -27274,7 +27308,7 @@
       <c r="AA878" s="1"/>
       <c r="AB878" s="1"/>
     </row>
-    <row r="879" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -27304,7 +27338,7 @@
       <c r="AA879" s="1"/>
       <c r="AB879" s="1"/>
     </row>
-    <row r="880" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -27334,7 +27368,7 @@
       <c r="AA880" s="1"/>
       <c r="AB880" s="1"/>
     </row>
-    <row r="881" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -27364,7 +27398,7 @@
       <c r="AA881" s="1"/>
       <c r="AB881" s="1"/>
     </row>
-    <row r="882" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -27394,7 +27428,7 @@
       <c r="AA882" s="1"/>
       <c r="AB882" s="1"/>
     </row>
-    <row r="883" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -27424,7 +27458,7 @@
       <c r="AA883" s="1"/>
       <c r="AB883" s="1"/>
     </row>
-    <row r="884" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -27454,7 +27488,7 @@
       <c r="AA884" s="1"/>
       <c r="AB884" s="1"/>
     </row>
-    <row r="885" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -27484,7 +27518,7 @@
       <c r="AA885" s="1"/>
       <c r="AB885" s="1"/>
     </row>
-    <row r="886" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -27514,7 +27548,7 @@
       <c r="AA886" s="1"/>
       <c r="AB886" s="1"/>
     </row>
-    <row r="887" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -27544,7 +27578,7 @@
       <c r="AA887" s="1"/>
       <c r="AB887" s="1"/>
     </row>
-    <row r="888" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -27574,7 +27608,7 @@
       <c r="AA888" s="1"/>
       <c r="AB888" s="1"/>
     </row>
-    <row r="889" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -27604,7 +27638,7 @@
       <c r="AA889" s="1"/>
       <c r="AB889" s="1"/>
     </row>
-    <row r="890" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -27634,7 +27668,7 @@
       <c r="AA890" s="1"/>
       <c r="AB890" s="1"/>
     </row>
-    <row r="891" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -27664,7 +27698,7 @@
       <c r="AA891" s="1"/>
       <c r="AB891" s="1"/>
     </row>
-    <row r="892" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -27694,7 +27728,7 @@
       <c r="AA892" s="1"/>
       <c r="AB892" s="1"/>
     </row>
-    <row r="893" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -27724,7 +27758,7 @@
       <c r="AA893" s="1"/>
       <c r="AB893" s="1"/>
     </row>
-    <row r="894" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -27754,7 +27788,7 @@
       <c r="AA894" s="1"/>
       <c r="AB894" s="1"/>
     </row>
-    <row r="895" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -27784,7 +27818,7 @@
       <c r="AA895" s="1"/>
       <c r="AB895" s="1"/>
     </row>
-    <row r="896" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -27814,7 +27848,7 @@
       <c r="AA896" s="1"/>
       <c r="AB896" s="1"/>
     </row>
-    <row r="897" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -27844,7 +27878,7 @@
       <c r="AA897" s="1"/>
       <c r="AB897" s="1"/>
     </row>
-    <row r="898" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -27874,7 +27908,7 @@
       <c r="AA898" s="1"/>
       <c r="AB898" s="1"/>
     </row>
-    <row r="899" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -27904,7 +27938,7 @@
       <c r="AA899" s="1"/>
       <c r="AB899" s="1"/>
     </row>
-    <row r="900" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -27934,7 +27968,7 @@
       <c r="AA900" s="1"/>
       <c r="AB900" s="1"/>
     </row>
-    <row r="901" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -27964,7 +27998,7 @@
       <c r="AA901" s="1"/>
       <c r="AB901" s="1"/>
     </row>
-    <row r="902" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -27994,7 +28028,7 @@
       <c r="AA902" s="1"/>
       <c r="AB902" s="1"/>
     </row>
-    <row r="903" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -28024,7 +28058,7 @@
       <c r="AA903" s="1"/>
       <c r="AB903" s="1"/>
     </row>
-    <row r="904" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -28054,7 +28088,7 @@
       <c r="AA904" s="1"/>
       <c r="AB904" s="1"/>
     </row>
-    <row r="905" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -28084,7 +28118,7 @@
       <c r="AA905" s="1"/>
       <c r="AB905" s="1"/>
     </row>
-    <row r="906" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -28114,7 +28148,7 @@
       <c r="AA906" s="1"/>
       <c r="AB906" s="1"/>
     </row>
-    <row r="907" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -28144,7 +28178,7 @@
       <c r="AA907" s="1"/>
       <c r="AB907" s="1"/>
     </row>
-    <row r="908" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -28174,7 +28208,7 @@
       <c r="AA908" s="1"/>
       <c r="AB908" s="1"/>
     </row>
-    <row r="909" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -28204,7 +28238,7 @@
       <c r="AA909" s="1"/>
       <c r="AB909" s="1"/>
     </row>
-    <row r="910" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -28234,7 +28268,7 @@
       <c r="AA910" s="1"/>
       <c r="AB910" s="1"/>
     </row>
-    <row r="911" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -28264,7 +28298,7 @@
       <c r="AA911" s="1"/>
       <c r="AB911" s="1"/>
     </row>
-    <row r="912" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -28294,7 +28328,7 @@
       <c r="AA912" s="1"/>
       <c r="AB912" s="1"/>
     </row>
-    <row r="913" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -28324,7 +28358,7 @@
       <c r="AA913" s="1"/>
       <c r="AB913" s="1"/>
     </row>
-    <row r="914" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -28354,7 +28388,7 @@
       <c r="AA914" s="1"/>
       <c r="AB914" s="1"/>
     </row>
-    <row r="915" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -28384,7 +28418,7 @@
       <c r="AA915" s="1"/>
       <c r="AB915" s="1"/>
     </row>
-    <row r="916" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -28414,7 +28448,7 @@
       <c r="AA916" s="1"/>
       <c r="AB916" s="1"/>
     </row>
-    <row r="917" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -28444,7 +28478,7 @@
       <c r="AA917" s="1"/>
       <c r="AB917" s="1"/>
     </row>
-    <row r="918" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -28474,7 +28508,7 @@
       <c r="AA918" s="1"/>
       <c r="AB918" s="1"/>
     </row>
-    <row r="919" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -28504,7 +28538,7 @@
       <c r="AA919" s="1"/>
       <c r="AB919" s="1"/>
     </row>
-    <row r="920" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -28534,7 +28568,7 @@
       <c r="AA920" s="1"/>
       <c r="AB920" s="1"/>
     </row>
-    <row r="921" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -28564,7 +28598,7 @@
       <c r="AA921" s="1"/>
       <c r="AB921" s="1"/>
     </row>
-    <row r="922" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -28594,7 +28628,7 @@
       <c r="AA922" s="1"/>
       <c r="AB922" s="1"/>
     </row>
-    <row r="923" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -28624,7 +28658,7 @@
       <c r="AA923" s="1"/>
       <c r="AB923" s="1"/>
     </row>
-    <row r="924" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -28654,7 +28688,7 @@
       <c r="AA924" s="1"/>
       <c r="AB924" s="1"/>
     </row>
-    <row r="925" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -28684,7 +28718,7 @@
       <c r="AA925" s="1"/>
       <c r="AB925" s="1"/>
     </row>
-    <row r="926" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -28714,7 +28748,7 @@
       <c r="AA926" s="1"/>
       <c r="AB926" s="1"/>
     </row>
-    <row r="927" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -28744,7 +28778,7 @@
       <c r="AA927" s="1"/>
       <c r="AB927" s="1"/>
     </row>
-    <row r="928" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -28774,7 +28808,7 @@
       <c r="AA928" s="1"/>
       <c r="AB928" s="1"/>
     </row>
-    <row r="929" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -28804,7 +28838,7 @@
       <c r="AA929" s="1"/>
       <c r="AB929" s="1"/>
     </row>
-    <row r="930" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -28834,7 +28868,7 @@
       <c r="AA930" s="1"/>
       <c r="AB930" s="1"/>
     </row>
-    <row r="931" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -28864,7 +28898,7 @@
       <c r="AA931" s="1"/>
       <c r="AB931" s="1"/>
     </row>
-    <row r="932" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -28894,7 +28928,7 @@
       <c r="AA932" s="1"/>
       <c r="AB932" s="1"/>
     </row>
-    <row r="933" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -28924,7 +28958,7 @@
       <c r="AA933" s="1"/>
       <c r="AB933" s="1"/>
     </row>
-    <row r="934" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -28954,7 +28988,7 @@
       <c r="AA934" s="1"/>
       <c r="AB934" s="1"/>
     </row>
-    <row r="935" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -28984,7 +29018,7 @@
       <c r="AA935" s="1"/>
       <c r="AB935" s="1"/>
     </row>
-    <row r="936" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -29014,7 +29048,7 @@
       <c r="AA936" s="1"/>
       <c r="AB936" s="1"/>
     </row>
-    <row r="937" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -29044,7 +29078,7 @@
       <c r="AA937" s="1"/>
       <c r="AB937" s="1"/>
     </row>
-    <row r="938" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -29074,7 +29108,7 @@
       <c r="AA938" s="1"/>
       <c r="AB938" s="1"/>
     </row>
-    <row r="939" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -29104,7 +29138,7 @@
       <c r="AA939" s="1"/>
       <c r="AB939" s="1"/>
     </row>
-    <row r="940" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -29134,7 +29168,7 @@
       <c r="AA940" s="1"/>
       <c r="AB940" s="1"/>
     </row>
-    <row r="941" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -29164,7 +29198,7 @@
       <c r="AA941" s="1"/>
       <c r="AB941" s="1"/>
     </row>
-    <row r="942" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -29194,7 +29228,7 @@
       <c r="AA942" s="1"/>
       <c r="AB942" s="1"/>
     </row>
-    <row r="943" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -29224,7 +29258,7 @@
       <c r="AA943" s="1"/>
       <c r="AB943" s="1"/>
     </row>
-    <row r="944" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -29254,7 +29288,7 @@
       <c r="AA944" s="1"/>
       <c r="AB944" s="1"/>
     </row>
-    <row r="945" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -29284,7 +29318,7 @@
       <c r="AA945" s="1"/>
       <c r="AB945" s="1"/>
     </row>
-    <row r="946" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -29314,7 +29348,7 @@
       <c r="AA946" s="1"/>
       <c r="AB946" s="1"/>
     </row>
-    <row r="947" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -29344,7 +29378,7 @@
       <c r="AA947" s="1"/>
       <c r="AB947" s="1"/>
     </row>
-    <row r="948" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -29374,7 +29408,7 @@
       <c r="AA948" s="1"/>
       <c r="AB948" s="1"/>
     </row>
-    <row r="949" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -29404,7 +29438,7 @@
       <c r="AA949" s="1"/>
       <c r="AB949" s="1"/>
     </row>
-    <row r="950" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -29434,7 +29468,7 @@
       <c r="AA950" s="1"/>
       <c r="AB950" s="1"/>
     </row>
-    <row r="951" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -29464,7 +29498,7 @@
       <c r="AA951" s="1"/>
       <c r="AB951" s="1"/>
     </row>
-    <row r="952" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -29494,7 +29528,7 @@
       <c r="AA952" s="1"/>
       <c r="AB952" s="1"/>
     </row>
-    <row r="953" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -29524,7 +29558,7 @@
       <c r="AA953" s="1"/>
       <c r="AB953" s="1"/>
     </row>
-    <row r="954" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -29554,7 +29588,7 @@
       <c r="AA954" s="1"/>
       <c r="AB954" s="1"/>
     </row>
-    <row r="955" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -29584,7 +29618,7 @@
       <c r="AA955" s="1"/>
       <c r="AB955" s="1"/>
     </row>
-    <row r="956" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -29614,7 +29648,7 @@
       <c r="AA956" s="1"/>
       <c r="AB956" s="1"/>
     </row>
-    <row r="957" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -29644,7 +29678,7 @@
       <c r="AA957" s="1"/>
       <c r="AB957" s="1"/>
     </row>
-    <row r="958" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -29674,7 +29708,7 @@
       <c r="AA958" s="1"/>
       <c r="AB958" s="1"/>
     </row>
-    <row r="959" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -29704,7 +29738,7 @@
       <c r="AA959" s="1"/>
       <c r="AB959" s="1"/>
     </row>
-    <row r="960" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -29734,7 +29768,7 @@
       <c r="AA960" s="1"/>
       <c r="AB960" s="1"/>
     </row>
-    <row r="961" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -29764,7 +29798,7 @@
       <c r="AA961" s="1"/>
       <c r="AB961" s="1"/>
     </row>
-    <row r="962" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -29794,7 +29828,7 @@
       <c r="AA962" s="1"/>
       <c r="AB962" s="1"/>
     </row>
-    <row r="963" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -29824,7 +29858,7 @@
       <c r="AA963" s="1"/>
       <c r="AB963" s="1"/>
     </row>
-    <row r="964" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -29854,7 +29888,7 @@
       <c r="AA964" s="1"/>
       <c r="AB964" s="1"/>
     </row>
-    <row r="965" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -29884,7 +29918,7 @@
       <c r="AA965" s="1"/>
       <c r="AB965" s="1"/>
     </row>
-    <row r="966" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -29914,7 +29948,7 @@
       <c r="AA966" s="1"/>
       <c r="AB966" s="1"/>
     </row>
-    <row r="967" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -29944,7 +29978,7 @@
       <c r="AA967" s="1"/>
       <c r="AB967" s="1"/>
     </row>
-    <row r="968" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -29974,7 +30008,7 @@
       <c r="AA968" s="1"/>
       <c r="AB968" s="1"/>
     </row>
-    <row r="969" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -30004,7 +30038,7 @@
       <c r="AA969" s="1"/>
       <c r="AB969" s="1"/>
     </row>
-    <row r="970" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -30034,7 +30068,7 @@
       <c r="AA970" s="1"/>
       <c r="AB970" s="1"/>
     </row>
-    <row r="971" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -30064,7 +30098,7 @@
       <c r="AA971" s="1"/>
       <c r="AB971" s="1"/>
     </row>
-    <row r="972" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -30094,7 +30128,7 @@
       <c r="AA972" s="1"/>
       <c r="AB972" s="1"/>
     </row>
-    <row r="973" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -30124,7 +30158,7 @@
       <c r="AA973" s="1"/>
       <c r="AB973" s="1"/>
     </row>
-    <row r="974" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -30154,7 +30188,7 @@
       <c r="AA974" s="1"/>
       <c r="AB974" s="1"/>
     </row>
-    <row r="975" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -30184,7 +30218,7 @@
       <c r="AA975" s="1"/>
       <c r="AB975" s="1"/>
     </row>
-    <row r="976" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -30214,7 +30248,7 @@
       <c r="AA976" s="1"/>
       <c r="AB976" s="1"/>
     </row>
-    <row r="977" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -30244,7 +30278,7 @@
       <c r="AA977" s="1"/>
       <c r="AB977" s="1"/>
     </row>
-    <row r="978" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -30274,7 +30308,7 @@
       <c r="AA978" s="1"/>
       <c r="AB978" s="1"/>
     </row>
-    <row r="979" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -30304,7 +30338,7 @@
       <c r="AA979" s="1"/>
       <c r="AB979" s="1"/>
     </row>
-    <row r="980" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -30334,7 +30368,7 @@
       <c r="AA980" s="1"/>
       <c r="AB980" s="1"/>
     </row>
-    <row r="981" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -30364,7 +30398,7 @@
       <c r="AA981" s="1"/>
       <c r="AB981" s="1"/>
     </row>
-    <row r="982" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -30394,7 +30428,7 @@
       <c r="AA982" s="1"/>
       <c r="AB982" s="1"/>
     </row>
-    <row r="983" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -30424,7 +30458,7 @@
       <c r="AA983" s="1"/>
       <c r="AB983" s="1"/>
     </row>
-    <row r="984" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -30454,7 +30488,7 @@
       <c r="AA984" s="1"/>
       <c r="AB984" s="1"/>
     </row>
-    <row r="985" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -30484,7 +30518,7 @@
       <c r="AA985" s="1"/>
       <c r="AB985" s="1"/>
     </row>
-    <row r="986" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -30514,7 +30548,7 @@
       <c r="AA986" s="1"/>
       <c r="AB986" s="1"/>
     </row>
-    <row r="987" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -30544,7 +30578,7 @@
       <c r="AA987" s="1"/>
       <c r="AB987" s="1"/>
     </row>
-    <row r="988" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -30574,7 +30608,7 @@
       <c r="AA988" s="1"/>
       <c r="AB988" s="1"/>
     </row>
-    <row r="989" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -30604,7 +30638,7 @@
       <c r="AA989" s="1"/>
       <c r="AB989" s="1"/>
     </row>
-    <row r="990" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -30634,7 +30668,7 @@
       <c r="AA990" s="1"/>
       <c r="AB990" s="1"/>
     </row>
-    <row r="991" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -30664,7 +30698,7 @@
       <c r="AA991" s="1"/>
       <c r="AB991" s="1"/>
     </row>
-    <row r="992" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -30694,7 +30728,7 @@
       <c r="AA992" s="1"/>
       <c r="AB992" s="1"/>
     </row>
-    <row r="993" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -30724,7 +30758,7 @@
       <c r="AA993" s="1"/>
       <c r="AB993" s="1"/>
     </row>
-    <row r="994" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -30754,7 +30788,7 @@
       <c r="AA994" s="1"/>
       <c r="AB994" s="1"/>
     </row>
-    <row r="995" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -30784,7 +30818,7 @@
       <c r="AA995" s="1"/>
       <c r="AB995" s="1"/>
     </row>
-    <row r="996" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -30814,7 +30848,7 @@
       <c r="AA996" s="1"/>
       <c r="AB996" s="1"/>
     </row>
-    <row r="997" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -30844,7 +30878,7 @@
       <c r="AA997" s="1"/>
       <c r="AB997" s="1"/>
     </row>
-    <row r="998" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -30874,7 +30908,7 @@
       <c r="AA998" s="1"/>
       <c r="AB998" s="1"/>
     </row>
-    <row r="999" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -30904,7 +30938,7 @@
       <c r="AA999" s="1"/>
       <c r="AB999" s="1"/>
     </row>
-    <row r="1000" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -30934,7 +30968,7 @@
       <c r="AA1000" s="1"/>
       <c r="AB1000" s="1"/>
     </row>
-    <row r="1001" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#MilestoneParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5834CCF-665E-450B-AE51-D88FCC76B714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94AF5FA-3791-46A4-93F9-3500F7111B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MilestoneParam" sheetId="1" r:id="rId1"/>
@@ -244,7 +244,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -461,15 +461,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AB1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" customWidth="1"/>
+    <col min="10" max="10" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +521,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -573,7 +573,7 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -602,7 +602,7 @@
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -631,7 +631,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="1"/>
@@ -681,7 +681,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1</v>
@@ -696,7 +696,7 @@
         <v>1.25</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -708,7 +708,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4"/>
       <c r="N6" s="1"/>
@@ -727,7 +727,7 @@
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
@@ -742,7 +742,7 @@
         <v>1.25</v>
       </c>
       <c r="G7" s="1">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -754,7 +754,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="4"/>
       <c r="N7" s="1"/>
@@ -773,7 +773,7 @@
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
@@ -788,7 +788,7 @@
         <v>1.3</v>
       </c>
       <c r="G8" s="1">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H8" s="1">
         <v>1.25</v>
@@ -800,7 +800,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L8" s="4"/>
       <c r="N8" s="1"/>
@@ -819,7 +819,7 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
@@ -834,7 +834,7 @@
         <v>1.3</v>
       </c>
       <c r="G9" s="1">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H9" s="1">
         <v>1.25</v>
@@ -846,7 +846,7 @@
         <v>6</v>
       </c>
       <c r="K9" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L9" s="1"/>
       <c r="N9" s="1"/>
@@ -865,7 +865,7 @@
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
     </row>
-    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>5</v>
@@ -880,7 +880,7 @@
         <v>1.3</v>
       </c>
       <c r="G10" s="1">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H10" s="1">
         <v>1.25</v>
@@ -892,7 +892,7 @@
         <v>6</v>
       </c>
       <c r="K10" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L10" s="1"/>
       <c r="N10" s="1"/>
@@ -911,7 +911,7 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>6</v>
@@ -926,7 +926,7 @@
         <v>1.3</v>
       </c>
       <c r="G11" s="1">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H11" s="1">
         <v>1.25</v>
@@ -938,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -958,7 +958,7 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>7</v>
@@ -973,7 +973,7 @@
         <v>1.3</v>
       </c>
       <c r="G12" s="1">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H12" s="1">
         <v>1.25</v>
@@ -985,7 +985,7 @@
         <v>6</v>
       </c>
       <c r="K12" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1005,7 +1005,7 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
     </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>8</v>
@@ -1021,7 +1021,7 @@
         <v>1.3</v>
       </c>
       <c r="G13" s="1">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H13" s="1">
         <v>1.25</v>
@@ -1053,7 +1053,7 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
     </row>
-    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>9</v>
@@ -1069,7 +1069,7 @@
         <v>1.35</v>
       </c>
       <c r="G14" s="1">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
@@ -1101,7 +1101,7 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>10</v>
@@ -1117,7 +1117,7 @@
         <v>1.35</v>
       </c>
       <c r="G15" s="1">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="H15" s="1">
         <v>2</v>
@@ -1149,7 +1149,7 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
     </row>
-    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>11</v>
@@ -1165,7 +1165,7 @@
         <v>1.35</v>
       </c>
       <c r="G16" s="1">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="H16" s="1">
         <v>2</v>
@@ -1197,7 +1197,7 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>12</v>
@@ -1213,7 +1213,7 @@
         <v>1.35</v>
       </c>
       <c r="G17" s="1">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1">
         <v>2</v>
@@ -1245,7 +1245,7 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
@@ -1261,7 +1261,7 @@
         <v>1.35</v>
       </c>
       <c r="G18" s="1">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
@@ -1273,7 +1273,7 @@
         <v>7</v>
       </c>
       <c r="K18" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="1"/>
@@ -1293,7 +1293,7 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>14</v>
@@ -1309,7 +1309,7 @@
         <v>1.35</v>
       </c>
       <c r="G19" s="1">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="H19" s="1">
         <v>2</v>
@@ -1321,7 +1321,7 @@
         <v>7</v>
       </c>
       <c r="K19" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1341,7 +1341,7 @@
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
     </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>15</v>
@@ -1357,7 +1357,7 @@
         <v>1.35</v>
       </c>
       <c r="G20" s="1">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="H20" s="1">
         <v>2</v>
@@ -1369,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="K20" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1389,7 +1389,7 @@
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
     </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>16</v>
@@ -1405,7 +1405,7 @@
         <v>1.35</v>
       </c>
       <c r="G21" s="1">
-        <v>1.3</v>
+        <v>12</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -1417,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="K21" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1437,7 +1437,7 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>17</v>
@@ -1453,7 +1453,7 @@
         <v>1.4</v>
       </c>
       <c r="G22" s="1">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1">
         <v>2.5</v>
@@ -1465,7 +1465,7 @@
         <v>8</v>
       </c>
       <c r="K22" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1485,7 +1485,7 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>18</v>
@@ -1501,7 +1501,7 @@
         <v>1.4</v>
       </c>
       <c r="G23" s="1">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="H23" s="1">
         <v>2.5</v>
@@ -1513,7 +1513,7 @@
         <v>8</v>
       </c>
       <c r="K23" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1533,7 +1533,7 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>19</v>
@@ -1549,7 +1549,7 @@
         <v>1.4</v>
       </c>
       <c r="G24" s="1">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="H24" s="1">
         <v>2.5</v>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="K24" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -1581,7 +1581,7 @@
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
     </row>
-    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>20</v>
@@ -1597,7 +1597,7 @@
         <v>1.4</v>
       </c>
       <c r="G25" s="1">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="H25" s="1">
         <v>2.5</v>
@@ -1609,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="K25" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1629,7 +1629,7 @@
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
     </row>
-    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>21</v>
@@ -1645,7 +1645,7 @@
         <v>1.4</v>
       </c>
       <c r="G26" s="1">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="H26" s="1">
         <v>2.5</v>
@@ -1657,7 +1657,7 @@
         <v>9</v>
       </c>
       <c r="K26" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1677,7 +1677,7 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>22</v>
@@ -1692,7 +1692,7 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="2">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2">
         <v>3</v>
@@ -1704,7 +1704,7 @@
         <v>9</v>
       </c>
       <c r="K27" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -1724,7 +1724,7 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>23</v>
@@ -1740,7 +1740,7 @@
         <v>1.5</v>
       </c>
       <c r="G28" s="2">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2">
         <v>3</v>
@@ -1752,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="K28" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -1772,7 +1772,7 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>24</v>
@@ -1788,7 +1788,7 @@
         <v>1.5</v>
       </c>
       <c r="G29" s="2">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2">
         <v>3</v>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
       <c r="K29" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -1820,7 +1820,7 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>25</v>
@@ -1836,7 +1836,7 @@
         <v>1.5</v>
       </c>
       <c r="G30" s="2">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="K30" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -1868,7 +1868,7 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
     </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1898,7 +1898,7 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1928,7 +1928,7 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1958,7 +1958,7 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
     </row>
-    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1988,7 +1988,7 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
     </row>
-    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2018,7 +2018,7 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
     </row>
-    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2048,7 +2048,7 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2078,7 +2078,7 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2108,7 +2108,7 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
     </row>
-    <row r="39" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2138,7 +2138,7 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
     </row>
-    <row r="40" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2168,7 +2168,7 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
     </row>
-    <row r="41" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2198,7 +2198,7 @@
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
     </row>
-    <row r="42" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2228,7 +2228,7 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
     </row>
-    <row r="43" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2258,7 +2258,7 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
     </row>
-    <row r="44" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2288,7 +2288,7 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
     </row>
-    <row r="45" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2318,7 +2318,7 @@
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
     </row>
-    <row r="46" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2348,7 +2348,7 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2378,7 +2378,7 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
     </row>
-    <row r="48" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2408,7 +2408,7 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
     </row>
-    <row r="49" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2438,7 +2438,7 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2468,7 +2468,7 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
     </row>
-    <row r="51" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2498,7 +2498,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2528,7 +2528,7 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
     </row>
-    <row r="53" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2558,7 +2558,7 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
     </row>
-    <row r="54" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2588,7 +2588,7 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
     </row>
-    <row r="55" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2618,7 +2618,7 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2648,7 +2648,7 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2678,7 +2678,7 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2708,7 +2708,7 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2738,7 +2738,7 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2768,7 +2768,7 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2798,7 +2798,7 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2828,7 +2828,7 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2858,7 +2858,7 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2888,7 +2888,7 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2918,7 +2918,7 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="66" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2948,7 +2948,7 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
     </row>
-    <row r="67" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2978,7 +2978,7 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
     </row>
-    <row r="68" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3008,7 +3008,7 @@
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
     </row>
-    <row r="69" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3038,7 +3038,7 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
     </row>
-    <row r="70" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3068,7 +3068,7 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3098,7 +3098,7 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3128,7 +3128,7 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
     </row>
-    <row r="73" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3158,7 +3158,7 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
     </row>
-    <row r="74" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3188,7 +3188,7 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
     </row>
-    <row r="75" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3218,7 +3218,7 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
     </row>
-    <row r="76" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3248,7 +3248,7 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
     </row>
-    <row r="77" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3278,7 +3278,7 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
     </row>
-    <row r="78" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3308,7 +3308,7 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
     </row>
-    <row r="79" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3338,7 +3338,7 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
     </row>
-    <row r="80" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3368,7 +3368,7 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
     </row>
-    <row r="81" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3398,7 +3398,7 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
     </row>
-    <row r="82" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3428,7 +3428,7 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
     </row>
-    <row r="83" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3458,7 +3458,7 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
     </row>
-    <row r="84" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3488,7 +3488,7 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
     </row>
-    <row r="85" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3518,7 +3518,7 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
     </row>
-    <row r="86" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3548,7 +3548,7 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
     </row>
-    <row r="87" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3578,7 +3578,7 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
     </row>
-    <row r="88" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3608,7 +3608,7 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
     </row>
-    <row r="89" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3638,7 +3638,7 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
     </row>
-    <row r="90" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3668,7 +3668,7 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
     </row>
-    <row r="91" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3698,7 +3698,7 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
     </row>
-    <row r="92" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3728,7 +3728,7 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
     </row>
-    <row r="93" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3758,7 +3758,7 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
     </row>
-    <row r="94" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3788,7 +3788,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3818,7 +3818,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3848,7 +3848,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3878,7 +3878,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3908,7 +3908,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3938,7 +3938,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3968,7 +3968,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3998,7 +3998,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4028,7 +4028,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4058,7 +4058,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4088,7 +4088,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4118,7 +4118,7 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
     </row>
-    <row r="106" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4148,7 +4148,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4178,7 +4178,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4208,7 +4208,7 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
     </row>
-    <row r="109" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4238,7 +4238,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4268,7 +4268,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4298,7 +4298,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4328,7 +4328,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4358,7 +4358,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4388,7 +4388,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4418,7 +4418,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4448,7 +4448,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4478,7 +4478,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4508,7 +4508,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4538,7 +4538,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4568,7 +4568,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4598,7 +4598,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4628,7 +4628,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4658,7 +4658,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4688,7 +4688,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4718,7 +4718,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4748,7 +4748,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4778,7 +4778,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4808,7 +4808,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4838,7 +4838,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4868,7 +4868,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4898,7 +4898,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4928,7 +4928,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4958,7 +4958,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4988,7 +4988,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5018,7 +5018,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5048,7 +5048,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5078,7 +5078,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5108,7 +5108,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5138,7 +5138,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5168,7 +5168,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5198,7 +5198,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5228,7 +5228,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5258,7 +5258,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5288,7 +5288,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5318,7 +5318,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5348,7 +5348,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5378,7 +5378,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5408,7 +5408,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5438,7 +5438,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5468,7 +5468,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5498,7 +5498,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5528,7 +5528,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5558,7 +5558,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5588,7 +5588,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5618,7 +5618,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5648,7 +5648,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5678,7 +5678,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5708,7 +5708,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5738,7 +5738,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5768,7 +5768,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5798,7 +5798,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5828,7 +5828,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5858,7 +5858,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5888,7 +5888,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5918,7 +5918,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5948,7 +5948,7 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
     </row>
-    <row r="167" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5978,7 +5978,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6008,7 +6008,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6038,7 +6038,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6068,7 +6068,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6098,7 +6098,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6128,7 +6128,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6158,7 +6158,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6188,7 +6188,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6218,7 +6218,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6248,7 +6248,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6278,7 +6278,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6308,7 +6308,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6338,7 +6338,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6368,7 +6368,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6398,7 +6398,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6428,7 +6428,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6458,7 +6458,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6488,7 +6488,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6518,7 +6518,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6548,7 +6548,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6578,7 +6578,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6608,7 +6608,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6638,7 +6638,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6668,7 +6668,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6698,7 +6698,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6728,7 +6728,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6758,7 +6758,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6788,7 +6788,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6818,7 +6818,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6848,7 +6848,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6878,7 +6878,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6908,7 +6908,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6938,7 +6938,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6968,7 +6968,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6998,7 +6998,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7028,7 +7028,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7058,7 +7058,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7088,7 +7088,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7118,7 +7118,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7148,7 +7148,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7178,7 +7178,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7208,7 +7208,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7238,7 +7238,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7268,7 +7268,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7298,7 +7298,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7328,7 +7328,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7358,7 +7358,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7388,7 +7388,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7418,7 +7418,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7448,7 +7448,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7478,7 +7478,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7508,7 +7508,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7538,7 +7538,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7568,7 +7568,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7598,7 +7598,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7628,7 +7628,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7658,7 +7658,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7688,7 +7688,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7718,7 +7718,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7748,7 +7748,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7778,7 +7778,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7808,7 +7808,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7838,7 +7838,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7868,7 +7868,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7898,7 +7898,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7928,7 +7928,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7958,7 +7958,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -7988,7 +7988,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8018,7 +8018,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8048,7 +8048,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8078,7 +8078,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8108,7 +8108,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8138,7 +8138,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8168,7 +8168,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8198,7 +8198,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8228,7 +8228,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8258,7 +8258,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8288,7 +8288,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8318,7 +8318,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8348,7 +8348,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8378,7 +8378,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8408,7 +8408,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8438,7 +8438,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8468,7 +8468,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8498,7 +8498,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8528,7 +8528,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8558,7 +8558,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8588,7 +8588,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8618,7 +8618,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8648,7 +8648,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8678,7 +8678,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8708,7 +8708,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8738,7 +8738,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8768,7 +8768,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8798,7 +8798,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8828,7 +8828,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8858,7 +8858,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8888,7 +8888,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -8918,7 +8918,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -8948,7 +8948,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -8978,7 +8978,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9008,7 +9008,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9038,7 +9038,7 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
     </row>
-    <row r="270" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9068,7 +9068,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9098,7 +9098,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9128,7 +9128,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9158,7 +9158,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9188,7 +9188,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
     </row>
-    <row r="275" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9218,7 +9218,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9248,7 +9248,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9278,7 +9278,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9308,7 +9308,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9338,7 +9338,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9368,7 +9368,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9398,7 +9398,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9428,7 +9428,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9458,7 +9458,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9488,7 +9488,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9518,7 +9518,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -9548,7 +9548,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -9578,7 +9578,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -9608,7 +9608,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -9638,7 +9638,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -9668,7 +9668,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -9698,7 +9698,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -9728,7 +9728,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -9758,7 +9758,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -9788,7 +9788,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -9818,7 +9818,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -9848,7 +9848,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -9878,7 +9878,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -9908,7 +9908,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -9938,7 +9938,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -9968,7 +9968,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -9998,7 +9998,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10028,7 +10028,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10058,7 +10058,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10088,7 +10088,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10118,7 +10118,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10148,7 +10148,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10178,7 +10178,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10208,7 +10208,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10238,7 +10238,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10268,7 +10268,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10298,7 +10298,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10328,7 +10328,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10358,7 +10358,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10388,7 +10388,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10418,7 +10418,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10448,7 +10448,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10478,7 +10478,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -10508,7 +10508,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -10538,7 +10538,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -10568,7 +10568,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -10598,7 +10598,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -10628,7 +10628,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -10658,7 +10658,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10688,7 +10688,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10718,7 +10718,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -10748,7 +10748,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -10778,7 +10778,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -10808,7 +10808,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -10838,7 +10838,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -10868,7 +10868,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -10898,7 +10898,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -10928,7 +10928,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -10958,7 +10958,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -10988,7 +10988,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11018,7 +11018,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11048,7 +11048,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11078,7 +11078,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11108,7 +11108,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11138,7 +11138,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11168,7 +11168,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11198,7 +11198,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11228,7 +11228,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11258,7 +11258,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11288,7 +11288,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11318,7 +11318,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11348,7 +11348,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11378,7 +11378,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11408,7 +11408,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11438,7 +11438,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11468,7 +11468,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11498,7 +11498,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11528,7 +11528,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -11558,7 +11558,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -11588,7 +11588,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -11618,7 +11618,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -11648,7 +11648,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -11678,7 +11678,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -11708,7 +11708,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -11738,7 +11738,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -11768,7 +11768,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -11798,7 +11798,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -11828,7 +11828,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -11858,7 +11858,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -11888,7 +11888,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -11918,7 +11918,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -11948,7 +11948,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -11978,7 +11978,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12008,7 +12008,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12038,7 +12038,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12068,7 +12068,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12098,7 +12098,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12128,7 +12128,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12158,7 +12158,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12188,7 +12188,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12218,7 +12218,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12248,7 +12248,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12278,7 +12278,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12308,7 +12308,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12338,7 +12338,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12368,7 +12368,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12398,7 +12398,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12428,7 +12428,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12458,7 +12458,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12488,7 +12488,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12518,7 +12518,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12548,7 +12548,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12578,7 +12578,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12608,7 +12608,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -12638,7 +12638,7 @@
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
     </row>
-    <row r="390" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -12668,7 +12668,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -12698,7 +12698,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -12728,7 +12728,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -12758,7 +12758,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -12788,7 +12788,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -12818,7 +12818,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -12848,7 +12848,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -12878,7 +12878,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -12908,7 +12908,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -12938,7 +12938,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -12968,7 +12968,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -12998,7 +12998,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13028,7 +13028,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13058,7 +13058,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13088,7 +13088,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13118,7 +13118,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13148,7 +13148,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13178,7 +13178,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13208,7 +13208,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13238,7 +13238,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13268,7 +13268,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13298,7 +13298,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13328,7 +13328,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13358,7 +13358,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13388,7 +13388,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13418,7 +13418,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13448,7 +13448,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13478,7 +13478,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13508,7 +13508,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13538,7 +13538,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13568,7 +13568,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -13598,7 +13598,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -13628,7 +13628,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -13658,7 +13658,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -13688,7 +13688,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -13718,7 +13718,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -13748,7 +13748,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -13778,7 +13778,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -13808,7 +13808,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -13838,7 +13838,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -13868,7 +13868,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -13898,7 +13898,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -13928,7 +13928,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -13958,7 +13958,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -13988,7 +13988,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14018,7 +14018,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14048,7 +14048,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14078,7 +14078,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14108,7 +14108,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14138,7 +14138,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14168,7 +14168,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14198,7 +14198,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14228,7 +14228,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14258,7 +14258,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14288,7 +14288,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14318,7 +14318,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14348,7 +14348,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14378,7 +14378,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14408,7 +14408,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14438,7 +14438,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14468,7 +14468,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14498,7 +14498,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14528,7 +14528,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -14558,7 +14558,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -14588,7 +14588,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -14618,7 +14618,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -14648,7 +14648,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -14678,7 +14678,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -14708,7 +14708,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -14738,7 +14738,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -14768,7 +14768,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -14798,7 +14798,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -14828,7 +14828,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -14858,7 +14858,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -14888,7 +14888,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -14918,7 +14918,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -14948,7 +14948,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -14978,7 +14978,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15008,7 +15008,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15038,7 +15038,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15068,7 +15068,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15098,7 +15098,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15128,7 +15128,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15158,7 +15158,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15188,7 +15188,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15218,7 +15218,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15248,7 +15248,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15278,7 +15278,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15308,7 +15308,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15338,7 +15338,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15368,7 +15368,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15398,7 +15398,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15428,7 +15428,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15458,7 +15458,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -15488,7 +15488,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -15518,7 +15518,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -15548,7 +15548,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -15578,7 +15578,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -15608,7 +15608,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -15638,7 +15638,7 @@
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
     </row>
-    <row r="490" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -15668,7 +15668,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -15698,7 +15698,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -15728,7 +15728,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -15758,7 +15758,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -15788,7 +15788,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -15818,7 +15818,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -15848,7 +15848,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -15878,7 +15878,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -15908,7 +15908,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -15938,7 +15938,7 @@
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
     </row>
-    <row r="500" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -15968,7 +15968,7 @@
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
     </row>
-    <row r="501" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -15998,7 +15998,7 @@
       <c r="AA501" s="1"/>
       <c r="AB501" s="1"/>
     </row>
-    <row r="502" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16028,7 +16028,7 @@
       <c r="AA502" s="1"/>
       <c r="AB502" s="1"/>
     </row>
-    <row r="503" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16058,7 +16058,7 @@
       <c r="AA503" s="1"/>
       <c r="AB503" s="1"/>
     </row>
-    <row r="504" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16088,7 +16088,7 @@
       <c r="AA504" s="1"/>
       <c r="AB504" s="1"/>
     </row>
-    <row r="505" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16118,7 +16118,7 @@
       <c r="AA505" s="1"/>
       <c r="AB505" s="1"/>
     </row>
-    <row r="506" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16148,7 +16148,7 @@
       <c r="AA506" s="1"/>
       <c r="AB506" s="1"/>
     </row>
-    <row r="507" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16178,7 +16178,7 @@
       <c r="AA507" s="1"/>
       <c r="AB507" s="1"/>
     </row>
-    <row r="508" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16208,7 +16208,7 @@
       <c r="AA508" s="1"/>
       <c r="AB508" s="1"/>
     </row>
-    <row r="509" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16238,7 +16238,7 @@
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
     </row>
-    <row r="510" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16268,7 +16268,7 @@
       <c r="AA510" s="1"/>
       <c r="AB510" s="1"/>
     </row>
-    <row r="511" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16298,7 +16298,7 @@
       <c r="AA511" s="1"/>
       <c r="AB511" s="1"/>
     </row>
-    <row r="512" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16328,7 +16328,7 @@
       <c r="AA512" s="1"/>
       <c r="AB512" s="1"/>
     </row>
-    <row r="513" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16358,7 +16358,7 @@
       <c r="AA513" s="1"/>
       <c r="AB513" s="1"/>
     </row>
-    <row r="514" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16388,7 +16388,7 @@
       <c r="AA514" s="1"/>
       <c r="AB514" s="1"/>
     </row>
-    <row r="515" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16418,7 +16418,7 @@
       <c r="AA515" s="1"/>
       <c r="AB515" s="1"/>
     </row>
-    <row r="516" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -16448,7 +16448,7 @@
       <c r="AA516" s="1"/>
       <c r="AB516" s="1"/>
     </row>
-    <row r="517" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -16478,7 +16478,7 @@
       <c r="AA517" s="1"/>
       <c r="AB517" s="1"/>
     </row>
-    <row r="518" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -16508,7 +16508,7 @@
       <c r="AA518" s="1"/>
       <c r="AB518" s="1"/>
     </row>
-    <row r="519" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -16538,7 +16538,7 @@
       <c r="AA519" s="1"/>
       <c r="AB519" s="1"/>
     </row>
-    <row r="520" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -16568,7 +16568,7 @@
       <c r="AA520" s="1"/>
       <c r="AB520" s="1"/>
     </row>
-    <row r="521" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -16598,7 +16598,7 @@
       <c r="AA521" s="1"/>
       <c r="AB521" s="1"/>
     </row>
-    <row r="522" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -16628,7 +16628,7 @@
       <c r="AA522" s="1"/>
       <c r="AB522" s="1"/>
     </row>
-    <row r="523" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -16658,7 +16658,7 @@
       <c r="AA523" s="1"/>
       <c r="AB523" s="1"/>
     </row>
-    <row r="524" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -16688,7 +16688,7 @@
       <c r="AA524" s="1"/>
       <c r="AB524" s="1"/>
     </row>
-    <row r="525" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -16718,7 +16718,7 @@
       <c r="AA525" s="1"/>
       <c r="AB525" s="1"/>
     </row>
-    <row r="526" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -16748,7 +16748,7 @@
       <c r="AA526" s="1"/>
       <c r="AB526" s="1"/>
     </row>
-    <row r="527" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -16778,7 +16778,7 @@
       <c r="AA527" s="1"/>
       <c r="AB527" s="1"/>
     </row>
-    <row r="528" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -16808,7 +16808,7 @@
       <c r="AA528" s="1"/>
       <c r="AB528" s="1"/>
     </row>
-    <row r="529" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -16838,7 +16838,7 @@
       <c r="AA529" s="1"/>
       <c r="AB529" s="1"/>
     </row>
-    <row r="530" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -16868,7 +16868,7 @@
       <c r="AA530" s="1"/>
       <c r="AB530" s="1"/>
     </row>
-    <row r="531" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -16898,7 +16898,7 @@
       <c r="AA531" s="1"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -16928,7 +16928,7 @@
       <c r="AA532" s="1"/>
       <c r="AB532" s="1"/>
     </row>
-    <row r="533" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -16958,7 +16958,7 @@
       <c r="AA533" s="1"/>
       <c r="AB533" s="1"/>
     </row>
-    <row r="534" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -16988,7 +16988,7 @@
       <c r="AA534" s="1"/>
       <c r="AB534" s="1"/>
     </row>
-    <row r="535" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17018,7 +17018,7 @@
       <c r="AA535" s="1"/>
       <c r="AB535" s="1"/>
     </row>
-    <row r="536" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17048,7 +17048,7 @@
       <c r="AA536" s="1"/>
       <c r="AB536" s="1"/>
     </row>
-    <row r="537" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17078,7 +17078,7 @@
       <c r="AA537" s="1"/>
       <c r="AB537" s="1"/>
     </row>
-    <row r="538" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17108,7 +17108,7 @@
       <c r="AA538" s="1"/>
       <c r="AB538" s="1"/>
     </row>
-    <row r="539" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17138,7 +17138,7 @@
       <c r="AA539" s="1"/>
       <c r="AB539" s="1"/>
     </row>
-    <row r="540" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17168,7 +17168,7 @@
       <c r="AA540" s="1"/>
       <c r="AB540" s="1"/>
     </row>
-    <row r="541" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17198,7 +17198,7 @@
       <c r="AA541" s="1"/>
       <c r="AB541" s="1"/>
     </row>
-    <row r="542" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17228,7 +17228,7 @@
       <c r="AA542" s="1"/>
       <c r="AB542" s="1"/>
     </row>
-    <row r="543" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17258,7 +17258,7 @@
       <c r="AA543" s="1"/>
       <c r="AB543" s="1"/>
     </row>
-    <row r="544" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17288,7 +17288,7 @@
       <c r="AA544" s="1"/>
       <c r="AB544" s="1"/>
     </row>
-    <row r="545" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17318,7 +17318,7 @@
       <c r="AA545" s="1"/>
       <c r="AB545" s="1"/>
     </row>
-    <row r="546" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -17348,7 +17348,7 @@
       <c r="AA546" s="1"/>
       <c r="AB546" s="1"/>
     </row>
-    <row r="547" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -17378,7 +17378,7 @@
       <c r="AA547" s="1"/>
       <c r="AB547" s="1"/>
     </row>
-    <row r="548" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -17408,7 +17408,7 @@
       <c r="AA548" s="1"/>
       <c r="AB548" s="1"/>
     </row>
-    <row r="549" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -17438,7 +17438,7 @@
       <c r="AA549" s="1"/>
       <c r="AB549" s="1"/>
     </row>
-    <row r="550" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -17468,7 +17468,7 @@
       <c r="AA550" s="1"/>
       <c r="AB550" s="1"/>
     </row>
-    <row r="551" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -17498,7 +17498,7 @@
       <c r="AA551" s="1"/>
       <c r="AB551" s="1"/>
     </row>
-    <row r="552" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -17528,7 +17528,7 @@
       <c r="AA552" s="1"/>
       <c r="AB552" s="1"/>
     </row>
-    <row r="553" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -17558,7 +17558,7 @@
       <c r="AA553" s="1"/>
       <c r="AB553" s="1"/>
     </row>
-    <row r="554" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -17588,7 +17588,7 @@
       <c r="AA554" s="1"/>
       <c r="AB554" s="1"/>
     </row>
-    <row r="555" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -17618,7 +17618,7 @@
       <c r="AA555" s="1"/>
       <c r="AB555" s="1"/>
     </row>
-    <row r="556" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -17648,7 +17648,7 @@
       <c r="AA556" s="1"/>
       <c r="AB556" s="1"/>
     </row>
-    <row r="557" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -17678,7 +17678,7 @@
       <c r="AA557" s="1"/>
       <c r="AB557" s="1"/>
     </row>
-    <row r="558" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -17708,7 +17708,7 @@
       <c r="AA558" s="1"/>
       <c r="AB558" s="1"/>
     </row>
-    <row r="559" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -17738,7 +17738,7 @@
       <c r="AA559" s="1"/>
       <c r="AB559" s="1"/>
     </row>
-    <row r="560" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -17768,7 +17768,7 @@
       <c r="AA560" s="1"/>
       <c r="AB560" s="1"/>
     </row>
-    <row r="561" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -17798,7 +17798,7 @@
       <c r="AA561" s="1"/>
       <c r="AB561" s="1"/>
     </row>
-    <row r="562" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -17828,7 +17828,7 @@
       <c r="AA562" s="1"/>
       <c r="AB562" s="1"/>
     </row>
-    <row r="563" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -17858,7 +17858,7 @@
       <c r="AA563" s="1"/>
       <c r="AB563" s="1"/>
     </row>
-    <row r="564" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -17888,7 +17888,7 @@
       <c r="AA564" s="1"/>
       <c r="AB564" s="1"/>
     </row>
-    <row r="565" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -17918,7 +17918,7 @@
       <c r="AA565" s="1"/>
       <c r="AB565" s="1"/>
     </row>
-    <row r="566" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -17948,7 +17948,7 @@
       <c r="AA566" s="1"/>
       <c r="AB566" s="1"/>
     </row>
-    <row r="567" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -17978,7 +17978,7 @@
       <c r="AA567" s="1"/>
       <c r="AB567" s="1"/>
     </row>
-    <row r="568" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18008,7 +18008,7 @@
       <c r="AA568" s="1"/>
       <c r="AB568" s="1"/>
     </row>
-    <row r="569" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18038,7 +18038,7 @@
       <c r="AA569" s="1"/>
       <c r="AB569" s="1"/>
     </row>
-    <row r="570" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18068,7 +18068,7 @@
       <c r="AA570" s="1"/>
       <c r="AB570" s="1"/>
     </row>
-    <row r="571" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18098,7 +18098,7 @@
       <c r="AA571" s="1"/>
       <c r="AB571" s="1"/>
     </row>
-    <row r="572" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18128,7 +18128,7 @@
       <c r="AA572" s="1"/>
       <c r="AB572" s="1"/>
     </row>
-    <row r="573" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18158,7 +18158,7 @@
       <c r="AA573" s="1"/>
       <c r="AB573" s="1"/>
     </row>
-    <row r="574" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18188,7 +18188,7 @@
       <c r="AA574" s="1"/>
       <c r="AB574" s="1"/>
     </row>
-    <row r="575" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18218,7 +18218,7 @@
       <c r="AA575" s="1"/>
       <c r="AB575" s="1"/>
     </row>
-    <row r="576" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18248,7 +18248,7 @@
       <c r="AA576" s="1"/>
       <c r="AB576" s="1"/>
     </row>
-    <row r="577" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18278,7 +18278,7 @@
       <c r="AA577" s="1"/>
       <c r="AB577" s="1"/>
     </row>
-    <row r="578" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -18308,7 +18308,7 @@
       <c r="AA578" s="1"/>
       <c r="AB578" s="1"/>
     </row>
-    <row r="579" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -18338,7 +18338,7 @@
       <c r="AA579" s="1"/>
       <c r="AB579" s="1"/>
     </row>
-    <row r="580" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -18368,7 +18368,7 @@
       <c r="AA580" s="1"/>
       <c r="AB580" s="1"/>
     </row>
-    <row r="581" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -18398,7 +18398,7 @@
       <c r="AA581" s="1"/>
       <c r="AB581" s="1"/>
     </row>
-    <row r="582" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -18428,7 +18428,7 @@
       <c r="AA582" s="1"/>
       <c r="AB582" s="1"/>
     </row>
-    <row r="583" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -18458,7 +18458,7 @@
       <c r="AA583" s="1"/>
       <c r="AB583" s="1"/>
     </row>
-    <row r="584" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -18488,7 +18488,7 @@
       <c r="AA584" s="1"/>
       <c r="AB584" s="1"/>
     </row>
-    <row r="585" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -18518,7 +18518,7 @@
       <c r="AA585" s="1"/>
       <c r="AB585" s="1"/>
     </row>
-    <row r="586" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -18548,7 +18548,7 @@
       <c r="AA586" s="1"/>
       <c r="AB586" s="1"/>
     </row>
-    <row r="587" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -18578,7 +18578,7 @@
       <c r="AA587" s="1"/>
       <c r="AB587" s="1"/>
     </row>
-    <row r="588" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -18608,7 +18608,7 @@
       <c r="AA588" s="1"/>
       <c r="AB588" s="1"/>
     </row>
-    <row r="589" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -18638,7 +18638,7 @@
       <c r="AA589" s="1"/>
       <c r="AB589" s="1"/>
     </row>
-    <row r="590" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -18668,7 +18668,7 @@
       <c r="AA590" s="1"/>
       <c r="AB590" s="1"/>
     </row>
-    <row r="591" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -18698,7 +18698,7 @@
       <c r="AA591" s="1"/>
       <c r="AB591" s="1"/>
     </row>
-    <row r="592" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -18728,7 +18728,7 @@
       <c r="AA592" s="1"/>
       <c r="AB592" s="1"/>
     </row>
-    <row r="593" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -18758,7 +18758,7 @@
       <c r="AA593" s="1"/>
       <c r="AB593" s="1"/>
     </row>
-    <row r="594" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -18788,7 +18788,7 @@
       <c r="AA594" s="1"/>
       <c r="AB594" s="1"/>
     </row>
-    <row r="595" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -18818,7 +18818,7 @@
       <c r="AA595" s="1"/>
       <c r="AB595" s="1"/>
     </row>
-    <row r="596" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -18848,7 +18848,7 @@
       <c r="AA596" s="1"/>
       <c r="AB596" s="1"/>
     </row>
-    <row r="597" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -18878,7 +18878,7 @@
       <c r="AA597" s="1"/>
       <c r="AB597" s="1"/>
     </row>
-    <row r="598" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -18908,7 +18908,7 @@
       <c r="AA598" s="1"/>
       <c r="AB598" s="1"/>
     </row>
-    <row r="599" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -18938,7 +18938,7 @@
       <c r="AA599" s="1"/>
       <c r="AB599" s="1"/>
     </row>
-    <row r="600" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -18968,7 +18968,7 @@
       <c r="AA600" s="1"/>
       <c r="AB600" s="1"/>
     </row>
-    <row r="601" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -18998,7 +18998,7 @@
       <c r="AA601" s="1"/>
       <c r="AB601" s="1"/>
     </row>
-    <row r="602" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19028,7 +19028,7 @@
       <c r="AA602" s="1"/>
       <c r="AB602" s="1"/>
     </row>
-    <row r="603" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19058,7 +19058,7 @@
       <c r="AA603" s="1"/>
       <c r="AB603" s="1"/>
     </row>
-    <row r="604" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19088,7 +19088,7 @@
       <c r="AA604" s="1"/>
       <c r="AB604" s="1"/>
     </row>
-    <row r="605" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19118,7 +19118,7 @@
       <c r="AA605" s="1"/>
       <c r="AB605" s="1"/>
     </row>
-    <row r="606" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19148,7 +19148,7 @@
       <c r="AA606" s="1"/>
       <c r="AB606" s="1"/>
     </row>
-    <row r="607" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19178,7 +19178,7 @@
       <c r="AA607" s="1"/>
       <c r="AB607" s="1"/>
     </row>
-    <row r="608" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19208,7 +19208,7 @@
       <c r="AA608" s="1"/>
       <c r="AB608" s="1"/>
     </row>
-    <row r="609" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -19238,7 +19238,7 @@
       <c r="AA609" s="1"/>
       <c r="AB609" s="1"/>
     </row>
-    <row r="610" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -19268,7 +19268,7 @@
       <c r="AA610" s="1"/>
       <c r="AB610" s="1"/>
     </row>
-    <row r="611" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -19298,7 +19298,7 @@
       <c r="AA611" s="1"/>
       <c r="AB611" s="1"/>
     </row>
-    <row r="612" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -19328,7 +19328,7 @@
       <c r="AA612" s="1"/>
       <c r="AB612" s="1"/>
     </row>
-    <row r="613" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -19358,7 +19358,7 @@
       <c r="AA613" s="1"/>
       <c r="AB613" s="1"/>
     </row>
-    <row r="614" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -19388,7 +19388,7 @@
       <c r="AA614" s="1"/>
       <c r="AB614" s="1"/>
     </row>
-    <row r="615" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -19418,7 +19418,7 @@
       <c r="AA615" s="1"/>
       <c r="AB615" s="1"/>
     </row>
-    <row r="616" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -19448,7 +19448,7 @@
       <c r="AA616" s="1"/>
       <c r="AB616" s="1"/>
     </row>
-    <row r="617" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -19478,7 +19478,7 @@
       <c r="AA617" s="1"/>
       <c r="AB617" s="1"/>
     </row>
-    <row r="618" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -19508,7 +19508,7 @@
       <c r="AA618" s="1"/>
       <c r="AB618" s="1"/>
     </row>
-    <row r="619" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -19538,7 +19538,7 @@
       <c r="AA619" s="1"/>
       <c r="AB619" s="1"/>
     </row>
-    <row r="620" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -19568,7 +19568,7 @@
       <c r="AA620" s="1"/>
       <c r="AB620" s="1"/>
     </row>
-    <row r="621" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -19598,7 +19598,7 @@
       <c r="AA621" s="1"/>
       <c r="AB621" s="1"/>
     </row>
-    <row r="622" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -19628,7 +19628,7 @@
       <c r="AA622" s="1"/>
       <c r="AB622" s="1"/>
     </row>
-    <row r="623" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -19658,7 +19658,7 @@
       <c r="AA623" s="1"/>
       <c r="AB623" s="1"/>
     </row>
-    <row r="624" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -19688,7 +19688,7 @@
       <c r="AA624" s="1"/>
       <c r="AB624" s="1"/>
     </row>
-    <row r="625" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -19718,7 +19718,7 @@
       <c r="AA625" s="1"/>
       <c r="AB625" s="1"/>
     </row>
-    <row r="626" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -19748,7 +19748,7 @@
       <c r="AA626" s="1"/>
       <c r="AB626" s="1"/>
     </row>
-    <row r="627" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -19778,7 +19778,7 @@
       <c r="AA627" s="1"/>
       <c r="AB627" s="1"/>
     </row>
-    <row r="628" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -19808,7 +19808,7 @@
       <c r="AA628" s="1"/>
       <c r="AB628" s="1"/>
     </row>
-    <row r="629" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -19838,7 +19838,7 @@
       <c r="AA629" s="1"/>
       <c r="AB629" s="1"/>
     </row>
-    <row r="630" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -19868,7 +19868,7 @@
       <c r="AA630" s="1"/>
       <c r="AB630" s="1"/>
     </row>
-    <row r="631" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -19898,7 +19898,7 @@
       <c r="AA631" s="1"/>
       <c r="AB631" s="1"/>
     </row>
-    <row r="632" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -19928,7 +19928,7 @@
       <c r="AA632" s="1"/>
       <c r="AB632" s="1"/>
     </row>
-    <row r="633" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -19958,7 +19958,7 @@
       <c r="AA633" s="1"/>
       <c r="AB633" s="1"/>
     </row>
-    <row r="634" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -19988,7 +19988,7 @@
       <c r="AA634" s="1"/>
       <c r="AB634" s="1"/>
     </row>
-    <row r="635" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20018,7 +20018,7 @@
       <c r="AA635" s="1"/>
       <c r="AB635" s="1"/>
     </row>
-    <row r="636" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20048,7 +20048,7 @@
       <c r="AA636" s="1"/>
       <c r="AB636" s="1"/>
     </row>
-    <row r="637" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20078,7 +20078,7 @@
       <c r="AA637" s="1"/>
       <c r="AB637" s="1"/>
     </row>
-    <row r="638" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20108,7 +20108,7 @@
       <c r="AA638" s="1"/>
       <c r="AB638" s="1"/>
     </row>
-    <row r="639" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20138,7 +20138,7 @@
       <c r="AA639" s="1"/>
       <c r="AB639" s="1"/>
     </row>
-    <row r="640" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20168,7 +20168,7 @@
       <c r="AA640" s="1"/>
       <c r="AB640" s="1"/>
     </row>
-    <row r="641" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -20198,7 +20198,7 @@
       <c r="AA641" s="1"/>
       <c r="AB641" s="1"/>
     </row>
-    <row r="642" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -20228,7 +20228,7 @@
       <c r="AA642" s="1"/>
       <c r="AB642" s="1"/>
     </row>
-    <row r="643" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -20258,7 +20258,7 @@
       <c r="AA643" s="1"/>
       <c r="AB643" s="1"/>
     </row>
-    <row r="644" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -20288,7 +20288,7 @@
       <c r="AA644" s="1"/>
       <c r="AB644" s="1"/>
     </row>
-    <row r="645" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -20318,7 +20318,7 @@
       <c r="AA645" s="1"/>
       <c r="AB645" s="1"/>
     </row>
-    <row r="646" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -20348,7 +20348,7 @@
       <c r="AA646" s="1"/>
       <c r="AB646" s="1"/>
     </row>
-    <row r="647" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -20378,7 +20378,7 @@
       <c r="AA647" s="1"/>
       <c r="AB647" s="1"/>
     </row>
-    <row r="648" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -20408,7 +20408,7 @@
       <c r="AA648" s="1"/>
       <c r="AB648" s="1"/>
     </row>
-    <row r="649" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -20438,7 +20438,7 @@
       <c r="AA649" s="1"/>
       <c r="AB649" s="1"/>
     </row>
-    <row r="650" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -20468,7 +20468,7 @@
       <c r="AA650" s="1"/>
       <c r="AB650" s="1"/>
     </row>
-    <row r="651" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -20498,7 +20498,7 @@
       <c r="AA651" s="1"/>
       <c r="AB651" s="1"/>
     </row>
-    <row r="652" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -20528,7 +20528,7 @@
       <c r="AA652" s="1"/>
       <c r="AB652" s="1"/>
     </row>
-    <row r="653" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -20558,7 +20558,7 @@
       <c r="AA653" s="1"/>
       <c r="AB653" s="1"/>
     </row>
-    <row r="654" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -20588,7 +20588,7 @@
       <c r="AA654" s="1"/>
       <c r="AB654" s="1"/>
     </row>
-    <row r="655" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -20618,7 +20618,7 @@
       <c r="AA655" s="1"/>
       <c r="AB655" s="1"/>
     </row>
-    <row r="656" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -20648,7 +20648,7 @@
       <c r="AA656" s="1"/>
       <c r="AB656" s="1"/>
     </row>
-    <row r="657" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -20678,7 +20678,7 @@
       <c r="AA657" s="1"/>
       <c r="AB657" s="1"/>
     </row>
-    <row r="658" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -20708,7 +20708,7 @@
       <c r="AA658" s="1"/>
       <c r="AB658" s="1"/>
     </row>
-    <row r="659" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -20738,7 +20738,7 @@
       <c r="AA659" s="1"/>
       <c r="AB659" s="1"/>
     </row>
-    <row r="660" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -20768,7 +20768,7 @@
       <c r="AA660" s="1"/>
       <c r="AB660" s="1"/>
     </row>
-    <row r="661" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -20798,7 +20798,7 @@
       <c r="AA661" s="1"/>
       <c r="AB661" s="1"/>
     </row>
-    <row r="662" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -20828,7 +20828,7 @@
       <c r="AA662" s="1"/>
       <c r="AB662" s="1"/>
     </row>
-    <row r="663" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -20858,7 +20858,7 @@
       <c r="AA663" s="1"/>
       <c r="AB663" s="1"/>
     </row>
-    <row r="664" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -20888,7 +20888,7 @@
       <c r="AA664" s="1"/>
       <c r="AB664" s="1"/>
     </row>
-    <row r="665" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -20918,7 +20918,7 @@
       <c r="AA665" s="1"/>
       <c r="AB665" s="1"/>
     </row>
-    <row r="666" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -20948,7 +20948,7 @@
       <c r="AA666" s="1"/>
       <c r="AB666" s="1"/>
     </row>
-    <row r="667" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -20978,7 +20978,7 @@
       <c r="AA667" s="1"/>
       <c r="AB667" s="1"/>
     </row>
-    <row r="668" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21008,7 +21008,7 @@
       <c r="AA668" s="1"/>
       <c r="AB668" s="1"/>
     </row>
-    <row r="669" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21038,7 +21038,7 @@
       <c r="AA669" s="1"/>
       <c r="AB669" s="1"/>
     </row>
-    <row r="670" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21068,7 +21068,7 @@
       <c r="AA670" s="1"/>
       <c r="AB670" s="1"/>
     </row>
-    <row r="671" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21098,7 +21098,7 @@
       <c r="AA671" s="1"/>
       <c r="AB671" s="1"/>
     </row>
-    <row r="672" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -21128,7 +21128,7 @@
       <c r="AA672" s="1"/>
       <c r="AB672" s="1"/>
     </row>
-    <row r="673" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -21158,7 +21158,7 @@
       <c r="AA673" s="1"/>
       <c r="AB673" s="1"/>
     </row>
-    <row r="674" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -21188,7 +21188,7 @@
       <c r="AA674" s="1"/>
       <c r="AB674" s="1"/>
     </row>
-    <row r="675" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -21218,7 +21218,7 @@
       <c r="AA675" s="1"/>
       <c r="AB675" s="1"/>
     </row>
-    <row r="676" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -21248,7 +21248,7 @@
       <c r="AA676" s="1"/>
       <c r="AB676" s="1"/>
     </row>
-    <row r="677" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -21278,7 +21278,7 @@
       <c r="AA677" s="1"/>
       <c r="AB677" s="1"/>
     </row>
-    <row r="678" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -21308,7 +21308,7 @@
       <c r="AA678" s="1"/>
       <c r="AB678" s="1"/>
     </row>
-    <row r="679" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -21338,7 +21338,7 @@
       <c r="AA679" s="1"/>
       <c r="AB679" s="1"/>
     </row>
-    <row r="680" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -21368,7 +21368,7 @@
       <c r="AA680" s="1"/>
       <c r="AB680" s="1"/>
     </row>
-    <row r="681" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -21398,7 +21398,7 @@
       <c r="AA681" s="1"/>
       <c r="AB681" s="1"/>
     </row>
-    <row r="682" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -21428,7 +21428,7 @@
       <c r="AA682" s="1"/>
       <c r="AB682" s="1"/>
     </row>
-    <row r="683" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -21458,7 +21458,7 @@
       <c r="AA683" s="1"/>
       <c r="AB683" s="1"/>
     </row>
-    <row r="684" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -21488,7 +21488,7 @@
       <c r="AA684" s="1"/>
       <c r="AB684" s="1"/>
     </row>
-    <row r="685" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -21518,7 +21518,7 @@
       <c r="AA685" s="1"/>
       <c r="AB685" s="1"/>
     </row>
-    <row r="686" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -21548,7 +21548,7 @@
       <c r="AA686" s="1"/>
       <c r="AB686" s="1"/>
     </row>
-    <row r="687" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -21578,7 +21578,7 @@
       <c r="AA687" s="1"/>
       <c r="AB687" s="1"/>
     </row>
-    <row r="688" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -21608,7 +21608,7 @@
       <c r="AA688" s="1"/>
       <c r="AB688" s="1"/>
     </row>
-    <row r="689" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -21638,7 +21638,7 @@
       <c r="AA689" s="1"/>
       <c r="AB689" s="1"/>
     </row>
-    <row r="690" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -21668,7 +21668,7 @@
       <c r="AA690" s="1"/>
       <c r="AB690" s="1"/>
     </row>
-    <row r="691" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -21698,7 +21698,7 @@
       <c r="AA691" s="1"/>
       <c r="AB691" s="1"/>
     </row>
-    <row r="692" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -21728,7 +21728,7 @@
       <c r="AA692" s="1"/>
       <c r="AB692" s="1"/>
     </row>
-    <row r="693" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -21758,7 +21758,7 @@
       <c r="AA693" s="1"/>
       <c r="AB693" s="1"/>
     </row>
-    <row r="694" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -21788,7 +21788,7 @@
       <c r="AA694" s="1"/>
       <c r="AB694" s="1"/>
     </row>
-    <row r="695" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -21818,7 +21818,7 @@
       <c r="AA695" s="1"/>
       <c r="AB695" s="1"/>
     </row>
-    <row r="696" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -21848,7 +21848,7 @@
       <c r="AA696" s="1"/>
       <c r="AB696" s="1"/>
     </row>
-    <row r="697" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -21878,7 +21878,7 @@
       <c r="AA697" s="1"/>
       <c r="AB697" s="1"/>
     </row>
-    <row r="698" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -21908,7 +21908,7 @@
       <c r="AA698" s="1"/>
       <c r="AB698" s="1"/>
     </row>
-    <row r="699" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -21938,7 +21938,7 @@
       <c r="AA699" s="1"/>
       <c r="AB699" s="1"/>
     </row>
-    <row r="700" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -21968,7 +21968,7 @@
       <c r="AA700" s="1"/>
       <c r="AB700" s="1"/>
     </row>
-    <row r="701" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -21998,7 +21998,7 @@
       <c r="AA701" s="1"/>
       <c r="AB701" s="1"/>
     </row>
-    <row r="702" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22028,7 +22028,7 @@
       <c r="AA702" s="1"/>
       <c r="AB702" s="1"/>
     </row>
-    <row r="703" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -22058,7 +22058,7 @@
       <c r="AA703" s="1"/>
       <c r="AB703" s="1"/>
     </row>
-    <row r="704" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -22088,7 +22088,7 @@
       <c r="AA704" s="1"/>
       <c r="AB704" s="1"/>
     </row>
-    <row r="705" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -22118,7 +22118,7 @@
       <c r="AA705" s="1"/>
       <c r="AB705" s="1"/>
     </row>
-    <row r="706" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -22148,7 +22148,7 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
-    <row r="707" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -22178,7 +22178,7 @@
       <c r="AA707" s="1"/>
       <c r="AB707" s="1"/>
     </row>
-    <row r="708" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -22208,7 +22208,7 @@
       <c r="AA708" s="1"/>
       <c r="AB708" s="1"/>
     </row>
-    <row r="709" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -22238,7 +22238,7 @@
       <c r="AA709" s="1"/>
       <c r="AB709" s="1"/>
     </row>
-    <row r="710" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -22268,7 +22268,7 @@
       <c r="AA710" s="1"/>
       <c r="AB710" s="1"/>
     </row>
-    <row r="711" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -22298,7 +22298,7 @@
       <c r="AA711" s="1"/>
       <c r="AB711" s="1"/>
     </row>
-    <row r="712" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -22328,7 +22328,7 @@
       <c r="AA712" s="1"/>
       <c r="AB712" s="1"/>
     </row>
-    <row r="713" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -22358,7 +22358,7 @@
       <c r="AA713" s="1"/>
       <c r="AB713" s="1"/>
     </row>
-    <row r="714" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -22388,7 +22388,7 @@
       <c r="AA714" s="1"/>
       <c r="AB714" s="1"/>
     </row>
-    <row r="715" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -22418,7 +22418,7 @@
       <c r="AA715" s="1"/>
       <c r="AB715" s="1"/>
     </row>
-    <row r="716" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -22448,7 +22448,7 @@
       <c r="AA716" s="1"/>
       <c r="AB716" s="1"/>
     </row>
-    <row r="717" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -22478,7 +22478,7 @@
       <c r="AA717" s="1"/>
       <c r="AB717" s="1"/>
     </row>
-    <row r="718" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -22508,7 +22508,7 @@
       <c r="AA718" s="1"/>
       <c r="AB718" s="1"/>
     </row>
-    <row r="719" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -22538,7 +22538,7 @@
       <c r="AA719" s="1"/>
       <c r="AB719" s="1"/>
     </row>
-    <row r="720" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -22568,7 +22568,7 @@
       <c r="AA720" s="1"/>
       <c r="AB720" s="1"/>
     </row>
-    <row r="721" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -22598,7 +22598,7 @@
       <c r="AA721" s="1"/>
       <c r="AB721" s="1"/>
     </row>
-    <row r="722" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -22628,7 +22628,7 @@
       <c r="AA722" s="1"/>
       <c r="AB722" s="1"/>
     </row>
-    <row r="723" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -22658,7 +22658,7 @@
       <c r="AA723" s="1"/>
       <c r="AB723" s="1"/>
     </row>
-    <row r="724" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -22688,7 +22688,7 @@
       <c r="AA724" s="1"/>
       <c r="AB724" s="1"/>
     </row>
-    <row r="725" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -22718,7 +22718,7 @@
       <c r="AA725" s="1"/>
       <c r="AB725" s="1"/>
     </row>
-    <row r="726" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -22748,7 +22748,7 @@
       <c r="AA726" s="1"/>
       <c r="AB726" s="1"/>
     </row>
-    <row r="727" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -22778,7 +22778,7 @@
       <c r="AA727" s="1"/>
       <c r="AB727" s="1"/>
     </row>
-    <row r="728" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -22808,7 +22808,7 @@
       <c r="AA728" s="1"/>
       <c r="AB728" s="1"/>
     </row>
-    <row r="729" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -22838,7 +22838,7 @@
       <c r="AA729" s="1"/>
       <c r="AB729" s="1"/>
     </row>
-    <row r="730" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -22868,7 +22868,7 @@
       <c r="AA730" s="1"/>
       <c r="AB730" s="1"/>
     </row>
-    <row r="731" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -22898,7 +22898,7 @@
       <c r="AA731" s="1"/>
       <c r="AB731" s="1"/>
     </row>
-    <row r="732" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -22928,7 +22928,7 @@
       <c r="AA732" s="1"/>
       <c r="AB732" s="1"/>
     </row>
-    <row r="733" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -22958,7 +22958,7 @@
       <c r="AA733" s="1"/>
       <c r="AB733" s="1"/>
     </row>
-    <row r="734" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -22988,7 +22988,7 @@
       <c r="AA734" s="1"/>
       <c r="AB734" s="1"/>
     </row>
-    <row r="735" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -23018,7 +23018,7 @@
       <c r="AA735" s="1"/>
       <c r="AB735" s="1"/>
     </row>
-    <row r="736" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -23048,7 +23048,7 @@
       <c r="AA736" s="1"/>
       <c r="AB736" s="1"/>
     </row>
-    <row r="737" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -23078,7 +23078,7 @@
       <c r="AA737" s="1"/>
       <c r="AB737" s="1"/>
     </row>
-    <row r="738" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -23108,7 +23108,7 @@
       <c r="AA738" s="1"/>
       <c r="AB738" s="1"/>
     </row>
-    <row r="739" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -23138,7 +23138,7 @@
       <c r="AA739" s="1"/>
       <c r="AB739" s="1"/>
     </row>
-    <row r="740" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -23168,7 +23168,7 @@
       <c r="AA740" s="1"/>
       <c r="AB740" s="1"/>
     </row>
-    <row r="741" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -23198,7 +23198,7 @@
       <c r="AA741" s="1"/>
       <c r="AB741" s="1"/>
     </row>
-    <row r="742" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -23228,7 +23228,7 @@
       <c r="AA742" s="1"/>
       <c r="AB742" s="1"/>
     </row>
-    <row r="743" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -23258,7 +23258,7 @@
       <c r="AA743" s="1"/>
       <c r="AB743" s="1"/>
     </row>
-    <row r="744" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -23288,7 +23288,7 @@
       <c r="AA744" s="1"/>
       <c r="AB744" s="1"/>
     </row>
-    <row r="745" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -23318,7 +23318,7 @@
       <c r="AA745" s="1"/>
       <c r="AB745" s="1"/>
     </row>
-    <row r="746" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -23348,7 +23348,7 @@
       <c r="AA746" s="1"/>
       <c r="AB746" s="1"/>
     </row>
-    <row r="747" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -23378,7 +23378,7 @@
       <c r="AA747" s="1"/>
       <c r="AB747" s="1"/>
     </row>
-    <row r="748" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -23408,7 +23408,7 @@
       <c r="AA748" s="1"/>
       <c r="AB748" s="1"/>
     </row>
-    <row r="749" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -23438,7 +23438,7 @@
       <c r="AA749" s="1"/>
       <c r="AB749" s="1"/>
     </row>
-    <row r="750" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -23468,7 +23468,7 @@
       <c r="AA750" s="1"/>
       <c r="AB750" s="1"/>
     </row>
-    <row r="751" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -23498,7 +23498,7 @@
       <c r="AA751" s="1"/>
       <c r="AB751" s="1"/>
     </row>
-    <row r="752" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -23528,7 +23528,7 @@
       <c r="AA752" s="1"/>
       <c r="AB752" s="1"/>
     </row>
-    <row r="753" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -23558,7 +23558,7 @@
       <c r="AA753" s="1"/>
       <c r="AB753" s="1"/>
     </row>
-    <row r="754" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -23588,7 +23588,7 @@
       <c r="AA754" s="1"/>
       <c r="AB754" s="1"/>
     </row>
-    <row r="755" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -23618,7 +23618,7 @@
       <c r="AA755" s="1"/>
       <c r="AB755" s="1"/>
     </row>
-    <row r="756" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -23648,7 +23648,7 @@
       <c r="AA756" s="1"/>
       <c r="AB756" s="1"/>
     </row>
-    <row r="757" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -23678,7 +23678,7 @@
       <c r="AA757" s="1"/>
       <c r="AB757" s="1"/>
     </row>
-    <row r="758" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -23708,7 +23708,7 @@
       <c r="AA758" s="1"/>
       <c r="AB758" s="1"/>
     </row>
-    <row r="759" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -23738,7 +23738,7 @@
       <c r="AA759" s="1"/>
       <c r="AB759" s="1"/>
     </row>
-    <row r="760" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -23768,7 +23768,7 @@
       <c r="AA760" s="1"/>
       <c r="AB760" s="1"/>
     </row>
-    <row r="761" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -23798,7 +23798,7 @@
       <c r="AA761" s="1"/>
       <c r="AB761" s="1"/>
     </row>
-    <row r="762" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -23828,7 +23828,7 @@
       <c r="AA762" s="1"/>
       <c r="AB762" s="1"/>
     </row>
-    <row r="763" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -23858,7 +23858,7 @@
       <c r="AA763" s="1"/>
       <c r="AB763" s="1"/>
     </row>
-    <row r="764" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -23888,7 +23888,7 @@
       <c r="AA764" s="1"/>
       <c r="AB764" s="1"/>
     </row>
-    <row r="765" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -23918,7 +23918,7 @@
       <c r="AA765" s="1"/>
       <c r="AB765" s="1"/>
     </row>
-    <row r="766" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -23948,7 +23948,7 @@
       <c r="AA766" s="1"/>
       <c r="AB766" s="1"/>
     </row>
-    <row r="767" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -23978,7 +23978,7 @@
       <c r="AA767" s="1"/>
       <c r="AB767" s="1"/>
     </row>
-    <row r="768" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -24008,7 +24008,7 @@
       <c r="AA768" s="1"/>
       <c r="AB768" s="1"/>
     </row>
-    <row r="769" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -24038,7 +24038,7 @@
       <c r="AA769" s="1"/>
       <c r="AB769" s="1"/>
     </row>
-    <row r="770" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -24068,7 +24068,7 @@
       <c r="AA770" s="1"/>
       <c r="AB770" s="1"/>
     </row>
-    <row r="771" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -24098,7 +24098,7 @@
       <c r="AA771" s="1"/>
       <c r="AB771" s="1"/>
     </row>
-    <row r="772" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -24128,7 +24128,7 @@
       <c r="AA772" s="1"/>
       <c r="AB772" s="1"/>
     </row>
-    <row r="773" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -24158,7 +24158,7 @@
       <c r="AA773" s="1"/>
       <c r="AB773" s="1"/>
     </row>
-    <row r="774" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -24188,7 +24188,7 @@
       <c r="AA774" s="1"/>
       <c r="AB774" s="1"/>
     </row>
-    <row r="775" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -24218,7 +24218,7 @@
       <c r="AA775" s="1"/>
       <c r="AB775" s="1"/>
     </row>
-    <row r="776" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -24248,7 +24248,7 @@
       <c r="AA776" s="1"/>
       <c r="AB776" s="1"/>
     </row>
-    <row r="777" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -24278,7 +24278,7 @@
       <c r="AA777" s="1"/>
       <c r="AB777" s="1"/>
     </row>
-    <row r="778" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -24308,7 +24308,7 @@
       <c r="AA778" s="1"/>
       <c r="AB778" s="1"/>
     </row>
-    <row r="779" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -24338,7 +24338,7 @@
       <c r="AA779" s="1"/>
       <c r="AB779" s="1"/>
     </row>
-    <row r="780" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -24368,7 +24368,7 @@
       <c r="AA780" s="1"/>
       <c r="AB780" s="1"/>
     </row>
-    <row r="781" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -24398,7 +24398,7 @@
       <c r="AA781" s="1"/>
       <c r="AB781" s="1"/>
     </row>
-    <row r="782" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -24428,7 +24428,7 @@
       <c r="AA782" s="1"/>
       <c r="AB782" s="1"/>
     </row>
-    <row r="783" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -24458,7 +24458,7 @@
       <c r="AA783" s="1"/>
       <c r="AB783" s="1"/>
     </row>
-    <row r="784" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -24488,7 +24488,7 @@
       <c r="AA784" s="1"/>
       <c r="AB784" s="1"/>
     </row>
-    <row r="785" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -24518,7 +24518,7 @@
       <c r="AA785" s="1"/>
       <c r="AB785" s="1"/>
     </row>
-    <row r="786" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -24548,7 +24548,7 @@
       <c r="AA786" s="1"/>
       <c r="AB786" s="1"/>
     </row>
-    <row r="787" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -24578,7 +24578,7 @@
       <c r="AA787" s="1"/>
       <c r="AB787" s="1"/>
     </row>
-    <row r="788" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -24608,7 +24608,7 @@
       <c r="AA788" s="1"/>
       <c r="AB788" s="1"/>
     </row>
-    <row r="789" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -24638,7 +24638,7 @@
       <c r="AA789" s="1"/>
       <c r="AB789" s="1"/>
     </row>
-    <row r="790" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -24668,7 +24668,7 @@
       <c r="AA790" s="1"/>
       <c r="AB790" s="1"/>
     </row>
-    <row r="791" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -24698,7 +24698,7 @@
       <c r="AA791" s="1"/>
       <c r="AB791" s="1"/>
     </row>
-    <row r="792" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -24728,7 +24728,7 @@
       <c r="AA792" s="1"/>
       <c r="AB792" s="1"/>
     </row>
-    <row r="793" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -24758,7 +24758,7 @@
       <c r="AA793" s="1"/>
       <c r="AB793" s="1"/>
     </row>
-    <row r="794" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -24788,7 +24788,7 @@
       <c r="AA794" s="1"/>
       <c r="AB794" s="1"/>
     </row>
-    <row r="795" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -24818,7 +24818,7 @@
       <c r="AA795" s="1"/>
       <c r="AB795" s="1"/>
     </row>
-    <row r="796" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -24848,7 +24848,7 @@
       <c r="AA796" s="1"/>
       <c r="AB796" s="1"/>
     </row>
-    <row r="797" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -24878,7 +24878,7 @@
       <c r="AA797" s="1"/>
       <c r="AB797" s="1"/>
     </row>
-    <row r="798" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -24908,7 +24908,7 @@
       <c r="AA798" s="1"/>
       <c r="AB798" s="1"/>
     </row>
-    <row r="799" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -24938,7 +24938,7 @@
       <c r="AA799" s="1"/>
       <c r="AB799" s="1"/>
     </row>
-    <row r="800" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -24968,7 +24968,7 @@
       <c r="AA800" s="1"/>
       <c r="AB800" s="1"/>
     </row>
-    <row r="801" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -24998,7 +24998,7 @@
       <c r="AA801" s="1"/>
       <c r="AB801" s="1"/>
     </row>
-    <row r="802" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -25028,7 +25028,7 @@
       <c r="AA802" s="1"/>
       <c r="AB802" s="1"/>
     </row>
-    <row r="803" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -25058,7 +25058,7 @@
       <c r="AA803" s="1"/>
       <c r="AB803" s="1"/>
     </row>
-    <row r="804" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -25088,7 +25088,7 @@
       <c r="AA804" s="1"/>
       <c r="AB804" s="1"/>
     </row>
-    <row r="805" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -25118,7 +25118,7 @@
       <c r="AA805" s="1"/>
       <c r="AB805" s="1"/>
     </row>
-    <row r="806" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -25148,7 +25148,7 @@
       <c r="AA806" s="1"/>
       <c r="AB806" s="1"/>
     </row>
-    <row r="807" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -25178,7 +25178,7 @@
       <c r="AA807" s="1"/>
       <c r="AB807" s="1"/>
     </row>
-    <row r="808" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -25208,7 +25208,7 @@
       <c r="AA808" s="1"/>
       <c r="AB808" s="1"/>
     </row>
-    <row r="809" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -25238,7 +25238,7 @@
       <c r="AA809" s="1"/>
       <c r="AB809" s="1"/>
     </row>
-    <row r="810" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -25268,7 +25268,7 @@
       <c r="AA810" s="1"/>
       <c r="AB810" s="1"/>
     </row>
-    <row r="811" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -25298,7 +25298,7 @@
       <c r="AA811" s="1"/>
       <c r="AB811" s="1"/>
     </row>
-    <row r="812" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -25328,7 +25328,7 @@
       <c r="AA812" s="1"/>
       <c r="AB812" s="1"/>
     </row>
-    <row r="813" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -25358,7 +25358,7 @@
       <c r="AA813" s="1"/>
       <c r="AB813" s="1"/>
     </row>
-    <row r="814" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -25388,7 +25388,7 @@
       <c r="AA814" s="1"/>
       <c r="AB814" s="1"/>
     </row>
-    <row r="815" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -25418,7 +25418,7 @@
       <c r="AA815" s="1"/>
       <c r="AB815" s="1"/>
     </row>
-    <row r="816" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -25448,7 +25448,7 @@
       <c r="AA816" s="1"/>
       <c r="AB816" s="1"/>
     </row>
-    <row r="817" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -25478,7 +25478,7 @@
       <c r="AA817" s="1"/>
       <c r="AB817" s="1"/>
     </row>
-    <row r="818" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -25508,7 +25508,7 @@
       <c r="AA818" s="1"/>
       <c r="AB818" s="1"/>
     </row>
-    <row r="819" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -25538,7 +25538,7 @@
       <c r="AA819" s="1"/>
       <c r="AB819" s="1"/>
     </row>
-    <row r="820" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -25568,7 +25568,7 @@
       <c r="AA820" s="1"/>
       <c r="AB820" s="1"/>
     </row>
-    <row r="821" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -25598,7 +25598,7 @@
       <c r="AA821" s="1"/>
       <c r="AB821" s="1"/>
     </row>
-    <row r="822" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -25628,7 +25628,7 @@
       <c r="AA822" s="1"/>
       <c r="AB822" s="1"/>
     </row>
-    <row r="823" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -25658,7 +25658,7 @@
       <c r="AA823" s="1"/>
       <c r="AB823" s="1"/>
     </row>
-    <row r="824" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -25688,7 +25688,7 @@
       <c r="AA824" s="1"/>
       <c r="AB824" s="1"/>
     </row>
-    <row r="825" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -25718,7 +25718,7 @@
       <c r="AA825" s="1"/>
       <c r="AB825" s="1"/>
     </row>
-    <row r="826" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -25748,7 +25748,7 @@
       <c r="AA826" s="1"/>
       <c r="AB826" s="1"/>
     </row>
-    <row r="827" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -25778,7 +25778,7 @@
       <c r="AA827" s="1"/>
       <c r="AB827" s="1"/>
     </row>
-    <row r="828" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -25808,7 +25808,7 @@
       <c r="AA828" s="1"/>
       <c r="AB828" s="1"/>
     </row>
-    <row r="829" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -25838,7 +25838,7 @@
       <c r="AA829" s="1"/>
       <c r="AB829" s="1"/>
     </row>
-    <row r="830" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -25868,7 +25868,7 @@
       <c r="AA830" s="1"/>
       <c r="AB830" s="1"/>
     </row>
-    <row r="831" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -25898,7 +25898,7 @@
       <c r="AA831" s="1"/>
       <c r="AB831" s="1"/>
     </row>
-    <row r="832" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -25928,7 +25928,7 @@
       <c r="AA832" s="1"/>
       <c r="AB832" s="1"/>
     </row>
-    <row r="833" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -25958,7 +25958,7 @@
       <c r="AA833" s="1"/>
       <c r="AB833" s="1"/>
     </row>
-    <row r="834" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -25988,7 +25988,7 @@
       <c r="AA834" s="1"/>
       <c r="AB834" s="1"/>
     </row>
-    <row r="835" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -26018,7 +26018,7 @@
       <c r="AA835" s="1"/>
       <c r="AB835" s="1"/>
     </row>
-    <row r="836" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -26048,7 +26048,7 @@
       <c r="AA836" s="1"/>
       <c r="AB836" s="1"/>
     </row>
-    <row r="837" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -26078,7 +26078,7 @@
       <c r="AA837" s="1"/>
       <c r="AB837" s="1"/>
     </row>
-    <row r="838" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -26108,7 +26108,7 @@
       <c r="AA838" s="1"/>
       <c r="AB838" s="1"/>
     </row>
-    <row r="839" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -26138,7 +26138,7 @@
       <c r="AA839" s="1"/>
       <c r="AB839" s="1"/>
     </row>
-    <row r="840" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -26168,7 +26168,7 @@
       <c r="AA840" s="1"/>
       <c r="AB840" s="1"/>
     </row>
-    <row r="841" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -26198,7 +26198,7 @@
       <c r="AA841" s="1"/>
       <c r="AB841" s="1"/>
     </row>
-    <row r="842" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -26228,7 +26228,7 @@
       <c r="AA842" s="1"/>
       <c r="AB842" s="1"/>
     </row>
-    <row r="843" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -26258,7 +26258,7 @@
       <c r="AA843" s="1"/>
       <c r="AB843" s="1"/>
     </row>
-    <row r="844" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -26288,7 +26288,7 @@
       <c r="AA844" s="1"/>
       <c r="AB844" s="1"/>
     </row>
-    <row r="845" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -26318,7 +26318,7 @@
       <c r="AA845" s="1"/>
       <c r="AB845" s="1"/>
     </row>
-    <row r="846" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -26348,7 +26348,7 @@
       <c r="AA846" s="1"/>
       <c r="AB846" s="1"/>
     </row>
-    <row r="847" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -26378,7 +26378,7 @@
       <c r="AA847" s="1"/>
       <c r="AB847" s="1"/>
     </row>
-    <row r="848" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -26408,7 +26408,7 @@
       <c r="AA848" s="1"/>
       <c r="AB848" s="1"/>
     </row>
-    <row r="849" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -26438,7 +26438,7 @@
       <c r="AA849" s="1"/>
       <c r="AB849" s="1"/>
     </row>
-    <row r="850" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -26468,7 +26468,7 @@
       <c r="AA850" s="1"/>
       <c r="AB850" s="1"/>
     </row>
-    <row r="851" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -26498,7 +26498,7 @@
       <c r="AA851" s="1"/>
       <c r="AB851" s="1"/>
     </row>
-    <row r="852" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -26528,7 +26528,7 @@
       <c r="AA852" s="1"/>
       <c r="AB852" s="1"/>
     </row>
-    <row r="853" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -26558,7 +26558,7 @@
       <c r="AA853" s="1"/>
       <c r="AB853" s="1"/>
     </row>
-    <row r="854" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -26588,7 +26588,7 @@
       <c r="AA854" s="1"/>
       <c r="AB854" s="1"/>
     </row>
-    <row r="855" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -26618,7 +26618,7 @@
       <c r="AA855" s="1"/>
       <c r="AB855" s="1"/>
     </row>
-    <row r="856" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -26648,7 +26648,7 @@
       <c r="AA856" s="1"/>
       <c r="AB856" s="1"/>
     </row>
-    <row r="857" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -26678,7 +26678,7 @@
       <c r="AA857" s="1"/>
       <c r="AB857" s="1"/>
     </row>
-    <row r="858" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -26708,7 +26708,7 @@
       <c r="AA858" s="1"/>
       <c r="AB858" s="1"/>
     </row>
-    <row r="859" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -26738,7 +26738,7 @@
       <c r="AA859" s="1"/>
       <c r="AB859" s="1"/>
     </row>
-    <row r="860" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -26768,7 +26768,7 @@
       <c r="AA860" s="1"/>
       <c r="AB860" s="1"/>
     </row>
-    <row r="861" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -26798,7 +26798,7 @@
       <c r="AA861" s="1"/>
       <c r="AB861" s="1"/>
     </row>
-    <row r="862" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -26828,7 +26828,7 @@
       <c r="AA862" s="1"/>
       <c r="AB862" s="1"/>
     </row>
-    <row r="863" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -26858,7 +26858,7 @@
       <c r="AA863" s="1"/>
       <c r="AB863" s="1"/>
     </row>
-    <row r="864" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -26888,7 +26888,7 @@
       <c r="AA864" s="1"/>
       <c r="AB864" s="1"/>
     </row>
-    <row r="865" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -26918,7 +26918,7 @@
       <c r="AA865" s="1"/>
       <c r="AB865" s="1"/>
     </row>
-    <row r="866" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -26948,7 +26948,7 @@
       <c r="AA866" s="1"/>
       <c r="AB866" s="1"/>
     </row>
-    <row r="867" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -26978,7 +26978,7 @@
       <c r="AA867" s="1"/>
       <c r="AB867" s="1"/>
     </row>
-    <row r="868" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -27008,7 +27008,7 @@
       <c r="AA868" s="1"/>
       <c r="AB868" s="1"/>
     </row>
-    <row r="869" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -27038,7 +27038,7 @@
       <c r="AA869" s="1"/>
       <c r="AB869" s="1"/>
     </row>
-    <row r="870" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -27068,7 +27068,7 @@
       <c r="AA870" s="1"/>
       <c r="AB870" s="1"/>
     </row>
-    <row r="871" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -27098,7 +27098,7 @@
       <c r="AA871" s="1"/>
       <c r="AB871" s="1"/>
     </row>
-    <row r="872" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -27128,7 +27128,7 @@
       <c r="AA872" s="1"/>
       <c r="AB872" s="1"/>
     </row>
-    <row r="873" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -27158,7 +27158,7 @@
       <c r="AA873" s="1"/>
       <c r="AB873" s="1"/>
     </row>
-    <row r="874" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -27188,7 +27188,7 @@
       <c r="AA874" s="1"/>
       <c r="AB874" s="1"/>
     </row>
-    <row r="875" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -27218,7 +27218,7 @@
       <c r="AA875" s="1"/>
       <c r="AB875" s="1"/>
     </row>
-    <row r="876" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -27248,7 +27248,7 @@
       <c r="AA876" s="1"/>
       <c r="AB876" s="1"/>
     </row>
-    <row r="877" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -27278,7 +27278,7 @@
       <c r="AA877" s="1"/>
       <c r="AB877" s="1"/>
     </row>
-    <row r="878" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -27308,7 +27308,7 @@
       <c r="AA878" s="1"/>
       <c r="AB878" s="1"/>
     </row>
-    <row r="879" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -27338,7 +27338,7 @@
       <c r="AA879" s="1"/>
       <c r="AB879" s="1"/>
     </row>
-    <row r="880" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -27368,7 +27368,7 @@
       <c r="AA880" s="1"/>
       <c r="AB880" s="1"/>
     </row>
-    <row r="881" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -27398,7 +27398,7 @@
       <c r="AA881" s="1"/>
       <c r="AB881" s="1"/>
     </row>
-    <row r="882" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -27428,7 +27428,7 @@
       <c r="AA882" s="1"/>
       <c r="AB882" s="1"/>
     </row>
-    <row r="883" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -27458,7 +27458,7 @@
       <c r="AA883" s="1"/>
       <c r="AB883" s="1"/>
     </row>
-    <row r="884" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -27488,7 +27488,7 @@
       <c r="AA884" s="1"/>
       <c r="AB884" s="1"/>
     </row>
-    <row r="885" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -27518,7 +27518,7 @@
       <c r="AA885" s="1"/>
       <c r="AB885" s="1"/>
     </row>
-    <row r="886" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -27548,7 +27548,7 @@
       <c r="AA886" s="1"/>
       <c r="AB886" s="1"/>
     </row>
-    <row r="887" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -27578,7 +27578,7 @@
       <c r="AA887" s="1"/>
       <c r="AB887" s="1"/>
     </row>
-    <row r="888" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -27608,7 +27608,7 @@
       <c r="AA888" s="1"/>
       <c r="AB888" s="1"/>
     </row>
-    <row r="889" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -27638,7 +27638,7 @@
       <c r="AA889" s="1"/>
       <c r="AB889" s="1"/>
     </row>
-    <row r="890" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -27668,7 +27668,7 @@
       <c r="AA890" s="1"/>
       <c r="AB890" s="1"/>
     </row>
-    <row r="891" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -27698,7 +27698,7 @@
       <c r="AA891" s="1"/>
       <c r="AB891" s="1"/>
     </row>
-    <row r="892" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -27728,7 +27728,7 @@
       <c r="AA892" s="1"/>
       <c r="AB892" s="1"/>
     </row>
-    <row r="893" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -27758,7 +27758,7 @@
       <c r="AA893" s="1"/>
       <c r="AB893" s="1"/>
     </row>
-    <row r="894" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -27788,7 +27788,7 @@
       <c r="AA894" s="1"/>
       <c r="AB894" s="1"/>
     </row>
-    <row r="895" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -27818,7 +27818,7 @@
       <c r="AA895" s="1"/>
       <c r="AB895" s="1"/>
     </row>
-    <row r="896" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -27848,7 +27848,7 @@
       <c r="AA896" s="1"/>
       <c r="AB896" s="1"/>
     </row>
-    <row r="897" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -27878,7 +27878,7 @@
       <c r="AA897" s="1"/>
       <c r="AB897" s="1"/>
     </row>
-    <row r="898" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -27908,7 +27908,7 @@
       <c r="AA898" s="1"/>
       <c r="AB898" s="1"/>
     </row>
-    <row r="899" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -27938,7 +27938,7 @@
       <c r="AA899" s="1"/>
       <c r="AB899" s="1"/>
     </row>
-    <row r="900" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -27968,7 +27968,7 @@
       <c r="AA900" s="1"/>
       <c r="AB900" s="1"/>
     </row>
-    <row r="901" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -27998,7 +27998,7 @@
       <c r="AA901" s="1"/>
       <c r="AB901" s="1"/>
     </row>
-    <row r="902" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -28028,7 +28028,7 @@
       <c r="AA902" s="1"/>
       <c r="AB902" s="1"/>
     </row>
-    <row r="903" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -28058,7 +28058,7 @@
       <c r="AA903" s="1"/>
       <c r="AB903" s="1"/>
     </row>
-    <row r="904" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -28088,7 +28088,7 @@
       <c r="AA904" s="1"/>
       <c r="AB904" s="1"/>
     </row>
-    <row r="905" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -28118,7 +28118,7 @@
       <c r="AA905" s="1"/>
       <c r="AB905" s="1"/>
     </row>
-    <row r="906" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -28148,7 +28148,7 @@
       <c r="AA906" s="1"/>
       <c r="AB906" s="1"/>
     </row>
-    <row r="907" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -28178,7 +28178,7 @@
       <c r="AA907" s="1"/>
       <c r="AB907" s="1"/>
     </row>
-    <row r="908" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -28208,7 +28208,7 @@
       <c r="AA908" s="1"/>
       <c r="AB908" s="1"/>
     </row>
-    <row r="909" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -28238,7 +28238,7 @@
       <c r="AA909" s="1"/>
       <c r="AB909" s="1"/>
     </row>
-    <row r="910" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -28268,7 +28268,7 @@
       <c r="AA910" s="1"/>
       <c r="AB910" s="1"/>
     </row>
-    <row r="911" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -28298,7 +28298,7 @@
       <c r="AA911" s="1"/>
       <c r="AB911" s="1"/>
     </row>
-    <row r="912" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -28328,7 +28328,7 @@
       <c r="AA912" s="1"/>
       <c r="AB912" s="1"/>
     </row>
-    <row r="913" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -28358,7 +28358,7 @@
       <c r="AA913" s="1"/>
       <c r="AB913" s="1"/>
     </row>
-    <row r="914" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -28388,7 +28388,7 @@
       <c r="AA914" s="1"/>
       <c r="AB914" s="1"/>
     </row>
-    <row r="915" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -28418,7 +28418,7 @@
       <c r="AA915" s="1"/>
       <c r="AB915" s="1"/>
     </row>
-    <row r="916" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -28448,7 +28448,7 @@
       <c r="AA916" s="1"/>
       <c r="AB916" s="1"/>
     </row>
-    <row r="917" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -28478,7 +28478,7 @@
       <c r="AA917" s="1"/>
       <c r="AB917" s="1"/>
     </row>
-    <row r="918" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -28508,7 +28508,7 @@
       <c r="AA918" s="1"/>
       <c r="AB918" s="1"/>
     </row>
-    <row r="919" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -28538,7 +28538,7 @@
       <c r="AA919" s="1"/>
       <c r="AB919" s="1"/>
     </row>
-    <row r="920" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -28568,7 +28568,7 @@
       <c r="AA920" s="1"/>
       <c r="AB920" s="1"/>
     </row>
-    <row r="921" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -28598,7 +28598,7 @@
       <c r="AA921" s="1"/>
       <c r="AB921" s="1"/>
     </row>
-    <row r="922" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -28628,7 +28628,7 @@
       <c r="AA922" s="1"/>
       <c r="AB922" s="1"/>
     </row>
-    <row r="923" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -28658,7 +28658,7 @@
       <c r="AA923" s="1"/>
       <c r="AB923" s="1"/>
     </row>
-    <row r="924" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -28688,7 +28688,7 @@
       <c r="AA924" s="1"/>
       <c r="AB924" s="1"/>
     </row>
-    <row r="925" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -28718,7 +28718,7 @@
       <c r="AA925" s="1"/>
       <c r="AB925" s="1"/>
     </row>
-    <row r="926" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -28748,7 +28748,7 @@
       <c r="AA926" s="1"/>
       <c r="AB926" s="1"/>
     </row>
-    <row r="927" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -28778,7 +28778,7 @@
       <c r="AA927" s="1"/>
       <c r="AB927" s="1"/>
     </row>
-    <row r="928" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -28808,7 +28808,7 @@
       <c r="AA928" s="1"/>
       <c r="AB928" s="1"/>
     </row>
-    <row r="929" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -28838,7 +28838,7 @@
       <c r="AA929" s="1"/>
       <c r="AB929" s="1"/>
     </row>
-    <row r="930" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -28868,7 +28868,7 @@
       <c r="AA930" s="1"/>
       <c r="AB930" s="1"/>
     </row>
-    <row r="931" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -28898,7 +28898,7 @@
       <c r="AA931" s="1"/>
       <c r="AB931" s="1"/>
     </row>
-    <row r="932" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -28928,7 +28928,7 @@
       <c r="AA932" s="1"/>
       <c r="AB932" s="1"/>
     </row>
-    <row r="933" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -28958,7 +28958,7 @@
       <c r="AA933" s="1"/>
       <c r="AB933" s="1"/>
     </row>
-    <row r="934" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -28988,7 +28988,7 @@
       <c r="AA934" s="1"/>
       <c r="AB934" s="1"/>
     </row>
-    <row r="935" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -29018,7 +29018,7 @@
       <c r="AA935" s="1"/>
       <c r="AB935" s="1"/>
     </row>
-    <row r="936" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -29048,7 +29048,7 @@
       <c r="AA936" s="1"/>
       <c r="AB936" s="1"/>
     </row>
-    <row r="937" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -29078,7 +29078,7 @@
       <c r="AA937" s="1"/>
       <c r="AB937" s="1"/>
     </row>
-    <row r="938" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -29108,7 +29108,7 @@
       <c r="AA938" s="1"/>
       <c r="AB938" s="1"/>
     </row>
-    <row r="939" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -29138,7 +29138,7 @@
       <c r="AA939" s="1"/>
       <c r="AB939" s="1"/>
     </row>
-    <row r="940" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -29168,7 +29168,7 @@
       <c r="AA940" s="1"/>
       <c r="AB940" s="1"/>
     </row>
-    <row r="941" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -29198,7 +29198,7 @@
       <c r="AA941" s="1"/>
       <c r="AB941" s="1"/>
     </row>
-    <row r="942" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -29228,7 +29228,7 @@
       <c r="AA942" s="1"/>
       <c r="AB942" s="1"/>
     </row>
-    <row r="943" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -29258,7 +29258,7 @@
       <c r="AA943" s="1"/>
       <c r="AB943" s="1"/>
     </row>
-    <row r="944" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -29288,7 +29288,7 @@
       <c r="AA944" s="1"/>
       <c r="AB944" s="1"/>
     </row>
-    <row r="945" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -29318,7 +29318,7 @@
       <c r="AA945" s="1"/>
       <c r="AB945" s="1"/>
     </row>
-    <row r="946" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -29348,7 +29348,7 @@
       <c r="AA946" s="1"/>
       <c r="AB946" s="1"/>
     </row>
-    <row r="947" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -29378,7 +29378,7 @@
       <c r="AA947" s="1"/>
       <c r="AB947" s="1"/>
     </row>
-    <row r="948" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -29408,7 +29408,7 @@
       <c r="AA948" s="1"/>
       <c r="AB948" s="1"/>
     </row>
-    <row r="949" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -29438,7 +29438,7 @@
       <c r="AA949" s="1"/>
       <c r="AB949" s="1"/>
     </row>
-    <row r="950" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -29468,7 +29468,7 @@
       <c r="AA950" s="1"/>
       <c r="AB950" s="1"/>
     </row>
-    <row r="951" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -29498,7 +29498,7 @@
       <c r="AA951" s="1"/>
       <c r="AB951" s="1"/>
     </row>
-    <row r="952" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -29528,7 +29528,7 @@
       <c r="AA952" s="1"/>
       <c r="AB952" s="1"/>
     </row>
-    <row r="953" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -29558,7 +29558,7 @@
       <c r="AA953" s="1"/>
       <c r="AB953" s="1"/>
     </row>
-    <row r="954" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -29588,7 +29588,7 @@
       <c r="AA954" s="1"/>
       <c r="AB954" s="1"/>
     </row>
-    <row r="955" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -29618,7 +29618,7 @@
       <c r="AA955" s="1"/>
       <c r="AB955" s="1"/>
     </row>
-    <row r="956" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -29648,7 +29648,7 @@
       <c r="AA956" s="1"/>
       <c r="AB956" s="1"/>
     </row>
-    <row r="957" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -29678,7 +29678,7 @@
       <c r="AA957" s="1"/>
       <c r="AB957" s="1"/>
     </row>
-    <row r="958" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -29708,7 +29708,7 @@
       <c r="AA958" s="1"/>
       <c r="AB958" s="1"/>
     </row>
-    <row r="959" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -29738,7 +29738,7 @@
       <c r="AA959" s="1"/>
       <c r="AB959" s="1"/>
     </row>
-    <row r="960" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -29768,7 +29768,7 @@
       <c r="AA960" s="1"/>
       <c r="AB960" s="1"/>
     </row>
-    <row r="961" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -29798,7 +29798,7 @@
       <c r="AA961" s="1"/>
       <c r="AB961" s="1"/>
     </row>
-    <row r="962" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -29828,7 +29828,7 @@
       <c r="AA962" s="1"/>
       <c r="AB962" s="1"/>
     </row>
-    <row r="963" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -29858,7 +29858,7 @@
       <c r="AA963" s="1"/>
       <c r="AB963" s="1"/>
     </row>
-    <row r="964" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -29888,7 +29888,7 @@
       <c r="AA964" s="1"/>
       <c r="AB964" s="1"/>
     </row>
-    <row r="965" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -29918,7 +29918,7 @@
       <c r="AA965" s="1"/>
       <c r="AB965" s="1"/>
     </row>
-    <row r="966" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -29948,7 +29948,7 @@
       <c r="AA966" s="1"/>
       <c r="AB966" s="1"/>
     </row>
-    <row r="967" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -29978,7 +29978,7 @@
       <c r="AA967" s="1"/>
       <c r="AB967" s="1"/>
     </row>
-    <row r="968" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -30008,7 +30008,7 @@
       <c r="AA968" s="1"/>
       <c r="AB968" s="1"/>
     </row>
-    <row r="969" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -30038,7 +30038,7 @@
       <c r="AA969" s="1"/>
       <c r="AB969" s="1"/>
     </row>
-    <row r="970" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -30068,7 +30068,7 @@
       <c r="AA970" s="1"/>
       <c r="AB970" s="1"/>
     </row>
-    <row r="971" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -30098,7 +30098,7 @@
       <c r="AA971" s="1"/>
       <c r="AB971" s="1"/>
     </row>
-    <row r="972" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -30128,7 +30128,7 @@
       <c r="AA972" s="1"/>
       <c r="AB972" s="1"/>
     </row>
-    <row r="973" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -30158,7 +30158,7 @@
       <c r="AA973" s="1"/>
       <c r="AB973" s="1"/>
     </row>
-    <row r="974" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -30188,7 +30188,7 @@
       <c r="AA974" s="1"/>
       <c r="AB974" s="1"/>
     </row>
-    <row r="975" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -30218,7 +30218,7 @@
       <c r="AA975" s="1"/>
       <c r="AB975" s="1"/>
     </row>
-    <row r="976" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -30248,7 +30248,7 @@
       <c r="AA976" s="1"/>
       <c r="AB976" s="1"/>
     </row>
-    <row r="977" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -30278,7 +30278,7 @@
       <c r="AA977" s="1"/>
       <c r="AB977" s="1"/>
     </row>
-    <row r="978" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -30308,7 +30308,7 @@
       <c r="AA978" s="1"/>
       <c r="AB978" s="1"/>
     </row>
-    <row r="979" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -30338,7 +30338,7 @@
       <c r="AA979" s="1"/>
       <c r="AB979" s="1"/>
     </row>
-    <row r="980" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -30368,7 +30368,7 @@
       <c r="AA980" s="1"/>
       <c r="AB980" s="1"/>
     </row>
-    <row r="981" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -30398,7 +30398,7 @@
       <c r="AA981" s="1"/>
       <c r="AB981" s="1"/>
     </row>
-    <row r="982" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -30428,7 +30428,7 @@
       <c r="AA982" s="1"/>
       <c r="AB982" s="1"/>
     </row>
-    <row r="983" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -30458,7 +30458,7 @@
       <c r="AA983" s="1"/>
       <c r="AB983" s="1"/>
     </row>
-    <row r="984" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -30488,7 +30488,7 @@
       <c r="AA984" s="1"/>
       <c r="AB984" s="1"/>
     </row>
-    <row r="985" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -30518,7 +30518,7 @@
       <c r="AA985" s="1"/>
       <c r="AB985" s="1"/>
     </row>
-    <row r="986" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -30548,7 +30548,7 @@
       <c r="AA986" s="1"/>
       <c r="AB986" s="1"/>
     </row>
-    <row r="987" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -30578,7 +30578,7 @@
       <c r="AA987" s="1"/>
       <c r="AB987" s="1"/>
     </row>
-    <row r="988" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -30608,7 +30608,7 @@
       <c r="AA988" s="1"/>
       <c r="AB988" s="1"/>
     </row>
-    <row r="989" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -30638,7 +30638,7 @@
       <c r="AA989" s="1"/>
       <c r="AB989" s="1"/>
     </row>
-    <row r="990" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -30668,7 +30668,7 @@
       <c r="AA990" s="1"/>
       <c r="AB990" s="1"/>
     </row>
-    <row r="991" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -30698,7 +30698,7 @@
       <c r="AA991" s="1"/>
       <c r="AB991" s="1"/>
     </row>
-    <row r="992" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -30728,7 +30728,7 @@
       <c r="AA992" s="1"/>
       <c r="AB992" s="1"/>
     </row>
-    <row r="993" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -30758,7 +30758,7 @@
       <c r="AA993" s="1"/>
       <c r="AB993" s="1"/>
     </row>
-    <row r="994" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -30788,7 +30788,7 @@
       <c r="AA994" s="1"/>
       <c r="AB994" s="1"/>
     </row>
-    <row r="995" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -30818,7 +30818,7 @@
       <c r="AA995" s="1"/>
       <c r="AB995" s="1"/>
     </row>
-    <row r="996" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -30848,7 +30848,7 @@
       <c r="AA996" s="1"/>
       <c r="AB996" s="1"/>
     </row>
-    <row r="997" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -30878,7 +30878,7 @@
       <c r="AA997" s="1"/>
       <c r="AB997" s="1"/>
     </row>
-    <row r="998" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -30908,7 +30908,7 @@
       <c r="AA998" s="1"/>
       <c r="AB998" s="1"/>
     </row>
-    <row r="999" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -30938,7 +30938,7 @@
       <c r="AA999" s="1"/>
       <c r="AB999" s="1"/>
     </row>
-    <row r="1000" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -30968,7 +30968,7 @@
       <c r="AA1000" s="1"/>
       <c r="AB1000" s="1"/>
     </row>
-    <row r="1001" spans="1:28" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>
